--- a/public/file/International Standard Rates Upload Template.xlsx
+++ b/public/file/International Standard Rates Upload Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0450E015-3FEE-4033-8631-042FE3D99402}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FDE8F72-4131-496C-B10C-5DB9BDC38F2D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="348" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,9 +26,6 @@
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <t>Range up</t>
-  </si>
   <si>
     <t>Range Down</t>
   </si>
@@ -65,6 +62,9 @@
   <si>
     <t>Zone 11</t>
   </si>
+  <si>
+    <t>Range Up</t>
+  </si>
 </sst>
 </file>
 
@@ -89,14 +89,13 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color rgb="FF000000"/>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="13"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -186,26 +185,26 @@
   </cellStyleXfs>
   <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -493,48 +492,48 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
+      <c r="A2" s="1">
         <v>0.01</v>
       </c>
       <c r="B2" s="4">
@@ -542,7 +541,7 @@
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
+      <c r="A3" s="1">
         <v>0.51</v>
       </c>
       <c r="B3" s="4">
@@ -550,7 +549,7 @@
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
+      <c r="A4" s="1">
         <v>1.01</v>
       </c>
       <c r="B4" s="4">
@@ -558,7 +557,7 @@
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A5" s="3">
+      <c r="A5" s="1">
         <v>1.51</v>
       </c>
       <c r="B5" s="4">
@@ -566,7 +565,7 @@
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A6" s="3">
+      <c r="A6" s="1">
         <v>2.0099999999999998</v>
       </c>
       <c r="B6" s="4">
@@ -574,7 +573,7 @@
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A7" s="3">
+      <c r="A7" s="1">
         <v>2.5099999999999998</v>
       </c>
       <c r="B7" s="4">
@@ -582,7 +581,7 @@
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A8" s="3">
+      <c r="A8" s="1">
         <v>3.01</v>
       </c>
       <c r="B8" s="4">
@@ -590,7 +589,7 @@
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A9" s="3">
+      <c r="A9" s="1">
         <v>3.51</v>
       </c>
       <c r="B9" s="4">
@@ -598,7 +597,7 @@
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A10" s="3">
+      <c r="A10" s="1">
         <v>4.01</v>
       </c>
       <c r="B10" s="4">
@@ -606,7 +605,7 @@
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A11" s="3">
+      <c r="A11" s="1">
         <v>4.51</v>
       </c>
       <c r="B11" s="4">
@@ -614,7 +613,7 @@
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A12" s="3">
+      <c r="A12" s="1">
         <v>5.01</v>
       </c>
       <c r="B12" s="4">
@@ -622,7 +621,7 @@
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A13" s="3">
+      <c r="A13" s="1">
         <v>5.51</v>
       </c>
       <c r="B13" s="4">
@@ -630,7 +629,7 @@
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A14" s="3">
+      <c r="A14" s="1">
         <v>6.01</v>
       </c>
       <c r="B14" s="4">
@@ -638,7 +637,7 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A15" s="3">
+      <c r="A15" s="1">
         <v>6.51</v>
       </c>
       <c r="B15" s="4">
@@ -646,7 +645,7 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A16" s="3">
+      <c r="A16" s="1">
         <v>7.01</v>
       </c>
       <c r="B16" s="4">
@@ -654,7 +653,7 @@
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="3">
+      <c r="A17" s="1">
         <v>7.51</v>
       </c>
       <c r="B17" s="4">
@@ -662,7 +661,7 @@
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="3">
+      <c r="A18" s="1">
         <v>8.01</v>
       </c>
       <c r="B18" s="4">
@@ -670,7 +669,7 @@
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="3">
+      <c r="A19" s="1">
         <v>8.51</v>
       </c>
       <c r="B19" s="4">
@@ -678,7 +677,7 @@
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="3">
+      <c r="A20" s="1">
         <v>9.01</v>
       </c>
       <c r="B20" s="4">
@@ -686,7 +685,7 @@
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="3">
+      <c r="A21" s="1">
         <v>9.51</v>
       </c>
       <c r="B21" s="4">
@@ -694,7 +693,7 @@
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="3">
+      <c r="A22" s="1">
         <v>10.01</v>
       </c>
       <c r="B22" s="4">
@@ -702,7 +701,7 @@
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="3">
+      <c r="A23" s="1">
         <v>10.51</v>
       </c>
       <c r="B23" s="4">
@@ -710,7 +709,7 @@
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="3">
+      <c r="A24" s="1">
         <v>11.01</v>
       </c>
       <c r="B24" s="4">
@@ -718,7 +717,7 @@
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="3">
+      <c r="A25" s="1">
         <v>11.51</v>
       </c>
       <c r="B25" s="4">
@@ -726,7 +725,7 @@
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="3">
+      <c r="A26" s="1">
         <v>12.01</v>
       </c>
       <c r="B26" s="4">
@@ -734,7 +733,7 @@
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="3">
+      <c r="A27" s="1">
         <v>12.51</v>
       </c>
       <c r="B27" s="4">
@@ -742,7 +741,7 @@
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="3">
+      <c r="A28" s="1">
         <v>13.01</v>
       </c>
       <c r="B28" s="4">
@@ -750,7 +749,7 @@
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="3">
+      <c r="A29" s="1">
         <v>13.51</v>
       </c>
       <c r="B29" s="4">
@@ -758,7 +757,7 @@
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A30" s="3">
+      <c r="A30" s="1">
         <v>14.01</v>
       </c>
       <c r="B30" s="4">
@@ -766,7 +765,7 @@
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A31" s="3">
+      <c r="A31" s="1">
         <v>14.51</v>
       </c>
       <c r="B31" s="4">
@@ -774,7 +773,7 @@
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A32" s="3">
+      <c r="A32" s="1">
         <v>15.01</v>
       </c>
       <c r="B32" s="4">
@@ -782,7 +781,7 @@
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A33" s="3">
+      <c r="A33" s="1">
         <v>15.51</v>
       </c>
       <c r="B33" s="4">
@@ -790,7 +789,7 @@
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A34" s="3">
+      <c r="A34" s="1">
         <v>16.010000000000002</v>
       </c>
       <c r="B34" s="4">
@@ -798,7 +797,7 @@
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A35" s="3">
+      <c r="A35" s="1">
         <v>16.510000000000002</v>
       </c>
       <c r="B35" s="4">
@@ -806,7 +805,7 @@
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A36" s="3">
+      <c r="A36" s="1">
         <v>17.010000000000002</v>
       </c>
       <c r="B36" s="4">
@@ -814,7 +813,7 @@
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A37" s="3">
+      <c r="A37" s="1">
         <v>17.510000000000002</v>
       </c>
       <c r="B37" s="4">
@@ -822,7 +821,7 @@
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A38" s="3">
+      <c r="A38" s="1">
         <v>18.010000000000002</v>
       </c>
       <c r="B38" s="4">
@@ -830,7 +829,7 @@
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A39" s="3">
+      <c r="A39" s="1">
         <v>18.510000000000002</v>
       </c>
       <c r="B39" s="4">
@@ -838,7 +837,7 @@
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A40" s="3">
+      <c r="A40" s="1">
         <v>19.010000000000002</v>
       </c>
       <c r="B40" s="4">
@@ -846,7 +845,7 @@
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A41" s="3">
+      <c r="A41" s="1">
         <v>19.510000000000002</v>
       </c>
       <c r="B41" s="5">
@@ -854,7 +853,7 @@
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A42" s="3">
+      <c r="A42" s="1">
         <v>20.010000000000002</v>
       </c>
       <c r="B42" s="4">
@@ -862,7 +861,7 @@
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A43" s="3">
+      <c r="A43" s="1">
         <v>20.51</v>
       </c>
       <c r="B43" s="4">
@@ -870,7 +869,7 @@
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A44" s="3">
+      <c r="A44" s="1">
         <v>21.01</v>
       </c>
       <c r="B44" s="4">
@@ -878,7 +877,7 @@
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A45" s="3">
+      <c r="A45" s="1">
         <v>21.51</v>
       </c>
       <c r="B45" s="4">
@@ -886,7 +885,7 @@
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A46" s="3">
+      <c r="A46" s="1">
         <v>22.01</v>
       </c>
       <c r="B46" s="4">
@@ -894,7 +893,7 @@
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A47" s="3">
+      <c r="A47" s="1">
         <v>22.51</v>
       </c>
       <c r="B47" s="4">
@@ -902,7 +901,7 @@
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A48" s="3">
+      <c r="A48" s="1">
         <v>23.01</v>
       </c>
       <c r="B48" s="4">
@@ -910,7 +909,7 @@
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A49" s="3">
+      <c r="A49" s="1">
         <v>23.51</v>
       </c>
       <c r="B49" s="4">
@@ -918,7 +917,7 @@
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A50" s="3">
+      <c r="A50" s="1">
         <v>24.01</v>
       </c>
       <c r="B50" s="4">
@@ -926,7 +925,7 @@
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A51" s="3">
+      <c r="A51" s="1">
         <v>24.51</v>
       </c>
       <c r="B51" s="4">
@@ -934,7 +933,7 @@
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A52" s="3">
+      <c r="A52" s="1">
         <v>25.01</v>
       </c>
       <c r="B52" s="4">
@@ -942,7 +941,7 @@
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A53" s="3">
+      <c r="A53" s="1">
         <v>25.51</v>
       </c>
       <c r="B53" s="4">
@@ -950,7 +949,7 @@
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A54" s="3">
+      <c r="A54" s="1">
         <v>26.01</v>
       </c>
       <c r="B54" s="4">
@@ -958,7 +957,7 @@
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A55" s="3">
+      <c r="A55" s="1">
         <v>26.51</v>
       </c>
       <c r="B55" s="4">
@@ -966,7 +965,7 @@
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A56" s="3">
+      <c r="A56" s="1">
         <v>27.01</v>
       </c>
       <c r="B56" s="4">
@@ -974,7 +973,7 @@
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A57" s="3">
+      <c r="A57" s="1">
         <v>27.51</v>
       </c>
       <c r="B57" s="4">
@@ -982,7 +981,7 @@
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A58" s="3">
+      <c r="A58" s="1">
         <v>28.01</v>
       </c>
       <c r="B58" s="4">
@@ -990,7 +989,7 @@
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A59" s="3">
+      <c r="A59" s="1">
         <v>28.51</v>
       </c>
       <c r="B59" s="4">
@@ -998,7 +997,7 @@
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A60" s="3">
+      <c r="A60" s="1">
         <v>29.01</v>
       </c>
       <c r="B60" s="4">
@@ -1006,7 +1005,7 @@
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A61" s="3">
+      <c r="A61" s="1">
         <v>29.51</v>
       </c>
       <c r="B61" s="4">
@@ -1014,7 +1013,7 @@
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A62" s="3">
+      <c r="A62" s="1">
         <v>30.01</v>
       </c>
       <c r="B62" s="6">
@@ -1022,7 +1021,7 @@
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A63" s="3">
+      <c r="A63" s="1">
         <v>30.51</v>
       </c>
       <c r="B63" s="7">
@@ -1030,7 +1029,7 @@
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A64" s="3">
+      <c r="A64" s="1">
         <v>31.01</v>
       </c>
       <c r="B64" s="7">
@@ -1038,7 +1037,7 @@
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A65" s="3">
+      <c r="A65" s="1">
         <v>31.51</v>
       </c>
       <c r="B65" s="7">
@@ -1046,7 +1045,7 @@
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A66" s="3">
+      <c r="A66" s="1">
         <v>32.01</v>
       </c>
       <c r="B66" s="7">
@@ -1054,7 +1053,7 @@
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A67" s="3">
+      <c r="A67" s="1">
         <v>32.51</v>
       </c>
       <c r="B67" s="7">
@@ -1062,7 +1061,7 @@
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A68" s="3">
+      <c r="A68" s="1">
         <v>33.01</v>
       </c>
       <c r="B68" s="7">
@@ -1070,7 +1069,7 @@
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A69" s="3">
+      <c r="A69" s="1">
         <v>33.51</v>
       </c>
       <c r="B69" s="7">
@@ -1078,7 +1077,7 @@
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A70" s="3">
+      <c r="A70" s="1">
         <v>34.01</v>
       </c>
       <c r="B70" s="7">
@@ -1086,7 +1085,7 @@
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="3">
+      <c r="A71" s="1">
         <v>34.51</v>
       </c>
       <c r="B71" s="7">
@@ -1094,7 +1093,7 @@
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A72" s="3">
+      <c r="A72" s="1">
         <v>35.01</v>
       </c>
       <c r="B72" s="7">
@@ -1102,7 +1101,7 @@
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A73" s="3">
+      <c r="A73" s="1">
         <v>35.51</v>
       </c>
       <c r="B73" s="7">
@@ -1110,7 +1109,7 @@
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A74" s="3">
+      <c r="A74" s="1">
         <v>36.01</v>
       </c>
       <c r="B74" s="7">
@@ -1118,7 +1117,7 @@
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" s="3">
+      <c r="A75" s="1">
         <v>36.51</v>
       </c>
       <c r="B75" s="7">
@@ -1126,7 +1125,7 @@
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A76" s="3">
+      <c r="A76" s="1">
         <v>37.01</v>
       </c>
       <c r="B76" s="7">
@@ -1134,7 +1133,7 @@
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A77" s="3">
+      <c r="A77" s="1">
         <v>37.51</v>
       </c>
       <c r="B77" s="7">
@@ -1142,7 +1141,7 @@
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A78" s="3">
+      <c r="A78" s="1">
         <v>38.01</v>
       </c>
       <c r="B78" s="7">
@@ -1150,7 +1149,7 @@
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A79" s="3">
+      <c r="A79" s="1">
         <v>38.51</v>
       </c>
       <c r="B79" s="7">
@@ -1158,7 +1157,7 @@
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A80" s="3">
+      <c r="A80" s="1">
         <v>39.01</v>
       </c>
       <c r="B80" s="7">
@@ -1166,7 +1165,7 @@
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A81" s="3">
+      <c r="A81" s="1">
         <v>39.51</v>
       </c>
       <c r="B81" s="7">
@@ -1174,7 +1173,7 @@
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A82" s="3">
+      <c r="A82" s="1">
         <v>40.01</v>
       </c>
       <c r="B82" s="7">
@@ -1182,7 +1181,7 @@
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A83" s="3">
+      <c r="A83" s="1">
         <v>40.51</v>
       </c>
       <c r="B83" s="7">
@@ -1190,7 +1189,7 @@
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A84" s="3">
+      <c r="A84" s="1">
         <v>41.01</v>
       </c>
       <c r="B84" s="7">
@@ -1198,7 +1197,7 @@
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A85" s="3">
+      <c r="A85" s="1">
         <v>41.51</v>
       </c>
       <c r="B85" s="7">
@@ -1206,7 +1205,7 @@
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A86" s="3">
+      <c r="A86" s="1">
         <v>42.01</v>
       </c>
       <c r="B86" s="7">
@@ -1214,7 +1213,7 @@
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A87" s="3">
+      <c r="A87" s="1">
         <v>42.51</v>
       </c>
       <c r="B87" s="7">
@@ -1222,7 +1221,7 @@
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A88" s="3">
+      <c r="A88" s="1">
         <v>43.01</v>
       </c>
       <c r="B88" s="7">
@@ -1230,7 +1229,7 @@
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A89" s="3">
+      <c r="A89" s="1">
         <v>43.51</v>
       </c>
       <c r="B89" s="7">
@@ -1238,7 +1237,7 @@
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A90" s="3">
+      <c r="A90" s="1">
         <v>44.01</v>
       </c>
       <c r="B90" s="7">
@@ -1246,7 +1245,7 @@
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A91" s="3">
+      <c r="A91" s="1">
         <v>44.51</v>
       </c>
       <c r="B91" s="7">
@@ -1254,7 +1253,7 @@
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A92" s="3">
+      <c r="A92" s="1">
         <v>45.01</v>
       </c>
       <c r="B92" s="7">
@@ -1262,7 +1261,7 @@
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A93" s="3">
+      <c r="A93" s="1">
         <v>45.51</v>
       </c>
       <c r="B93" s="7">
@@ -1270,7 +1269,7 @@
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A94" s="3">
+      <c r="A94" s="1">
         <v>46.01</v>
       </c>
       <c r="B94" s="7">
@@ -1278,7 +1277,7 @@
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A95" s="3">
+      <c r="A95" s="1">
         <v>46.51</v>
       </c>
       <c r="B95" s="7">
@@ -1286,7 +1285,7 @@
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A96" s="3">
+      <c r="A96" s="1">
         <v>47.01</v>
       </c>
       <c r="B96" s="7">
@@ -1294,7 +1293,7 @@
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A97" s="3">
+      <c r="A97" s="1">
         <v>47.51</v>
       </c>
       <c r="B97" s="7">
@@ -1302,7 +1301,7 @@
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A98" s="3">
+      <c r="A98" s="1">
         <v>48.01</v>
       </c>
       <c r="B98" s="7">
@@ -1310,7 +1309,7 @@
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A99" s="3">
+      <c r="A99" s="1">
         <v>48.51</v>
       </c>
       <c r="B99" s="7">
@@ -1318,7 +1317,7 @@
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A100" s="3">
+      <c r="A100" s="1">
         <v>49.01</v>
       </c>
       <c r="B100" s="7">
@@ -1326,7 +1325,7 @@
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A101" s="3">
+      <c r="A101" s="1">
         <v>49.51</v>
       </c>
       <c r="B101" s="7">
@@ -1334,7 +1333,7 @@
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A102" s="3">
+      <c r="A102" s="1">
         <v>50.01</v>
       </c>
       <c r="B102" s="7">
@@ -1342,7 +1341,7 @@
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A103" s="3">
+      <c r="A103" s="1">
         <v>50.51</v>
       </c>
       <c r="B103" s="7">
@@ -1350,7 +1349,7 @@
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A104" s="3">
+      <c r="A104" s="1">
         <v>51.01</v>
       </c>
       <c r="B104" s="7">
@@ -1358,7 +1357,7 @@
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A105" s="3">
+      <c r="A105" s="1">
         <v>51.51</v>
       </c>
       <c r="B105" s="7">
@@ -1366,7 +1365,7 @@
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A106" s="3">
+      <c r="A106" s="1">
         <v>52.01</v>
       </c>
       <c r="B106" s="7">
@@ -1374,7 +1373,7 @@
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A107" s="3">
+      <c r="A107" s="1">
         <v>52.51</v>
       </c>
       <c r="B107" s="7">
@@ -1382,7 +1381,7 @@
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A108" s="3">
+      <c r="A108" s="1">
         <v>53.01</v>
       </c>
       <c r="B108" s="7">
@@ -1390,7 +1389,7 @@
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A109" s="3">
+      <c r="A109" s="1">
         <v>53.51</v>
       </c>
       <c r="B109" s="7">
@@ -1398,7 +1397,7 @@
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A110" s="3">
+      <c r="A110" s="1">
         <v>54.01</v>
       </c>
       <c r="B110" s="7">
@@ -1406,7 +1405,7 @@
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A111" s="3">
+      <c r="A111" s="1">
         <v>54.51</v>
       </c>
       <c r="B111" s="7">
@@ -1414,7 +1413,7 @@
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A112" s="3">
+      <c r="A112" s="1">
         <v>55.01</v>
       </c>
       <c r="B112" s="7">
@@ -1422,7 +1421,7 @@
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A113" s="3">
+      <c r="A113" s="1">
         <v>55.51</v>
       </c>
       <c r="B113" s="7">
@@ -1430,7 +1429,7 @@
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A114" s="3">
+      <c r="A114" s="1">
         <v>56.01</v>
       </c>
       <c r="B114" s="7">
@@ -1438,7 +1437,7 @@
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A115" s="3">
+      <c r="A115" s="1">
         <v>56.51</v>
       </c>
       <c r="B115" s="7">
@@ -1446,7 +1445,7 @@
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A116" s="3">
+      <c r="A116" s="1">
         <v>57.01</v>
       </c>
       <c r="B116" s="7">
@@ -1454,7 +1453,7 @@
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A117" s="3">
+      <c r="A117" s="1">
         <v>57.51</v>
       </c>
       <c r="B117" s="7">
@@ -1462,7 +1461,7 @@
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A118" s="3">
+      <c r="A118" s="1">
         <v>58.01</v>
       </c>
       <c r="B118" s="7">
@@ -1470,7 +1469,7 @@
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A119" s="3">
+      <c r="A119" s="1">
         <v>58.51</v>
       </c>
       <c r="B119" s="7">
@@ -1478,7 +1477,7 @@
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A120" s="3">
+      <c r="A120" s="1">
         <v>59.01</v>
       </c>
       <c r="B120" s="7">
@@ -1486,7 +1485,7 @@
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A121" s="3">
+      <c r="A121" s="1">
         <v>59.51</v>
       </c>
       <c r="B121" s="7">
@@ -1494,7 +1493,7 @@
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A122" s="3">
+      <c r="A122" s="1">
         <v>60.01</v>
       </c>
       <c r="B122" s="7">
@@ -1502,7 +1501,7 @@
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A123" s="3">
+      <c r="A123" s="1">
         <v>60.51</v>
       </c>
       <c r="B123" s="7">
@@ -1510,7 +1509,7 @@
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A124" s="3">
+      <c r="A124" s="1">
         <v>61.01</v>
       </c>
       <c r="B124" s="7">
@@ -1518,7 +1517,7 @@
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A125" s="3">
+      <c r="A125" s="1">
         <v>61.51</v>
       </c>
       <c r="B125" s="7">
@@ -1526,7 +1525,7 @@
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A126" s="3">
+      <c r="A126" s="1">
         <v>62.01</v>
       </c>
       <c r="B126" s="7">
@@ -1534,7 +1533,7 @@
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A127" s="3">
+      <c r="A127" s="1">
         <v>62.51</v>
       </c>
       <c r="B127" s="7">
@@ -1542,7 +1541,7 @@
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A128" s="3">
+      <c r="A128" s="1">
         <v>63.01</v>
       </c>
       <c r="B128" s="7">
@@ -1550,7 +1549,7 @@
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A129" s="3">
+      <c r="A129" s="1">
         <v>63.51</v>
       </c>
       <c r="B129" s="7">
@@ -1558,7 +1557,7 @@
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A130" s="3">
+      <c r="A130" s="1">
         <v>64.010000000000005</v>
       </c>
       <c r="B130" s="7">
@@ -1566,7 +1565,7 @@
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A131" s="3">
+      <c r="A131" s="1">
         <v>64.510000000000005</v>
       </c>
       <c r="B131" s="7">
@@ -1574,7 +1573,7 @@
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A132" s="3">
+      <c r="A132" s="1">
         <v>65.010000000000005</v>
       </c>
       <c r="B132" s="7">
@@ -1582,7 +1581,7 @@
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A133" s="3">
+      <c r="A133" s="1">
         <v>65.510000000000005</v>
       </c>
       <c r="B133" s="7">
@@ -1590,7 +1589,7 @@
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A134" s="3">
+      <c r="A134" s="1">
         <v>66.010000000000005</v>
       </c>
       <c r="B134" s="7">
@@ -1598,7 +1597,7 @@
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A135" s="3">
+      <c r="A135" s="1">
         <v>66.510000000000005</v>
       </c>
       <c r="B135" s="7">
@@ -1606,7 +1605,7 @@
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A136" s="3">
+      <c r="A136" s="1">
         <v>67.010000000000005</v>
       </c>
       <c r="B136" s="7">
@@ -1614,7 +1613,7 @@
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A137" s="3">
+      <c r="A137" s="1">
         <v>67.510000000000005</v>
       </c>
       <c r="B137" s="7">
@@ -1622,7 +1621,7 @@
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A138" s="3">
+      <c r="A138" s="1">
         <v>68.010000000000005</v>
       </c>
       <c r="B138" s="7">
@@ -1630,7 +1629,7 @@
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A139" s="3">
+      <c r="A139" s="1">
         <v>68.510000000000005</v>
       </c>
       <c r="B139" s="7">
@@ -1638,7 +1637,7 @@
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A140" s="3">
+      <c r="A140" s="1">
         <v>69.010000000000005</v>
       </c>
       <c r="B140" s="7">
@@ -1646,7 +1645,7 @@
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A141" s="3">
+      <c r="A141" s="1">
         <v>69.510000000000005</v>
       </c>
       <c r="B141" s="7">
@@ -1654,7 +1653,7 @@
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A142" s="3">
+      <c r="A142" s="1">
         <v>70.010000000000005</v>
       </c>
       <c r="B142" s="7">
@@ -1662,7 +1661,7 @@
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A143" s="3">
+      <c r="A143" s="1">
         <v>70.510000000000005</v>
       </c>
       <c r="B143" s="7">
@@ -1670,7 +1669,7 @@
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A144" s="3">
+      <c r="A144" s="1">
         <v>71.010000000000005</v>
       </c>
       <c r="B144" s="7">
@@ -1678,7 +1677,7 @@
       </c>
     </row>
     <row r="145" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A145" s="3">
+      <c r="A145" s="1">
         <v>71.510000000000005</v>
       </c>
       <c r="B145" s="7">
@@ -1686,7 +1685,7 @@
       </c>
     </row>
     <row r="146" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A146" s="3">
+      <c r="A146" s="1">
         <v>72.010000000000005</v>
       </c>
       <c r="B146" s="7">
@@ -1694,7 +1693,7 @@
       </c>
     </row>
     <row r="147" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A147" s="3">
+      <c r="A147" s="1">
         <v>72.510000000000005</v>
       </c>
       <c r="B147" s="7">
@@ -1702,7 +1701,7 @@
       </c>
     </row>
     <row r="148" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A148" s="3">
+      <c r="A148" s="1">
         <v>73.010000000000005</v>
       </c>
       <c r="B148" s="7">
@@ -1710,7 +1709,7 @@
       </c>
     </row>
     <row r="149" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A149" s="3">
+      <c r="A149" s="1">
         <v>73.510000000000005</v>
       </c>
       <c r="B149" s="7">
@@ -1718,7 +1717,7 @@
       </c>
     </row>
     <row r="150" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A150" s="3">
+      <c r="A150" s="1">
         <v>74.010000000000005</v>
       </c>
       <c r="B150" s="7">
@@ -1726,7 +1725,7 @@
       </c>
     </row>
     <row r="151" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A151" s="3">
+      <c r="A151" s="1">
         <v>74.510000000000005</v>
       </c>
       <c r="B151" s="7">
@@ -1734,7 +1733,7 @@
       </c>
     </row>
     <row r="152" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A152" s="3">
+      <c r="A152" s="1">
         <v>75.010000000000005</v>
       </c>
       <c r="B152" s="7">
@@ -1742,7 +1741,7 @@
       </c>
     </row>
     <row r="153" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A153" s="3">
+      <c r="A153" s="1">
         <v>75.510000000000005</v>
       </c>
       <c r="B153" s="7">
@@ -1750,7 +1749,7 @@
       </c>
     </row>
     <row r="154" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A154" s="3">
+      <c r="A154" s="1">
         <v>76.010000000000005</v>
       </c>
       <c r="B154" s="7">
@@ -1758,7 +1757,7 @@
       </c>
     </row>
     <row r="155" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A155" s="3">
+      <c r="A155" s="1">
         <v>76.510000000000005</v>
       </c>
       <c r="B155" s="7">
@@ -1766,7 +1765,7 @@
       </c>
     </row>
     <row r="156" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A156" s="3">
+      <c r="A156" s="1">
         <v>77.010000000000005</v>
       </c>
       <c r="B156" s="7">
@@ -1774,7 +1773,7 @@
       </c>
     </row>
     <row r="157" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A157" s="3">
+      <c r="A157" s="1">
         <v>77.510000000000005</v>
       </c>
       <c r="B157" s="7">
@@ -1782,7 +1781,7 @@
       </c>
     </row>
     <row r="158" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A158" s="3">
+      <c r="A158" s="1">
         <v>78.010000000000005</v>
       </c>
       <c r="B158" s="7">
@@ -1790,7 +1789,7 @@
       </c>
     </row>
     <row r="159" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A159" s="3">
+      <c r="A159" s="1">
         <v>78.510000000000005</v>
       </c>
       <c r="B159" s="7">
@@ -1798,7 +1797,7 @@
       </c>
     </row>
     <row r="160" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A160" s="3">
+      <c r="A160" s="1">
         <v>79.010000000000005</v>
       </c>
       <c r="B160" s="7">
@@ -1806,7 +1805,7 @@
       </c>
     </row>
     <row r="161" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A161" s="3">
+      <c r="A161" s="1">
         <v>79.510000000000005</v>
       </c>
       <c r="B161" s="7">
@@ -1814,7 +1813,7 @@
       </c>
     </row>
     <row r="162" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A162" s="3">
+      <c r="A162" s="1">
         <v>80.010000000000005</v>
       </c>
       <c r="B162" s="7">
@@ -1822,7 +1821,7 @@
       </c>
     </row>
     <row r="163" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A163" s="3">
+      <c r="A163" s="1">
         <v>80.510000000000005</v>
       </c>
       <c r="B163" s="7">
@@ -1830,7 +1829,7 @@
       </c>
     </row>
     <row r="164" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A164" s="3">
+      <c r="A164" s="1">
         <v>81.010000000000005</v>
       </c>
       <c r="B164" s="7">
@@ -1838,7 +1837,7 @@
       </c>
     </row>
     <row r="165" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A165" s="3">
+      <c r="A165" s="1">
         <v>81.510000000000005</v>
       </c>
       <c r="B165" s="7">
@@ -1846,7 +1845,7 @@
       </c>
     </row>
     <row r="166" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A166" s="3">
+      <c r="A166" s="1">
         <v>82.01</v>
       </c>
       <c r="B166" s="7">
@@ -1854,7 +1853,7 @@
       </c>
     </row>
     <row r="167" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A167" s="3">
+      <c r="A167" s="1">
         <v>82.51</v>
       </c>
       <c r="B167" s="7">
@@ -1862,7 +1861,7 @@
       </c>
     </row>
     <row r="168" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A168" s="3">
+      <c r="A168" s="1">
         <v>83.01</v>
       </c>
       <c r="B168" s="7">
@@ -1870,7 +1869,7 @@
       </c>
     </row>
     <row r="169" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A169" s="3">
+      <c r="A169" s="1">
         <v>83.51</v>
       </c>
       <c r="B169" s="7">
@@ -1878,7 +1877,7 @@
       </c>
     </row>
     <row r="170" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A170" s="3">
+      <c r="A170" s="1">
         <v>84.01</v>
       </c>
       <c r="B170" s="7">
@@ -1886,7 +1885,7 @@
       </c>
     </row>
     <row r="171" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A171" s="3">
+      <c r="A171" s="1">
         <v>84.51</v>
       </c>
       <c r="B171" s="7">
@@ -1894,7 +1893,7 @@
       </c>
     </row>
     <row r="172" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A172" s="3">
+      <c r="A172" s="1">
         <v>85.01</v>
       </c>
       <c r="B172" s="7">
@@ -1902,7 +1901,7 @@
       </c>
     </row>
     <row r="173" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A173" s="3">
+      <c r="A173" s="1">
         <v>85.51</v>
       </c>
       <c r="B173" s="7">
@@ -1910,7 +1909,7 @@
       </c>
     </row>
     <row r="174" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A174" s="3">
+      <c r="A174" s="1">
         <v>86.01</v>
       </c>
       <c r="B174" s="7">
@@ -1918,7 +1917,7 @@
       </c>
     </row>
     <row r="175" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A175" s="3">
+      <c r="A175" s="1">
         <v>86.51</v>
       </c>
       <c r="B175" s="7">
@@ -1926,7 +1925,7 @@
       </c>
     </row>
     <row r="176" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A176" s="3">
+      <c r="A176" s="1">
         <v>87.01</v>
       </c>
       <c r="B176" s="7">
@@ -1934,7 +1933,7 @@
       </c>
     </row>
     <row r="177" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A177" s="3">
+      <c r="A177" s="1">
         <v>87.51</v>
       </c>
       <c r="B177" s="7">
@@ -1942,7 +1941,7 @@
       </c>
     </row>
     <row r="178" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A178" s="3">
+      <c r="A178" s="1">
         <v>88.01</v>
       </c>
       <c r="B178" s="7">
@@ -1950,7 +1949,7 @@
       </c>
     </row>
     <row r="179" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A179" s="3">
+      <c r="A179" s="1">
         <v>88.51</v>
       </c>
       <c r="B179" s="7">
@@ -1958,7 +1957,7 @@
       </c>
     </row>
     <row r="180" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A180" s="3">
+      <c r="A180" s="1">
         <v>89.01</v>
       </c>
       <c r="B180" s="7">
@@ -1966,7 +1965,7 @@
       </c>
     </row>
     <row r="181" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A181" s="3">
+      <c r="A181" s="1">
         <v>89.51</v>
       </c>
       <c r="B181" s="7">
@@ -1974,7 +1973,7 @@
       </c>
     </row>
     <row r="182" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A182" s="3">
+      <c r="A182" s="1">
         <v>90.01</v>
       </c>
       <c r="B182" s="7">
@@ -1982,7 +1981,7 @@
       </c>
     </row>
     <row r="183" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A183" s="3">
+      <c r="A183" s="1">
         <v>90.51</v>
       </c>
       <c r="B183" s="7">
@@ -1990,7 +1989,7 @@
       </c>
     </row>
     <row r="184" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A184" s="3">
+      <c r="A184" s="1">
         <v>91.01</v>
       </c>
       <c r="B184" s="7">
@@ -1998,7 +1997,7 @@
       </c>
     </row>
     <row r="185" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A185" s="3">
+      <c r="A185" s="1">
         <v>91.51</v>
       </c>
       <c r="B185" s="7">
@@ -2006,7 +2005,7 @@
       </c>
     </row>
     <row r="186" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A186" s="3">
+      <c r="A186" s="1">
         <v>92.01</v>
       </c>
       <c r="B186" s="7">
@@ -2014,7 +2013,7 @@
       </c>
     </row>
     <row r="187" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A187" s="3">
+      <c r="A187" s="1">
         <v>92.51</v>
       </c>
       <c r="B187" s="7">
@@ -2022,7 +2021,7 @@
       </c>
     </row>
     <row r="188" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A188" s="3">
+      <c r="A188" s="1">
         <v>93.01</v>
       </c>
       <c r="B188" s="7">
@@ -2030,7 +2029,7 @@
       </c>
     </row>
     <row r="189" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A189" s="3">
+      <c r="A189" s="1">
         <v>93.51</v>
       </c>
       <c r="B189" s="7">
@@ -2038,7 +2037,7 @@
       </c>
     </row>
     <row r="190" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A190" s="3">
+      <c r="A190" s="1">
         <v>94.01</v>
       </c>
       <c r="B190" s="7">
@@ -2046,7 +2045,7 @@
       </c>
     </row>
     <row r="191" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A191" s="3">
+      <c r="A191" s="1">
         <v>94.51</v>
       </c>
       <c r="B191" s="7">
@@ -2054,7 +2053,7 @@
       </c>
     </row>
     <row r="192" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A192" s="3">
+      <c r="A192" s="1">
         <v>95.01</v>
       </c>
       <c r="B192" s="7">
@@ -2062,7 +2061,7 @@
       </c>
     </row>
     <row r="193" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A193" s="3">
+      <c r="A193" s="1">
         <v>95.51</v>
       </c>
       <c r="B193" s="7">
@@ -2070,7 +2069,7 @@
       </c>
     </row>
     <row r="194" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A194" s="3">
+      <c r="A194" s="1">
         <v>96.01</v>
       </c>
       <c r="B194" s="7">
@@ -2078,7 +2077,7 @@
       </c>
     </row>
     <row r="195" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A195" s="3">
+      <c r="A195" s="1">
         <v>96.51</v>
       </c>
       <c r="B195" s="7">
@@ -2086,7 +2085,7 @@
       </c>
     </row>
     <row r="196" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A196" s="3">
+      <c r="A196" s="1">
         <v>97.01</v>
       </c>
       <c r="B196" s="7">
@@ -2094,7 +2093,7 @@
       </c>
     </row>
     <row r="197" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A197" s="3">
+      <c r="A197" s="1">
         <v>97.51</v>
       </c>
       <c r="B197" s="7">
@@ -2102,7 +2101,7 @@
       </c>
     </row>
     <row r="198" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A198" s="3">
+      <c r="A198" s="1">
         <v>98.01</v>
       </c>
       <c r="B198" s="7">
@@ -2110,7 +2109,7 @@
       </c>
     </row>
     <row r="199" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A199" s="3">
+      <c r="A199" s="1">
         <v>98.51</v>
       </c>
       <c r="B199" s="7">
@@ -2118,7 +2117,7 @@
       </c>
     </row>
     <row r="200" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A200" s="3">
+      <c r="A200" s="1">
         <v>99.01</v>
       </c>
       <c r="B200" s="7">
@@ -2126,7 +2125,7 @@
       </c>
     </row>
     <row r="201" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A201" s="3">
+      <c r="A201" s="1">
         <v>99.51</v>
       </c>
       <c r="B201" s="8">
@@ -2134,7 +2133,7 @@
       </c>
     </row>
     <row r="202" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A202" s="3">
+      <c r="A202" s="1">
         <v>100.01</v>
       </c>
       <c r="B202" s="7">
@@ -2142,7 +2141,7 @@
       </c>
     </row>
     <row r="203" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A203" s="3">
+      <c r="A203" s="1">
         <v>100.51</v>
       </c>
       <c r="B203" s="7">
@@ -2150,7 +2149,7 @@
       </c>
     </row>
     <row r="204" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A204" s="3">
+      <c r="A204" s="1">
         <v>101.01</v>
       </c>
       <c r="B204" s="7">
@@ -2158,7 +2157,7 @@
       </c>
     </row>
     <row r="205" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A205" s="3">
+      <c r="A205" s="1">
         <v>101.51</v>
       </c>
       <c r="B205" s="8">
@@ -2166,7 +2165,7 @@
       </c>
     </row>
     <row r="206" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A206" s="3">
+      <c r="A206" s="1">
         <v>102.01</v>
       </c>
       <c r="B206" s="7">
@@ -2174,7 +2173,7 @@
       </c>
     </row>
     <row r="207" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A207" s="3">
+      <c r="A207" s="1">
         <v>102.51</v>
       </c>
       <c r="B207" s="7">
@@ -2182,7 +2181,7 @@
       </c>
     </row>
     <row r="208" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A208" s="3">
+      <c r="A208" s="1">
         <v>103.01</v>
       </c>
       <c r="B208" s="7">
@@ -2190,7 +2189,7 @@
       </c>
     </row>
     <row r="209" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A209" s="3">
+      <c r="A209" s="1">
         <v>103.51</v>
       </c>
       <c r="B209" s="8">
@@ -2198,7 +2197,7 @@
       </c>
     </row>
     <row r="210" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A210" s="3">
+      <c r="A210" s="1">
         <v>104.01</v>
       </c>
       <c r="B210" s="7">
@@ -2206,7 +2205,7 @@
       </c>
     </row>
     <row r="211" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A211" s="3">
+      <c r="A211" s="1">
         <v>104.51</v>
       </c>
       <c r="B211" s="7">
@@ -2214,7 +2213,7 @@
       </c>
     </row>
     <row r="212" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A212" s="3">
+      <c r="A212" s="1">
         <v>105.01</v>
       </c>
       <c r="B212" s="7">
@@ -2222,7 +2221,7 @@
       </c>
     </row>
     <row r="213" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A213" s="3">
+      <c r="A213" s="1">
         <v>105.51</v>
       </c>
       <c r="B213" s="8">
@@ -2230,7 +2229,7 @@
       </c>
     </row>
     <row r="214" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A214" s="3">
+      <c r="A214" s="1">
         <v>106.01</v>
       </c>
       <c r="B214" s="7">
@@ -2238,7 +2237,7 @@
       </c>
     </row>
     <row r="215" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A215" s="3">
+      <c r="A215" s="1">
         <v>106.51</v>
       </c>
       <c r="B215" s="7">
@@ -2246,7 +2245,7 @@
       </c>
     </row>
     <row r="216" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A216" s="3">
+      <c r="A216" s="1">
         <v>107.01</v>
       </c>
       <c r="B216" s="7">
@@ -2254,7 +2253,7 @@
       </c>
     </row>
     <row r="217" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A217" s="3">
+      <c r="A217" s="1">
         <v>107.51</v>
       </c>
       <c r="B217" s="8">
@@ -2262,7 +2261,7 @@
       </c>
     </row>
     <row r="218" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A218" s="3">
+      <c r="A218" s="1">
         <v>108.01</v>
       </c>
       <c r="B218" s="7">
@@ -2270,7 +2269,7 @@
       </c>
     </row>
     <row r="219" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A219" s="3">
+      <c r="A219" s="1">
         <v>108.51</v>
       </c>
       <c r="B219" s="7">
@@ -2278,7 +2277,7 @@
       </c>
     </row>
     <row r="220" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A220" s="3">
+      <c r="A220" s="1">
         <v>109.01</v>
       </c>
       <c r="B220" s="7">
@@ -2286,7 +2285,7 @@
       </c>
     </row>
     <row r="221" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A221" s="3">
+      <c r="A221" s="1">
         <v>109.51</v>
       </c>
       <c r="B221" s="8">
@@ -2294,7 +2293,7 @@
       </c>
     </row>
     <row r="222" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A222" s="3">
+      <c r="A222" s="1">
         <v>110.01</v>
       </c>
       <c r="B222" s="7">
@@ -2302,7 +2301,7 @@
       </c>
     </row>
     <row r="223" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A223" s="3">
+      <c r="A223" s="1">
         <v>110.51</v>
       </c>
       <c r="B223" s="7">
@@ -2310,7 +2309,7 @@
       </c>
     </row>
     <row r="224" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A224" s="3">
+      <c r="A224" s="1">
         <v>111.01</v>
       </c>
       <c r="B224" s="7">
@@ -2318,7 +2317,7 @@
       </c>
     </row>
     <row r="225" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A225" s="3">
+      <c r="A225" s="1">
         <v>111.51</v>
       </c>
       <c r="B225" s="8">
@@ -2326,7 +2325,7 @@
       </c>
     </row>
     <row r="226" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A226" s="3">
+      <c r="A226" s="1">
         <v>112.01</v>
       </c>
       <c r="B226" s="7">
@@ -2334,7 +2333,7 @@
       </c>
     </row>
     <row r="227" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A227" s="3">
+      <c r="A227" s="1">
         <v>112.51</v>
       </c>
       <c r="B227" s="7">
@@ -2342,7 +2341,7 @@
       </c>
     </row>
     <row r="228" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A228" s="3">
+      <c r="A228" s="1">
         <v>113.01</v>
       </c>
       <c r="B228" s="7">
@@ -2350,7 +2349,7 @@
       </c>
     </row>
     <row r="229" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A229" s="3">
+      <c r="A229" s="1">
         <v>113.51</v>
       </c>
       <c r="B229" s="8">
@@ -2358,7 +2357,7 @@
       </c>
     </row>
     <row r="230" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A230" s="3">
+      <c r="A230" s="1">
         <v>114.01</v>
       </c>
       <c r="B230" s="7">
@@ -2366,7 +2365,7 @@
       </c>
     </row>
     <row r="231" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A231" s="3">
+      <c r="A231" s="1">
         <v>114.51</v>
       </c>
       <c r="B231" s="7">
@@ -2374,7 +2373,7 @@
       </c>
     </row>
     <row r="232" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A232" s="3">
+      <c r="A232" s="1">
         <v>115.01</v>
       </c>
       <c r="B232" s="7">
@@ -2382,7 +2381,7 @@
       </c>
     </row>
     <row r="233" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A233" s="3">
+      <c r="A233" s="1">
         <v>115.51</v>
       </c>
       <c r="B233" s="8">
@@ -2390,7 +2389,7 @@
       </c>
     </row>
     <row r="234" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A234" s="3">
+      <c r="A234" s="1">
         <v>116.01</v>
       </c>
       <c r="B234" s="7">
@@ -2398,7 +2397,7 @@
       </c>
     </row>
     <row r="235" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A235" s="3">
+      <c r="A235" s="1">
         <v>116.51</v>
       </c>
       <c r="B235" s="7">
@@ -2406,7 +2405,7 @@
       </c>
     </row>
     <row r="236" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A236" s="3">
+      <c r="A236" s="1">
         <v>117.01</v>
       </c>
       <c r="B236" s="7">
@@ -2414,7 +2413,7 @@
       </c>
     </row>
     <row r="237" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A237" s="3">
+      <c r="A237" s="1">
         <v>117.51</v>
       </c>
       <c r="B237" s="8">
@@ -2422,7 +2421,7 @@
       </c>
     </row>
     <row r="238" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A238" s="3">
+      <c r="A238" s="1">
         <v>118.01</v>
       </c>
       <c r="B238" s="7">
@@ -2430,7 +2429,7 @@
       </c>
     </row>
     <row r="239" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A239" s="3">
+      <c r="A239" s="1">
         <v>118.51</v>
       </c>
       <c r="B239" s="7">
@@ -2438,7 +2437,7 @@
       </c>
     </row>
     <row r="240" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A240" s="3">
+      <c r="A240" s="1">
         <v>119.01</v>
       </c>
       <c r="B240" s="7">
@@ -2446,7 +2445,7 @@
       </c>
     </row>
     <row r="241" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A241" s="3">
+      <c r="A241" s="1">
         <v>119.51</v>
       </c>
       <c r="B241" s="8">
@@ -2454,7 +2453,7 @@
       </c>
     </row>
     <row r="242" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A242" s="3">
+      <c r="A242" s="1">
         <v>120.01</v>
       </c>
       <c r="B242" s="7">
@@ -2462,7 +2461,7 @@
       </c>
     </row>
     <row r="243" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A243" s="3">
+      <c r="A243" s="1">
         <v>120.51</v>
       </c>
       <c r="B243" s="7">
@@ -2470,7 +2469,7 @@
       </c>
     </row>
     <row r="244" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A244" s="3">
+      <c r="A244" s="1">
         <v>121.01</v>
       </c>
       <c r="B244" s="7">
@@ -2478,7 +2477,7 @@
       </c>
     </row>
     <row r="245" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A245" s="3">
+      <c r="A245" s="1">
         <v>121.51</v>
       </c>
       <c r="B245" s="8">
@@ -2486,7 +2485,7 @@
       </c>
     </row>
     <row r="246" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A246" s="3">
+      <c r="A246" s="1">
         <v>122.01</v>
       </c>
       <c r="B246" s="7">
@@ -2494,7 +2493,7 @@
       </c>
     </row>
     <row r="247" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A247" s="3">
+      <c r="A247" s="1">
         <v>122.51</v>
       </c>
       <c r="B247" s="7">
@@ -2502,7 +2501,7 @@
       </c>
     </row>
     <row r="248" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A248" s="3">
+      <c r="A248" s="1">
         <v>123.01</v>
       </c>
       <c r="B248" s="7">
@@ -2510,7 +2509,7 @@
       </c>
     </row>
     <row r="249" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A249" s="3">
+      <c r="A249" s="1">
         <v>123.51</v>
       </c>
       <c r="B249" s="8">
@@ -2518,7 +2517,7 @@
       </c>
     </row>
     <row r="250" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A250" s="3">
+      <c r="A250" s="1">
         <v>124.01</v>
       </c>
       <c r="B250" s="7">
@@ -2526,7 +2525,7 @@
       </c>
     </row>
     <row r="251" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A251" s="3">
+      <c r="A251" s="1">
         <v>124.51</v>
       </c>
       <c r="B251" s="7">
@@ -2534,7 +2533,7 @@
       </c>
     </row>
     <row r="252" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A252" s="3">
+      <c r="A252" s="1">
         <v>125.01</v>
       </c>
       <c r="B252" s="7">
@@ -2542,7 +2541,7 @@
       </c>
     </row>
     <row r="253" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A253" s="3">
+      <c r="A253" s="1">
         <v>125.51</v>
       </c>
       <c r="B253" s="8">
@@ -2550,7 +2549,7 @@
       </c>
     </row>
     <row r="254" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A254" s="3">
+      <c r="A254" s="1">
         <v>126.01</v>
       </c>
       <c r="B254" s="7">
@@ -2558,7 +2557,7 @@
       </c>
     </row>
     <row r="255" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A255" s="3">
+      <c r="A255" s="1">
         <v>126.51</v>
       </c>
       <c r="B255" s="7">
@@ -2566,7 +2565,7 @@
       </c>
     </row>
     <row r="256" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A256" s="3">
+      <c r="A256" s="1">
         <v>127.01</v>
       </c>
       <c r="B256" s="7">
@@ -2574,7 +2573,7 @@
       </c>
     </row>
     <row r="257" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A257" s="3">
+      <c r="A257" s="1">
         <v>127.51</v>
       </c>
       <c r="B257" s="8">
@@ -2582,7 +2581,7 @@
       </c>
     </row>
     <row r="258" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A258" s="3">
+      <c r="A258" s="1">
         <v>128.01</v>
       </c>
       <c r="B258" s="7">
@@ -2590,7 +2589,7 @@
       </c>
     </row>
     <row r="259" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A259" s="3">
+      <c r="A259" s="1">
         <v>128.51</v>
       </c>
       <c r="B259" s="7">
@@ -2598,7 +2597,7 @@
       </c>
     </row>
     <row r="260" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A260" s="3">
+      <c r="A260" s="1">
         <v>129.01</v>
       </c>
       <c r="B260" s="7">
@@ -2606,7 +2605,7 @@
       </c>
     </row>
     <row r="261" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A261" s="3">
+      <c r="A261" s="1">
         <v>129.51</v>
       </c>
       <c r="B261" s="8">
@@ -2614,7 +2613,7 @@
       </c>
     </row>
     <row r="262" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A262" s="3">
+      <c r="A262" s="1">
         <v>130.01</v>
       </c>
       <c r="B262" s="7">
@@ -2622,7 +2621,7 @@
       </c>
     </row>
     <row r="263" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A263" s="3">
+      <c r="A263" s="1">
         <v>130.51</v>
       </c>
       <c r="B263" s="7">
@@ -2630,7 +2629,7 @@
       </c>
     </row>
     <row r="264" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A264" s="3">
+      <c r="A264" s="1">
         <v>131.01</v>
       </c>
       <c r="B264" s="7">
@@ -2638,7 +2637,7 @@
       </c>
     </row>
     <row r="265" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A265" s="3">
+      <c r="A265" s="1">
         <v>131.51</v>
       </c>
       <c r="B265" s="8">
@@ -2646,7 +2645,7 @@
       </c>
     </row>
     <row r="266" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A266" s="3">
+      <c r="A266" s="1">
         <v>132.01</v>
       </c>
       <c r="B266" s="7">
@@ -2654,7 +2653,7 @@
       </c>
     </row>
     <row r="267" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A267" s="3">
+      <c r="A267" s="1">
         <v>132.51</v>
       </c>
       <c r="B267" s="7">
@@ -2662,7 +2661,7 @@
       </c>
     </row>
     <row r="268" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A268" s="3">
+      <c r="A268" s="1">
         <v>133.01</v>
       </c>
       <c r="B268" s="7">
@@ -2670,7 +2669,7 @@
       </c>
     </row>
     <row r="269" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A269" s="3">
+      <c r="A269" s="1">
         <v>133.51</v>
       </c>
       <c r="B269" s="8">
@@ -2678,7 +2677,7 @@
       </c>
     </row>
     <row r="270" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A270" s="3">
+      <c r="A270" s="1">
         <v>134.01</v>
       </c>
       <c r="B270" s="7">
@@ -2686,7 +2685,7 @@
       </c>
     </row>
     <row r="271" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A271" s="3">
+      <c r="A271" s="1">
         <v>134.51</v>
       </c>
       <c r="B271" s="7">
@@ -2694,7 +2693,7 @@
       </c>
     </row>
     <row r="272" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A272" s="3">
+      <c r="A272" s="1">
         <v>135.01</v>
       </c>
       <c r="B272" s="7">
@@ -2702,7 +2701,7 @@
       </c>
     </row>
     <row r="273" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A273" s="3">
+      <c r="A273" s="1">
         <v>135.51</v>
       </c>
       <c r="B273" s="8">
@@ -2710,7 +2709,7 @@
       </c>
     </row>
     <row r="274" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A274" s="3">
+      <c r="A274" s="1">
         <v>136.01</v>
       </c>
       <c r="B274" s="7">
@@ -2718,7 +2717,7 @@
       </c>
     </row>
     <row r="275" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A275" s="3">
+      <c r="A275" s="1">
         <v>136.51</v>
       </c>
       <c r="B275" s="7">
@@ -2726,7 +2725,7 @@
       </c>
     </row>
     <row r="276" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A276" s="3">
+      <c r="A276" s="1">
         <v>137.01</v>
       </c>
       <c r="B276" s="7">
@@ -2734,7 +2733,7 @@
       </c>
     </row>
     <row r="277" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A277" s="3">
+      <c r="A277" s="1">
         <v>137.51</v>
       </c>
       <c r="B277" s="8">
@@ -2742,7 +2741,7 @@
       </c>
     </row>
     <row r="278" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A278" s="3">
+      <c r="A278" s="1">
         <v>138.01</v>
       </c>
       <c r="B278" s="7">
@@ -2750,7 +2749,7 @@
       </c>
     </row>
     <row r="279" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A279" s="3">
+      <c r="A279" s="1">
         <v>138.51</v>
       </c>
       <c r="B279" s="7">
@@ -2758,7 +2757,7 @@
       </c>
     </row>
     <row r="280" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A280" s="3">
+      <c r="A280" s="1">
         <v>139.01</v>
       </c>
       <c r="B280" s="7">
@@ -2766,7 +2765,7 @@
       </c>
     </row>
     <row r="281" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A281" s="3">
+      <c r="A281" s="1">
         <v>139.51</v>
       </c>
       <c r="B281" s="8">
@@ -2774,7 +2773,7 @@
       </c>
     </row>
     <row r="282" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A282" s="3">
+      <c r="A282" s="1">
         <v>140.01</v>
       </c>
       <c r="B282" s="7">
@@ -2782,7 +2781,7 @@
       </c>
     </row>
     <row r="283" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A283" s="3">
+      <c r="A283" s="1">
         <v>140.51</v>
       </c>
       <c r="B283" s="7">
@@ -2790,7 +2789,7 @@
       </c>
     </row>
     <row r="284" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A284" s="3">
+      <c r="A284" s="1">
         <v>141.01</v>
       </c>
       <c r="B284" s="7">
@@ -2798,7 +2797,7 @@
       </c>
     </row>
     <row r="285" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A285" s="3">
+      <c r="A285" s="1">
         <v>141.51</v>
       </c>
       <c r="B285" s="8">
@@ -2806,7 +2805,7 @@
       </c>
     </row>
     <row r="286" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A286" s="3">
+      <c r="A286" s="1">
         <v>142.01</v>
       </c>
       <c r="B286" s="7">
@@ -2814,7 +2813,7 @@
       </c>
     </row>
     <row r="287" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A287" s="3">
+      <c r="A287" s="1">
         <v>142.51</v>
       </c>
       <c r="B287" s="7">
@@ -2822,7 +2821,7 @@
       </c>
     </row>
     <row r="288" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A288" s="3">
+      <c r="A288" s="1">
         <v>143.01</v>
       </c>
       <c r="B288" s="7">
@@ -2830,7 +2829,7 @@
       </c>
     </row>
     <row r="289" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A289" s="3">
+      <c r="A289" s="1">
         <v>143.51</v>
       </c>
       <c r="B289" s="8">
@@ -2838,7 +2837,7 @@
       </c>
     </row>
     <row r="290" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A290" s="3">
+      <c r="A290" s="1">
         <v>144.01</v>
       </c>
       <c r="B290" s="7">
@@ -2846,7 +2845,7 @@
       </c>
     </row>
     <row r="291" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A291" s="3">
+      <c r="A291" s="1">
         <v>144.51</v>
       </c>
       <c r="B291" s="7">
@@ -2854,7 +2853,7 @@
       </c>
     </row>
     <row r="292" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A292" s="3">
+      <c r="A292" s="1">
         <v>145.01</v>
       </c>
       <c r="B292" s="7">
@@ -2862,7 +2861,7 @@
       </c>
     </row>
     <row r="293" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A293" s="3">
+      <c r="A293" s="1">
         <v>145.51</v>
       </c>
       <c r="B293" s="8">
@@ -2870,7 +2869,7 @@
       </c>
     </row>
     <row r="294" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A294" s="3">
+      <c r="A294" s="1">
         <v>146.01</v>
       </c>
       <c r="B294" s="7">
@@ -2878,7 +2877,7 @@
       </c>
     </row>
     <row r="295" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A295" s="3">
+      <c r="A295" s="1">
         <v>146.51</v>
       </c>
       <c r="B295" s="7">
@@ -2886,7 +2885,7 @@
       </c>
     </row>
     <row r="296" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A296" s="3">
+      <c r="A296" s="1">
         <v>147.01</v>
       </c>
       <c r="B296" s="7">
@@ -2894,7 +2893,7 @@
       </c>
     </row>
     <row r="297" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A297" s="3">
+      <c r="A297" s="1">
         <v>147.51</v>
       </c>
       <c r="B297" s="8">
@@ -2902,7 +2901,7 @@
       </c>
     </row>
     <row r="298" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A298" s="3">
+      <c r="A298" s="1">
         <v>148.01</v>
       </c>
       <c r="B298" s="7">
@@ -2910,7 +2909,7 @@
       </c>
     </row>
     <row r="299" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A299" s="3">
+      <c r="A299" s="1">
         <v>148.51</v>
       </c>
       <c r="B299" s="7">
@@ -2918,7 +2917,7 @@
       </c>
     </row>
     <row r="300" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A300" s="3">
+      <c r="A300" s="1">
         <v>149.01</v>
       </c>
       <c r="B300" s="7">
@@ -2926,7 +2925,7 @@
       </c>
     </row>
     <row r="301" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A301" s="3">
+      <c r="A301" s="1">
         <v>149.51</v>
       </c>
       <c r="B301" s="8">
@@ -2934,7 +2933,7 @@
       </c>
     </row>
     <row r="302" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A302" s="3">
+      <c r="A302" s="1">
         <v>150.01</v>
       </c>
       <c r="B302" s="7">
@@ -2942,7 +2941,7 @@
       </c>
     </row>
     <row r="303" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A303" s="3">
+      <c r="A303" s="1">
         <v>150.51</v>
       </c>
       <c r="B303" s="7">
@@ -2950,7 +2949,7 @@
       </c>
     </row>
     <row r="304" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A304" s="3">
+      <c r="A304" s="1">
         <v>151.01</v>
       </c>
       <c r="B304" s="7">
@@ -2958,7 +2957,7 @@
       </c>
     </row>
     <row r="305" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A305" s="3">
+      <c r="A305" s="1">
         <v>151.51</v>
       </c>
       <c r="B305" s="8">
@@ -2966,7 +2965,7 @@
       </c>
     </row>
     <row r="306" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A306" s="3">
+      <c r="A306" s="1">
         <v>152.01</v>
       </c>
       <c r="B306" s="7">
@@ -2974,7 +2973,7 @@
       </c>
     </row>
     <row r="307" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A307" s="3">
+      <c r="A307" s="1">
         <v>152.51</v>
       </c>
       <c r="B307" s="7">
@@ -2982,7 +2981,7 @@
       </c>
     </row>
     <row r="308" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A308" s="3">
+      <c r="A308" s="1">
         <v>153.01</v>
       </c>
       <c r="B308" s="7">
@@ -2990,7 +2989,7 @@
       </c>
     </row>
     <row r="309" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A309" s="3">
+      <c r="A309" s="1">
         <v>153.51</v>
       </c>
       <c r="B309" s="8">
@@ -2998,7 +2997,7 @@
       </c>
     </row>
     <row r="310" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A310" s="3">
+      <c r="A310" s="1">
         <v>154.01</v>
       </c>
       <c r="B310" s="7">
@@ -3006,7 +3005,7 @@
       </c>
     </row>
     <row r="311" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A311" s="3">
+      <c r="A311" s="1">
         <v>154.51</v>
       </c>
       <c r="B311" s="7">
@@ -3014,7 +3013,7 @@
       </c>
     </row>
     <row r="312" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A312" s="3">
+      <c r="A312" s="1">
         <v>155.01</v>
       </c>
       <c r="B312" s="7">
@@ -3022,7 +3021,7 @@
       </c>
     </row>
     <row r="313" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A313" s="3">
+      <c r="A313" s="1">
         <v>155.51</v>
       </c>
       <c r="B313" s="8">
@@ -3030,7 +3029,7 @@
       </c>
     </row>
     <row r="314" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A314" s="3">
+      <c r="A314" s="1">
         <v>156.01</v>
       </c>
       <c r="B314" s="7">
@@ -3038,7 +3037,7 @@
       </c>
     </row>
     <row r="315" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A315" s="3">
+      <c r="A315" s="1">
         <v>156.51</v>
       </c>
       <c r="B315" s="7">
@@ -3046,7 +3045,7 @@
       </c>
     </row>
     <row r="316" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A316" s="3">
+      <c r="A316" s="1">
         <v>157.01</v>
       </c>
       <c r="B316" s="7">
@@ -3054,7 +3053,7 @@
       </c>
     </row>
     <row r="317" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A317" s="3">
+      <c r="A317" s="1">
         <v>157.51</v>
       </c>
       <c r="B317" s="8">
@@ -3062,7 +3061,7 @@
       </c>
     </row>
     <row r="318" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A318" s="3">
+      <c r="A318" s="1">
         <v>158.01</v>
       </c>
       <c r="B318" s="7">
@@ -3070,7 +3069,7 @@
       </c>
     </row>
     <row r="319" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A319" s="3">
+      <c r="A319" s="1">
         <v>158.51</v>
       </c>
       <c r="B319" s="7">
@@ -3078,7 +3077,7 @@
       </c>
     </row>
     <row r="320" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A320" s="3">
+      <c r="A320" s="1">
         <v>159.01</v>
       </c>
       <c r="B320" s="7">
@@ -3086,7 +3085,7 @@
       </c>
     </row>
     <row r="321" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A321" s="3">
+      <c r="A321" s="1">
         <v>159.51</v>
       </c>
       <c r="B321" s="8">
@@ -3094,7 +3093,7 @@
       </c>
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A322" s="3">
+      <c r="A322" s="1">
         <v>160.01</v>
       </c>
       <c r="B322" s="7">
@@ -3102,7 +3101,7 @@
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A323" s="3">
+      <c r="A323" s="1">
         <v>160.51</v>
       </c>
       <c r="B323" s="7">
@@ -3110,7 +3109,7 @@
       </c>
     </row>
     <row r="324" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A324" s="3">
+      <c r="A324" s="1">
         <v>161.01</v>
       </c>
       <c r="B324" s="7">
@@ -3118,7 +3117,7 @@
       </c>
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A325" s="3">
+      <c r="A325" s="1">
         <v>161.51</v>
       </c>
       <c r="B325" s="8">
@@ -3126,7 +3125,7 @@
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A326" s="3">
+      <c r="A326" s="1">
         <v>162.01</v>
       </c>
       <c r="B326" s="7">
@@ -3134,7 +3133,7 @@
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A327" s="3">
+      <c r="A327" s="1">
         <v>162.51</v>
       </c>
       <c r="B327" s="7">
@@ -3142,7 +3141,7 @@
       </c>
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A328" s="3">
+      <c r="A328" s="1">
         <v>163.01</v>
       </c>
       <c r="B328" s="7">
@@ -3150,7 +3149,7 @@
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A329" s="3">
+      <c r="A329" s="1">
         <v>163.51</v>
       </c>
       <c r="B329" s="8">
@@ -3158,7 +3157,7 @@
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A330" s="3">
+      <c r="A330" s="1">
         <v>164.01</v>
       </c>
       <c r="B330" s="7">
@@ -3166,7 +3165,7 @@
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A331" s="3">
+      <c r="A331" s="1">
         <v>164.51</v>
       </c>
       <c r="B331" s="7">
@@ -3174,7 +3173,7 @@
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A332" s="3">
+      <c r="A332" s="1">
         <v>165.01</v>
       </c>
       <c r="B332" s="7">
@@ -3182,7 +3181,7 @@
       </c>
     </row>
     <row r="333" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A333" s="3">
+      <c r="A333" s="1">
         <v>165.51</v>
       </c>
       <c r="B333" s="8">
@@ -3190,7 +3189,7 @@
       </c>
     </row>
     <row r="334" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A334" s="3">
+      <c r="A334" s="1">
         <v>166.01</v>
       </c>
       <c r="B334" s="7">
@@ -3198,7 +3197,7 @@
       </c>
     </row>
     <row r="335" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A335" s="3">
+      <c r="A335" s="1">
         <v>166.51</v>
       </c>
       <c r="B335" s="7">
@@ -3206,7 +3205,7 @@
       </c>
     </row>
     <row r="336" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A336" s="3">
+      <c r="A336" s="1">
         <v>167.01</v>
       </c>
       <c r="B336" s="7">
@@ -3214,7 +3213,7 @@
       </c>
     </row>
     <row r="337" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A337" s="3">
+      <c r="A337" s="1">
         <v>167.51</v>
       </c>
       <c r="B337" s="8">
@@ -3222,7 +3221,7 @@
       </c>
     </row>
     <row r="338" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A338" s="3">
+      <c r="A338" s="1">
         <v>168.01</v>
       </c>
       <c r="B338" s="7">
@@ -3230,7 +3229,7 @@
       </c>
     </row>
     <row r="339" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A339" s="3">
+      <c r="A339" s="1">
         <v>168.51</v>
       </c>
       <c r="B339" s="7">
@@ -3238,7 +3237,7 @@
       </c>
     </row>
     <row r="340" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A340" s="3">
+      <c r="A340" s="1">
         <v>169.01</v>
       </c>
       <c r="B340" s="7">
@@ -3246,7 +3245,7 @@
       </c>
     </row>
     <row r="341" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A341" s="3">
+      <c r="A341" s="1">
         <v>169.51</v>
       </c>
       <c r="B341" s="8">
@@ -3254,7 +3253,7 @@
       </c>
     </row>
     <row r="342" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A342" s="3">
+      <c r="A342" s="1">
         <v>170.01</v>
       </c>
       <c r="B342" s="7">
@@ -3262,7 +3261,7 @@
       </c>
     </row>
     <row r="343" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A343" s="3">
+      <c r="A343" s="1">
         <v>170.51</v>
       </c>
       <c r="B343" s="7">
@@ -3270,7 +3269,7 @@
       </c>
     </row>
     <row r="344" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A344" s="3">
+      <c r="A344" s="1">
         <v>171.01</v>
       </c>
       <c r="B344" s="7">
@@ -3278,7 +3277,7 @@
       </c>
     </row>
     <row r="345" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A345" s="3">
+      <c r="A345" s="1">
         <v>171.51</v>
       </c>
       <c r="B345" s="8">
@@ -3286,7 +3285,7 @@
       </c>
     </row>
     <row r="346" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A346" s="3">
+      <c r="A346" s="1">
         <v>172.01</v>
       </c>
       <c r="B346" s="7">
@@ -3294,7 +3293,7 @@
       </c>
     </row>
     <row r="347" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A347" s="3">
+      <c r="A347" s="1">
         <v>172.51</v>
       </c>
       <c r="B347" s="7">
@@ -3302,7 +3301,7 @@
       </c>
     </row>
     <row r="348" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A348" s="3">
+      <c r="A348" s="1">
         <v>173.01</v>
       </c>
       <c r="B348" s="7">
@@ -3310,7 +3309,7 @@
       </c>
     </row>
     <row r="349" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A349" s="3">
+      <c r="A349" s="1">
         <v>173.51</v>
       </c>
       <c r="B349" s="8">
@@ -3318,7 +3317,7 @@
       </c>
     </row>
     <row r="350" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A350" s="3">
+      <c r="A350" s="1">
         <v>174.01</v>
       </c>
       <c r="B350" s="7">
@@ -3326,7 +3325,7 @@
       </c>
     </row>
     <row r="351" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A351" s="3">
+      <c r="A351" s="1">
         <v>174.51</v>
       </c>
       <c r="B351" s="7">
@@ -3334,7 +3333,7 @@
       </c>
     </row>
     <row r="352" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A352" s="3">
+      <c r="A352" s="1">
         <v>175.01</v>
       </c>
       <c r="B352" s="7">
@@ -3342,7 +3341,7 @@
       </c>
     </row>
     <row r="353" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A353" s="3">
+      <c r="A353" s="1">
         <v>175.51</v>
       </c>
       <c r="B353" s="8">
@@ -3350,7 +3349,7 @@
       </c>
     </row>
     <row r="354" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A354" s="3">
+      <c r="A354" s="1">
         <v>176.01</v>
       </c>
       <c r="B354" s="7">
@@ -3358,7 +3357,7 @@
       </c>
     </row>
     <row r="355" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A355" s="3">
+      <c r="A355" s="1">
         <v>176.51</v>
       </c>
       <c r="B355" s="7">
@@ -3366,7 +3365,7 @@
       </c>
     </row>
     <row r="356" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A356" s="3">
+      <c r="A356" s="1">
         <v>177.01</v>
       </c>
       <c r="B356" s="7">
@@ -3374,7 +3373,7 @@
       </c>
     </row>
     <row r="357" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A357" s="3">
+      <c r="A357" s="1">
         <v>177.51</v>
       </c>
       <c r="B357" s="8">
@@ -3382,7 +3381,7 @@
       </c>
     </row>
     <row r="358" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A358" s="3">
+      <c r="A358" s="1">
         <v>178.01</v>
       </c>
       <c r="B358" s="7">
@@ -3390,7 +3389,7 @@
       </c>
     </row>
     <row r="359" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A359" s="3">
+      <c r="A359" s="1">
         <v>178.51</v>
       </c>
       <c r="B359" s="7">
@@ -3398,7 +3397,7 @@
       </c>
     </row>
     <row r="360" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A360" s="3">
+      <c r="A360" s="1">
         <v>179.01</v>
       </c>
       <c r="B360" s="7">
@@ -3406,7 +3405,7 @@
       </c>
     </row>
     <row r="361" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A361" s="3">
+      <c r="A361" s="1">
         <v>179.51</v>
       </c>
       <c r="B361" s="8">
@@ -3414,7 +3413,7 @@
       </c>
     </row>
     <row r="362" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A362" s="3">
+      <c r="A362" s="1">
         <v>180.01</v>
       </c>
       <c r="B362" s="7">
@@ -3422,7 +3421,7 @@
       </c>
     </row>
     <row r="363" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A363" s="3">
+      <c r="A363" s="1">
         <v>180.51</v>
       </c>
       <c r="B363" s="7">
@@ -3430,7 +3429,7 @@
       </c>
     </row>
     <row r="364" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A364" s="3">
+      <c r="A364" s="1">
         <v>181.01</v>
       </c>
       <c r="B364" s="7">
@@ -3438,7 +3437,7 @@
       </c>
     </row>
     <row r="365" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A365" s="3">
+      <c r="A365" s="1">
         <v>181.51</v>
       </c>
       <c r="B365" s="8">
@@ -3446,7 +3445,7 @@
       </c>
     </row>
     <row r="366" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A366" s="3">
+      <c r="A366" s="1">
         <v>182.01</v>
       </c>
       <c r="B366" s="7">
@@ -3454,7 +3453,7 @@
       </c>
     </row>
     <row r="367" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A367" s="3">
+      <c r="A367" s="1">
         <v>182.51</v>
       </c>
       <c r="B367" s="7">
@@ -3462,7 +3461,7 @@
       </c>
     </row>
     <row r="368" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A368" s="3">
+      <c r="A368" s="1">
         <v>183.01</v>
       </c>
       <c r="B368" s="7">
@@ -3470,7 +3469,7 @@
       </c>
     </row>
     <row r="369" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A369" s="3">
+      <c r="A369" s="1">
         <v>183.51</v>
       </c>
       <c r="B369" s="8">
@@ -3478,7 +3477,7 @@
       </c>
     </row>
     <row r="370" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A370" s="3">
+      <c r="A370" s="1">
         <v>184.01</v>
       </c>
       <c r="B370" s="7">
@@ -3486,7 +3485,7 @@
       </c>
     </row>
     <row r="371" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A371" s="3">
+      <c r="A371" s="1">
         <v>184.51</v>
       </c>
       <c r="B371" s="7">
@@ -3494,7 +3493,7 @@
       </c>
     </row>
     <row r="372" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A372" s="3">
+      <c r="A372" s="1">
         <v>185.01</v>
       </c>
       <c r="B372" s="7">
@@ -3502,7 +3501,7 @@
       </c>
     </row>
     <row r="373" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A373" s="3">
+      <c r="A373" s="1">
         <v>185.51</v>
       </c>
       <c r="B373" s="8">
@@ -3510,7 +3509,7 @@
       </c>
     </row>
     <row r="374" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A374" s="3">
+      <c r="A374" s="1">
         <v>186.01</v>
       </c>
       <c r="B374" s="7">
@@ -3518,7 +3517,7 @@
       </c>
     </row>
     <row r="375" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A375" s="3">
+      <c r="A375" s="1">
         <v>186.51</v>
       </c>
       <c r="B375" s="7">
@@ -3526,7 +3525,7 @@
       </c>
     </row>
     <row r="376" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A376" s="3">
+      <c r="A376" s="1">
         <v>187.01</v>
       </c>
       <c r="B376" s="7">
@@ -3534,7 +3533,7 @@
       </c>
     </row>
     <row r="377" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A377" s="3">
+      <c r="A377" s="1">
         <v>187.51</v>
       </c>
       <c r="B377" s="8">
@@ -3542,7 +3541,7 @@
       </c>
     </row>
     <row r="378" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A378" s="3">
+      <c r="A378" s="1">
         <v>188.01</v>
       </c>
       <c r="B378" s="7">
@@ -3550,7 +3549,7 @@
       </c>
     </row>
     <row r="379" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A379" s="3">
+      <c r="A379" s="1">
         <v>188.51</v>
       </c>
       <c r="B379" s="7">
@@ -3558,7 +3557,7 @@
       </c>
     </row>
     <row r="380" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A380" s="3">
+      <c r="A380" s="1">
         <v>189.01</v>
       </c>
       <c r="B380" s="7">
@@ -3566,7 +3565,7 @@
       </c>
     </row>
     <row r="381" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A381" s="3">
+      <c r="A381" s="1">
         <v>189.51</v>
       </c>
       <c r="B381" s="8">
@@ -3574,7 +3573,7 @@
       </c>
     </row>
     <row r="382" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A382" s="3">
+      <c r="A382" s="1">
         <v>190.01</v>
       </c>
       <c r="B382" s="7">
@@ -3582,7 +3581,7 @@
       </c>
     </row>
     <row r="383" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A383" s="3">
+      <c r="A383" s="1">
         <v>190.51</v>
       </c>
       <c r="B383" s="7">
@@ -3590,7 +3589,7 @@
       </c>
     </row>
     <row r="384" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A384" s="3">
+      <c r="A384" s="1">
         <v>191.01</v>
       </c>
       <c r="B384" s="7">
@@ -3598,7 +3597,7 @@
       </c>
     </row>
     <row r="385" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A385" s="3">
+      <c r="A385" s="1">
         <v>191.51</v>
       </c>
       <c r="B385" s="8">
@@ -3606,7 +3605,7 @@
       </c>
     </row>
     <row r="386" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A386" s="3">
+      <c r="A386" s="1">
         <v>192.01</v>
       </c>
       <c r="B386" s="7">
@@ -3614,7 +3613,7 @@
       </c>
     </row>
     <row r="387" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A387" s="3">
+      <c r="A387" s="1">
         <v>192.51</v>
       </c>
       <c r="B387" s="7">
@@ -3622,7 +3621,7 @@
       </c>
     </row>
     <row r="388" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A388" s="3">
+      <c r="A388" s="1">
         <v>193.01</v>
       </c>
       <c r="B388" s="7">
@@ -3630,7 +3629,7 @@
       </c>
     </row>
     <row r="389" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A389" s="3">
+      <c r="A389" s="1">
         <v>193.51</v>
       </c>
       <c r="B389" s="8">
@@ -3638,7 +3637,7 @@
       </c>
     </row>
     <row r="390" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A390" s="3">
+      <c r="A390" s="1">
         <v>194.01</v>
       </c>
       <c r="B390" s="7">
@@ -3646,7 +3645,7 @@
       </c>
     </row>
     <row r="391" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A391" s="3">
+      <c r="A391" s="1">
         <v>194.51</v>
       </c>
       <c r="B391" s="7">
@@ -3654,7 +3653,7 @@
       </c>
     </row>
     <row r="392" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A392" s="3">
+      <c r="A392" s="1">
         <v>195.01</v>
       </c>
       <c r="B392" s="7">
@@ -3662,7 +3661,7 @@
       </c>
     </row>
     <row r="393" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A393" s="3">
+      <c r="A393" s="1">
         <v>195.51</v>
       </c>
       <c r="B393" s="8">
@@ -3670,7 +3669,7 @@
       </c>
     </row>
     <row r="394" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A394" s="3">
+      <c r="A394" s="1">
         <v>196.01</v>
       </c>
       <c r="B394" s="7">
@@ -3678,7 +3677,7 @@
       </c>
     </row>
     <row r="395" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A395" s="3">
+      <c r="A395" s="1">
         <v>196.51</v>
       </c>
       <c r="B395" s="7">
@@ -3686,7 +3685,7 @@
       </c>
     </row>
     <row r="396" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A396" s="3">
+      <c r="A396" s="1">
         <v>197.01</v>
       </c>
       <c r="B396" s="7">
@@ -3694,7 +3693,7 @@
       </c>
     </row>
     <row r="397" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A397" s="3">
+      <c r="A397" s="1">
         <v>197.51</v>
       </c>
       <c r="B397" s="8">
@@ -3702,7 +3701,7 @@
       </c>
     </row>
     <row r="398" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A398" s="3">
+      <c r="A398" s="1">
         <v>198.01</v>
       </c>
       <c r="B398" s="7">
@@ -3710,7 +3709,7 @@
       </c>
     </row>
     <row r="399" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A399" s="3">
+      <c r="A399" s="1">
         <v>198.51</v>
       </c>
       <c r="B399" s="7">
@@ -3718,7 +3717,7 @@
       </c>
     </row>
     <row r="400" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A400" s="3">
+      <c r="A400" s="1">
         <v>199.01</v>
       </c>
       <c r="B400" s="7">
@@ -3726,7 +3725,7 @@
       </c>
     </row>
     <row r="401" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A401" s="3">
+      <c r="A401" s="1">
         <v>199.51</v>
       </c>
       <c r="B401" s="8">
@@ -3734,7 +3733,7 @@
       </c>
     </row>
     <row r="402" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A402" s="3">
+      <c r="A402" s="1">
         <v>200.01</v>
       </c>
       <c r="B402" s="7">
@@ -3742,7 +3741,7 @@
       </c>
     </row>
     <row r="403" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A403" s="3">
+      <c r="A403" s="1">
         <v>200.51</v>
       </c>
       <c r="B403" s="7">
@@ -3750,7 +3749,7 @@
       </c>
     </row>
     <row r="404" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A404" s="3">
+      <c r="A404" s="1">
         <v>201.01</v>
       </c>
       <c r="B404" s="7">
@@ -3758,7 +3757,7 @@
       </c>
     </row>
     <row r="405" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A405" s="3">
+      <c r="A405" s="1">
         <v>201.51</v>
       </c>
       <c r="B405" s="8">
@@ -3766,7 +3765,7 @@
       </c>
     </row>
     <row r="406" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A406" s="3">
+      <c r="A406" s="1">
         <v>202.01</v>
       </c>
       <c r="B406" s="7">
@@ -3774,7 +3773,7 @@
       </c>
     </row>
     <row r="407" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A407" s="3">
+      <c r="A407" s="1">
         <v>202.51</v>
       </c>
       <c r="B407" s="7">
@@ -3782,7 +3781,7 @@
       </c>
     </row>
     <row r="408" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A408" s="3">
+      <c r="A408" s="1">
         <v>203.01</v>
       </c>
       <c r="B408" s="7">
@@ -3790,7 +3789,7 @@
       </c>
     </row>
     <row r="409" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A409" s="3">
+      <c r="A409" s="1">
         <v>203.51</v>
       </c>
       <c r="B409" s="8">
@@ -3798,7 +3797,7 @@
       </c>
     </row>
     <row r="410" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A410" s="3">
+      <c r="A410" s="1">
         <v>204.01</v>
       </c>
       <c r="B410" s="7">
@@ -3806,7 +3805,7 @@
       </c>
     </row>
     <row r="411" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A411" s="3">
+      <c r="A411" s="1">
         <v>204.51</v>
       </c>
       <c r="B411" s="7">
@@ -3814,7 +3813,7 @@
       </c>
     </row>
     <row r="412" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A412" s="3">
+      <c r="A412" s="1">
         <v>205.01</v>
       </c>
       <c r="B412" s="7">
@@ -3822,7 +3821,7 @@
       </c>
     </row>
     <row r="413" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A413" s="3">
+      <c r="A413" s="1">
         <v>205.51</v>
       </c>
       <c r="B413" s="8">
@@ -3830,7 +3829,7 @@
       </c>
     </row>
     <row r="414" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A414" s="3">
+      <c r="A414" s="1">
         <v>206.01</v>
       </c>
       <c r="B414" s="7">
@@ -3838,7 +3837,7 @@
       </c>
     </row>
     <row r="415" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A415" s="3">
+      <c r="A415" s="1">
         <v>206.51</v>
       </c>
       <c r="B415" s="7">
@@ -3846,7 +3845,7 @@
       </c>
     </row>
     <row r="416" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A416" s="3">
+      <c r="A416" s="1">
         <v>207.01</v>
       </c>
       <c r="B416" s="7">
@@ -3854,7 +3853,7 @@
       </c>
     </row>
     <row r="417" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A417" s="3">
+      <c r="A417" s="1">
         <v>207.51</v>
       </c>
       <c r="B417" s="8">
@@ -3862,7 +3861,7 @@
       </c>
     </row>
     <row r="418" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A418" s="3">
+      <c r="A418" s="1">
         <v>208.01</v>
       </c>
       <c r="B418" s="7">
@@ -3870,7 +3869,7 @@
       </c>
     </row>
     <row r="419" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A419" s="3">
+      <c r="A419" s="1">
         <v>208.51</v>
       </c>
       <c r="B419" s="7">
@@ -3878,7 +3877,7 @@
       </c>
     </row>
     <row r="420" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A420" s="3">
+      <c r="A420" s="1">
         <v>209.01</v>
       </c>
       <c r="B420" s="7">
@@ -3886,7 +3885,7 @@
       </c>
     </row>
     <row r="421" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A421" s="3">
+      <c r="A421" s="1">
         <v>209.51</v>
       </c>
       <c r="B421" s="8">
@@ -3894,7 +3893,7 @@
       </c>
     </row>
     <row r="422" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A422" s="3">
+      <c r="A422" s="1">
         <v>210.01</v>
       </c>
       <c r="B422" s="7">
@@ -3902,7 +3901,7 @@
       </c>
     </row>
     <row r="423" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A423" s="3">
+      <c r="A423" s="1">
         <v>210.51</v>
       </c>
       <c r="B423" s="7">
@@ -3910,7 +3909,7 @@
       </c>
     </row>
     <row r="424" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A424" s="3">
+      <c r="A424" s="1">
         <v>211.01</v>
       </c>
       <c r="B424" s="7">
@@ -3918,7 +3917,7 @@
       </c>
     </row>
     <row r="425" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A425" s="3">
+      <c r="A425" s="1">
         <v>211.51</v>
       </c>
       <c r="B425" s="8">
@@ -3926,7 +3925,7 @@
       </c>
     </row>
     <row r="426" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A426" s="3">
+      <c r="A426" s="1">
         <v>212.01</v>
       </c>
       <c r="B426" s="7">
@@ -3934,7 +3933,7 @@
       </c>
     </row>
     <row r="427" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A427" s="3">
+      <c r="A427" s="1">
         <v>212.51</v>
       </c>
       <c r="B427" s="7">
@@ -3942,7 +3941,7 @@
       </c>
     </row>
     <row r="428" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A428" s="3">
+      <c r="A428" s="1">
         <v>213.01</v>
       </c>
       <c r="B428" s="7">
@@ -3950,7 +3949,7 @@
       </c>
     </row>
     <row r="429" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A429" s="3">
+      <c r="A429" s="1">
         <v>213.51</v>
       </c>
       <c r="B429" s="8">
@@ -3958,7 +3957,7 @@
       </c>
     </row>
     <row r="430" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A430" s="3">
+      <c r="A430" s="1">
         <v>214.01</v>
       </c>
       <c r="B430" s="7">
@@ -3966,7 +3965,7 @@
       </c>
     </row>
     <row r="431" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A431" s="3">
+      <c r="A431" s="1">
         <v>214.51</v>
       </c>
       <c r="B431" s="7">
@@ -3974,7 +3973,7 @@
       </c>
     </row>
     <row r="432" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A432" s="3">
+      <c r="A432" s="1">
         <v>215.01</v>
       </c>
       <c r="B432" s="7">
@@ -3982,7 +3981,7 @@
       </c>
     </row>
     <row r="433" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A433" s="3">
+      <c r="A433" s="1">
         <v>215.51</v>
       </c>
       <c r="B433" s="8">
@@ -3990,7 +3989,7 @@
       </c>
     </row>
     <row r="434" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A434" s="3">
+      <c r="A434" s="1">
         <v>216.01</v>
       </c>
       <c r="B434" s="7">
@@ -3998,7 +3997,7 @@
       </c>
     </row>
     <row r="435" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A435" s="3">
+      <c r="A435" s="1">
         <v>216.51</v>
       </c>
       <c r="B435" s="7">
@@ -4006,7 +4005,7 @@
       </c>
     </row>
     <row r="436" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A436" s="3">
+      <c r="A436" s="1">
         <v>217.01</v>
       </c>
       <c r="B436" s="7">
@@ -4014,7 +4013,7 @@
       </c>
     </row>
     <row r="437" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A437" s="3">
+      <c r="A437" s="1">
         <v>217.51</v>
       </c>
       <c r="B437" s="8">
@@ -4022,7 +4021,7 @@
       </c>
     </row>
     <row r="438" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A438" s="3">
+      <c r="A438" s="1">
         <v>218.01</v>
       </c>
       <c r="B438" s="7">
@@ -4030,7 +4029,7 @@
       </c>
     </row>
     <row r="439" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A439" s="3">
+      <c r="A439" s="1">
         <v>218.51</v>
       </c>
       <c r="B439" s="7">
@@ -4038,7 +4037,7 @@
       </c>
     </row>
     <row r="440" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A440" s="3">
+      <c r="A440" s="1">
         <v>219.01</v>
       </c>
       <c r="B440" s="7">
@@ -4046,7 +4045,7 @@
       </c>
     </row>
     <row r="441" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A441" s="3">
+      <c r="A441" s="1">
         <v>219.51</v>
       </c>
       <c r="B441" s="8">
@@ -4054,7 +4053,7 @@
       </c>
     </row>
     <row r="442" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A442" s="3">
+      <c r="A442" s="1">
         <v>220.01</v>
       </c>
       <c r="B442" s="7">
@@ -4062,7 +4061,7 @@
       </c>
     </row>
     <row r="443" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A443" s="3">
+      <c r="A443" s="1">
         <v>220.51</v>
       </c>
       <c r="B443" s="7">
@@ -4070,7 +4069,7 @@
       </c>
     </row>
     <row r="444" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A444" s="3">
+      <c r="A444" s="1">
         <v>221.01</v>
       </c>
       <c r="B444" s="7">
@@ -4078,7 +4077,7 @@
       </c>
     </row>
     <row r="445" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A445" s="3">
+      <c r="A445" s="1">
         <v>221.51</v>
       </c>
       <c r="B445" s="8">
@@ -4086,7 +4085,7 @@
       </c>
     </row>
     <row r="446" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A446" s="3">
+      <c r="A446" s="1">
         <v>222.01</v>
       </c>
       <c r="B446" s="7">
@@ -4094,7 +4093,7 @@
       </c>
     </row>
     <row r="447" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A447" s="3">
+      <c r="A447" s="1">
         <v>222.51</v>
       </c>
       <c r="B447" s="7">
@@ -4102,7 +4101,7 @@
       </c>
     </row>
     <row r="448" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A448" s="3">
+      <c r="A448" s="1">
         <v>223.01</v>
       </c>
       <c r="B448" s="7">
@@ -4110,7 +4109,7 @@
       </c>
     </row>
     <row r="449" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A449" s="3">
+      <c r="A449" s="1">
         <v>223.51</v>
       </c>
       <c r="B449" s="8">
@@ -4118,7 +4117,7 @@
       </c>
     </row>
     <row r="450" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A450" s="3">
+      <c r="A450" s="1">
         <v>224.01</v>
       </c>
       <c r="B450" s="7">
@@ -4126,7 +4125,7 @@
       </c>
     </row>
     <row r="451" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A451" s="3">
+      <c r="A451" s="1">
         <v>224.51</v>
       </c>
       <c r="B451" s="7">
@@ -4134,7 +4133,7 @@
       </c>
     </row>
     <row r="452" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A452" s="3">
+      <c r="A452" s="1">
         <v>225.01</v>
       </c>
       <c r="B452" s="7">
@@ -4142,7 +4141,7 @@
       </c>
     </row>
     <row r="453" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A453" s="3">
+      <c r="A453" s="1">
         <v>225.51</v>
       </c>
       <c r="B453" s="8">
@@ -4150,7 +4149,7 @@
       </c>
     </row>
     <row r="454" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A454" s="3">
+      <c r="A454" s="1">
         <v>226.01</v>
       </c>
       <c r="B454" s="7">
@@ -4158,7 +4157,7 @@
       </c>
     </row>
     <row r="455" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A455" s="3">
+      <c r="A455" s="1">
         <v>226.51</v>
       </c>
       <c r="B455" s="7">
@@ -4166,7 +4165,7 @@
       </c>
     </row>
     <row r="456" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A456" s="3">
+      <c r="A456" s="1">
         <v>227.01</v>
       </c>
       <c r="B456" s="7">
@@ -4174,7 +4173,7 @@
       </c>
     </row>
     <row r="457" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A457" s="3">
+      <c r="A457" s="1">
         <v>227.51</v>
       </c>
       <c r="B457" s="8">
@@ -4182,7 +4181,7 @@
       </c>
     </row>
     <row r="458" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A458" s="3">
+      <c r="A458" s="1">
         <v>228.01</v>
       </c>
       <c r="B458" s="7">
@@ -4190,7 +4189,7 @@
       </c>
     </row>
     <row r="459" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A459" s="3">
+      <c r="A459" s="1">
         <v>228.51</v>
       </c>
       <c r="B459" s="7">
@@ -4198,7 +4197,7 @@
       </c>
     </row>
     <row r="460" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A460" s="3">
+      <c r="A460" s="1">
         <v>229.01</v>
       </c>
       <c r="B460" s="7">
@@ -4206,7 +4205,7 @@
       </c>
     </row>
     <row r="461" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A461" s="3">
+      <c r="A461" s="1">
         <v>229.51</v>
       </c>
       <c r="B461" s="8">
@@ -4214,7 +4213,7 @@
       </c>
     </row>
     <row r="462" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A462" s="3">
+      <c r="A462" s="1">
         <v>230.01</v>
       </c>
       <c r="B462" s="7">
@@ -4222,7 +4221,7 @@
       </c>
     </row>
     <row r="463" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A463" s="3">
+      <c r="A463" s="1">
         <v>230.51</v>
       </c>
       <c r="B463" s="7">
@@ -4230,7 +4229,7 @@
       </c>
     </row>
     <row r="464" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A464" s="3">
+      <c r="A464" s="1">
         <v>231.01</v>
       </c>
       <c r="B464" s="7">
@@ -4238,7 +4237,7 @@
       </c>
     </row>
     <row r="465" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A465" s="3">
+      <c r="A465" s="1">
         <v>231.51</v>
       </c>
       <c r="B465" s="8">
@@ -4246,7 +4245,7 @@
       </c>
     </row>
     <row r="466" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A466" s="3">
+      <c r="A466" s="1">
         <v>232.01</v>
       </c>
       <c r="B466" s="7">
@@ -4254,7 +4253,7 @@
       </c>
     </row>
     <row r="467" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A467" s="3">
+      <c r="A467" s="1">
         <v>232.51</v>
       </c>
       <c r="B467" s="7">
@@ -4262,7 +4261,7 @@
       </c>
     </row>
     <row r="468" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A468" s="3">
+      <c r="A468" s="1">
         <v>233.01</v>
       </c>
       <c r="B468" s="7">
@@ -4270,7 +4269,7 @@
       </c>
     </row>
     <row r="469" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A469" s="3">
+      <c r="A469" s="1">
         <v>233.51</v>
       </c>
       <c r="B469" s="8">
@@ -4278,7 +4277,7 @@
       </c>
     </row>
     <row r="470" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A470" s="3">
+      <c r="A470" s="1">
         <v>234.01</v>
       </c>
       <c r="B470" s="7">
@@ -4286,7 +4285,7 @@
       </c>
     </row>
     <row r="471" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A471" s="3">
+      <c r="A471" s="1">
         <v>234.51</v>
       </c>
       <c r="B471" s="7">
@@ -4294,7 +4293,7 @@
       </c>
     </row>
     <row r="472" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A472" s="3">
+      <c r="A472" s="1">
         <v>235.01</v>
       </c>
       <c r="B472" s="7">
@@ -4302,7 +4301,7 @@
       </c>
     </row>
     <row r="473" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A473" s="3">
+      <c r="A473" s="1">
         <v>235.51</v>
       </c>
       <c r="B473" s="8">
@@ -4310,7 +4309,7 @@
       </c>
     </row>
     <row r="474" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A474" s="3">
+      <c r="A474" s="1">
         <v>236.01</v>
       </c>
       <c r="B474" s="7">
@@ -4318,7 +4317,7 @@
       </c>
     </row>
     <row r="475" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A475" s="3">
+      <c r="A475" s="1">
         <v>236.51</v>
       </c>
       <c r="B475" s="7">
@@ -4326,7 +4325,7 @@
       </c>
     </row>
     <row r="476" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A476" s="3">
+      <c r="A476" s="1">
         <v>237.01</v>
       </c>
       <c r="B476" s="7">
@@ -4334,7 +4333,7 @@
       </c>
     </row>
     <row r="477" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A477" s="3">
+      <c r="A477" s="1">
         <v>237.51</v>
       </c>
       <c r="B477" s="8">
@@ -4342,7 +4341,7 @@
       </c>
     </row>
     <row r="478" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A478" s="3">
+      <c r="A478" s="1">
         <v>238.01</v>
       </c>
       <c r="B478" s="7">
@@ -4350,7 +4349,7 @@
       </c>
     </row>
     <row r="479" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A479" s="3">
+      <c r="A479" s="1">
         <v>238.51</v>
       </c>
       <c r="B479" s="7">
@@ -4358,7 +4357,7 @@
       </c>
     </row>
     <row r="480" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A480" s="3">
+      <c r="A480" s="1">
         <v>239.01</v>
       </c>
       <c r="B480" s="7">
@@ -4366,7 +4365,7 @@
       </c>
     </row>
     <row r="481" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A481" s="3">
+      <c r="A481" s="1">
         <v>239.51</v>
       </c>
       <c r="B481" s="8">
@@ -4374,7 +4373,7 @@
       </c>
     </row>
     <row r="482" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A482" s="3">
+      <c r="A482" s="1">
         <v>240.01</v>
       </c>
       <c r="B482" s="7">
@@ -4382,7 +4381,7 @@
       </c>
     </row>
     <row r="483" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A483" s="3">
+      <c r="A483" s="1">
         <v>240.51</v>
       </c>
       <c r="B483" s="7">
@@ -4390,7 +4389,7 @@
       </c>
     </row>
     <row r="484" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A484" s="3">
+      <c r="A484" s="1">
         <v>241.01</v>
       </c>
       <c r="B484" s="7">
@@ -4398,7 +4397,7 @@
       </c>
     </row>
     <row r="485" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A485" s="3">
+      <c r="A485" s="1">
         <v>241.51</v>
       </c>
       <c r="B485" s="8">
@@ -4406,7 +4405,7 @@
       </c>
     </row>
     <row r="486" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A486" s="3">
+      <c r="A486" s="1">
         <v>242.01</v>
       </c>
       <c r="B486" s="7">
@@ -4414,7 +4413,7 @@
       </c>
     </row>
     <row r="487" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A487" s="3">
+      <c r="A487" s="1">
         <v>242.51</v>
       </c>
       <c r="B487" s="7">
@@ -4422,7 +4421,7 @@
       </c>
     </row>
     <row r="488" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A488" s="3">
+      <c r="A488" s="1">
         <v>243.01</v>
       </c>
       <c r="B488" s="7">
@@ -4430,7 +4429,7 @@
       </c>
     </row>
     <row r="489" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A489" s="3">
+      <c r="A489" s="1">
         <v>243.51</v>
       </c>
       <c r="B489" s="8">
@@ -4438,7 +4437,7 @@
       </c>
     </row>
     <row r="490" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A490" s="3">
+      <c r="A490" s="1">
         <v>244.01</v>
       </c>
       <c r="B490" s="7">
@@ -4446,7 +4445,7 @@
       </c>
     </row>
     <row r="491" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A491" s="3">
+      <c r="A491" s="1">
         <v>244.51</v>
       </c>
       <c r="B491" s="7">
@@ -4454,7 +4453,7 @@
       </c>
     </row>
     <row r="492" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A492" s="3">
+      <c r="A492" s="1">
         <v>245.01</v>
       </c>
       <c r="B492" s="7">
@@ -4462,7 +4461,7 @@
       </c>
     </row>
     <row r="493" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A493" s="3">
+      <c r="A493" s="1">
         <v>245.51</v>
       </c>
       <c r="B493" s="8">
@@ -4470,7 +4469,7 @@
       </c>
     </row>
     <row r="494" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A494" s="3">
+      <c r="A494" s="1">
         <v>246.01</v>
       </c>
       <c r="B494" s="7">
@@ -4478,7 +4477,7 @@
       </c>
     </row>
     <row r="495" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A495" s="3">
+      <c r="A495" s="1">
         <v>246.51</v>
       </c>
       <c r="B495" s="7">
@@ -4486,7 +4485,7 @@
       </c>
     </row>
     <row r="496" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A496" s="3">
+      <c r="A496" s="1">
         <v>247.01</v>
       </c>
       <c r="B496" s="7">
@@ -4494,7 +4493,7 @@
       </c>
     </row>
     <row r="497" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A497" s="3">
+      <c r="A497" s="1">
         <v>247.51</v>
       </c>
       <c r="B497" s="8">
@@ -4502,7 +4501,7 @@
       </c>
     </row>
     <row r="498" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A498" s="3">
+      <c r="A498" s="1">
         <v>248.01</v>
       </c>
       <c r="B498" s="7">
@@ -4510,7 +4509,7 @@
       </c>
     </row>
     <row r="499" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A499" s="3">
+      <c r="A499" s="1">
         <v>248.51</v>
       </c>
       <c r="B499" s="7">
@@ -4518,7 +4517,7 @@
       </c>
     </row>
     <row r="500" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A500" s="3">
+      <c r="A500" s="1">
         <v>249.01</v>
       </c>
       <c r="B500" s="7">
@@ -4526,7 +4525,7 @@
       </c>
     </row>
     <row r="501" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A501" s="3">
+      <c r="A501" s="1">
         <v>249.51</v>
       </c>
       <c r="B501" s="8">
@@ -4534,7 +4533,7 @@
       </c>
     </row>
     <row r="502" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A502" s="3">
+      <c r="A502" s="1">
         <v>250.01</v>
       </c>
       <c r="B502" s="7">
@@ -4542,7 +4541,7 @@
       </c>
     </row>
     <row r="503" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A503" s="3">
+      <c r="A503" s="1">
         <v>250.51</v>
       </c>
       <c r="B503" s="7">
@@ -4550,7 +4549,7 @@
       </c>
     </row>
     <row r="504" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A504" s="3">
+      <c r="A504" s="1">
         <v>251.01</v>
       </c>
       <c r="B504" s="7">
@@ -4558,7 +4557,7 @@
       </c>
     </row>
     <row r="505" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A505" s="3">
+      <c r="A505" s="1">
         <v>251.51</v>
       </c>
       <c r="B505" s="8">
@@ -4566,7 +4565,7 @@
       </c>
     </row>
     <row r="506" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A506" s="3">
+      <c r="A506" s="1">
         <v>252.01</v>
       </c>
       <c r="B506" s="7">
@@ -4574,7 +4573,7 @@
       </c>
     </row>
     <row r="507" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A507" s="3">
+      <c r="A507" s="1">
         <v>252.51</v>
       </c>
       <c r="B507" s="7">
@@ -4582,7 +4581,7 @@
       </c>
     </row>
     <row r="508" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A508" s="3">
+      <c r="A508" s="1">
         <v>253.01</v>
       </c>
       <c r="B508" s="7">
@@ -4590,7 +4589,7 @@
       </c>
     </row>
     <row r="509" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A509" s="3">
+      <c r="A509" s="1">
         <v>253.51</v>
       </c>
       <c r="B509" s="8">
@@ -4598,7 +4597,7 @@
       </c>
     </row>
     <row r="510" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A510" s="3">
+      <c r="A510" s="1">
         <v>254.01</v>
       </c>
       <c r="B510" s="7">
@@ -4606,7 +4605,7 @@
       </c>
     </row>
     <row r="511" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A511" s="3">
+      <c r="A511" s="1">
         <v>254.51</v>
       </c>
       <c r="B511" s="7">
@@ -4614,7 +4613,7 @@
       </c>
     </row>
     <row r="512" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A512" s="3">
+      <c r="A512" s="1">
         <v>255.01</v>
       </c>
       <c r="B512" s="7">
@@ -4622,7 +4621,7 @@
       </c>
     </row>
     <row r="513" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A513" s="3">
+      <c r="A513" s="1">
         <v>255.51</v>
       </c>
       <c r="B513" s="8">
@@ -4630,7 +4629,7 @@
       </c>
     </row>
     <row r="514" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A514" s="3">
+      <c r="A514" s="1">
         <v>256.01</v>
       </c>
       <c r="B514" s="7">
@@ -4638,7 +4637,7 @@
       </c>
     </row>
     <row r="515" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A515" s="3">
+      <c r="A515" s="1">
         <v>256.51</v>
       </c>
       <c r="B515" s="7">
@@ -4646,7 +4645,7 @@
       </c>
     </row>
     <row r="516" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A516" s="3">
+      <c r="A516" s="1">
         <v>257.01</v>
       </c>
       <c r="B516" s="7">
@@ -4654,7 +4653,7 @@
       </c>
     </row>
     <row r="517" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A517" s="3">
+      <c r="A517" s="1">
         <v>257.51</v>
       </c>
       <c r="B517" s="8">
@@ -4662,7 +4661,7 @@
       </c>
     </row>
     <row r="518" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A518" s="3">
+      <c r="A518" s="1">
         <v>258.01</v>
       </c>
       <c r="B518" s="7">
@@ -4670,7 +4669,7 @@
       </c>
     </row>
     <row r="519" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A519" s="3">
+      <c r="A519" s="1">
         <v>258.51</v>
       </c>
       <c r="B519" s="7">
@@ -4678,7 +4677,7 @@
       </c>
     </row>
     <row r="520" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A520" s="3">
+      <c r="A520" s="1">
         <v>259.01</v>
       </c>
       <c r="B520" s="7">
@@ -4686,7 +4685,7 @@
       </c>
     </row>
     <row r="521" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A521" s="3">
+      <c r="A521" s="1">
         <v>259.51</v>
       </c>
       <c r="B521" s="8">
@@ -4694,7 +4693,7 @@
       </c>
     </row>
     <row r="522" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A522" s="3">
+      <c r="A522" s="1">
         <v>260.01</v>
       </c>
       <c r="B522" s="7">
@@ -4702,7 +4701,7 @@
       </c>
     </row>
     <row r="523" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A523" s="3">
+      <c r="A523" s="1">
         <v>260.51</v>
       </c>
       <c r="B523" s="7">
@@ -4710,7 +4709,7 @@
       </c>
     </row>
     <row r="524" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A524" s="3">
+      <c r="A524" s="1">
         <v>261.01</v>
       </c>
       <c r="B524" s="7">
@@ -4718,7 +4717,7 @@
       </c>
     </row>
     <row r="525" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A525" s="3">
+      <c r="A525" s="1">
         <v>261.51</v>
       </c>
       <c r="B525" s="8">
@@ -4726,7 +4725,7 @@
       </c>
     </row>
     <row r="526" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A526" s="3">
+      <c r="A526" s="1">
         <v>262.01</v>
       </c>
       <c r="B526" s="7">
@@ -4734,7 +4733,7 @@
       </c>
     </row>
     <row r="527" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A527" s="3">
+      <c r="A527" s="1">
         <v>262.51</v>
       </c>
       <c r="B527" s="7">
@@ -4742,7 +4741,7 @@
       </c>
     </row>
     <row r="528" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A528" s="3">
+      <c r="A528" s="1">
         <v>263.01</v>
       </c>
       <c r="B528" s="7">
@@ -4750,7 +4749,7 @@
       </c>
     </row>
     <row r="529" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A529" s="3">
+      <c r="A529" s="1">
         <v>263.51</v>
       </c>
       <c r="B529" s="8">
@@ -4758,7 +4757,7 @@
       </c>
     </row>
     <row r="530" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A530" s="3">
+      <c r="A530" s="1">
         <v>264.01</v>
       </c>
       <c r="B530" s="7">
@@ -4766,7 +4765,7 @@
       </c>
     </row>
     <row r="531" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A531" s="3">
+      <c r="A531" s="1">
         <v>264.51</v>
       </c>
       <c r="B531" s="7">
@@ -4774,7 +4773,7 @@
       </c>
     </row>
     <row r="532" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A532" s="3">
+      <c r="A532" s="1">
         <v>265.01</v>
       </c>
       <c r="B532" s="7">
@@ -4782,7 +4781,7 @@
       </c>
     </row>
     <row r="533" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A533" s="3">
+      <c r="A533" s="1">
         <v>265.51</v>
       </c>
       <c r="B533" s="8">
@@ -4790,7 +4789,7 @@
       </c>
     </row>
     <row r="534" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A534" s="3">
+      <c r="A534" s="1">
         <v>266.01</v>
       </c>
       <c r="B534" s="7">
@@ -4798,7 +4797,7 @@
       </c>
     </row>
     <row r="535" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A535" s="3">
+      <c r="A535" s="1">
         <v>266.51</v>
       </c>
       <c r="B535" s="7">
@@ -4806,7 +4805,7 @@
       </c>
     </row>
     <row r="536" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A536" s="3">
+      <c r="A536" s="1">
         <v>267.01</v>
       </c>
       <c r="B536" s="7">
@@ -4814,7 +4813,7 @@
       </c>
     </row>
     <row r="537" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A537" s="3">
+      <c r="A537" s="1">
         <v>267.51</v>
       </c>
       <c r="B537" s="8">
@@ -4822,7 +4821,7 @@
       </c>
     </row>
     <row r="538" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A538" s="3">
+      <c r="A538" s="1">
         <v>268.01</v>
       </c>
       <c r="B538" s="7">
@@ -4830,7 +4829,7 @@
       </c>
     </row>
     <row r="539" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A539" s="3">
+      <c r="A539" s="1">
         <v>268.51</v>
       </c>
       <c r="B539" s="7">
@@ -4838,7 +4837,7 @@
       </c>
     </row>
     <row r="540" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A540" s="3">
+      <c r="A540" s="1">
         <v>269.01</v>
       </c>
       <c r="B540" s="7">
@@ -4846,7 +4845,7 @@
       </c>
     </row>
     <row r="541" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A541" s="3">
+      <c r="A541" s="1">
         <v>269.51</v>
       </c>
       <c r="B541" s="8">
@@ -4854,7 +4853,7 @@
       </c>
     </row>
     <row r="542" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A542" s="3">
+      <c r="A542" s="1">
         <v>270.01</v>
       </c>
       <c r="B542" s="7">
@@ -4862,7 +4861,7 @@
       </c>
     </row>
     <row r="543" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A543" s="3">
+      <c r="A543" s="1">
         <v>270.51</v>
       </c>
       <c r="B543" s="7">
@@ -4870,7 +4869,7 @@
       </c>
     </row>
     <row r="544" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A544" s="3">
+      <c r="A544" s="1">
         <v>271.01</v>
       </c>
       <c r="B544" s="7">
@@ -4878,7 +4877,7 @@
       </c>
     </row>
     <row r="545" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A545" s="3">
+      <c r="A545" s="1">
         <v>271.51</v>
       </c>
       <c r="B545" s="8">
@@ -4886,7 +4885,7 @@
       </c>
     </row>
     <row r="546" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A546" s="3">
+      <c r="A546" s="1">
         <v>272.01</v>
       </c>
       <c r="B546" s="7">
@@ -4894,7 +4893,7 @@
       </c>
     </row>
     <row r="547" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A547" s="3">
+      <c r="A547" s="1">
         <v>272.51</v>
       </c>
       <c r="B547" s="7">
@@ -4902,7 +4901,7 @@
       </c>
     </row>
     <row r="548" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A548" s="3">
+      <c r="A548" s="1">
         <v>273.01</v>
       </c>
       <c r="B548" s="7">
@@ -4910,7 +4909,7 @@
       </c>
     </row>
     <row r="549" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A549" s="3">
+      <c r="A549" s="1">
         <v>273.51</v>
       </c>
       <c r="B549" s="8">
@@ -4918,7 +4917,7 @@
       </c>
     </row>
     <row r="550" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A550" s="3">
+      <c r="A550" s="1">
         <v>274.01</v>
       </c>
       <c r="B550" s="7">
@@ -4926,7 +4925,7 @@
       </c>
     </row>
     <row r="551" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A551" s="3">
+      <c r="A551" s="1">
         <v>274.51</v>
       </c>
       <c r="B551" s="7">
@@ -4934,7 +4933,7 @@
       </c>
     </row>
     <row r="552" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A552" s="3">
+      <c r="A552" s="1">
         <v>275.01</v>
       </c>
       <c r="B552" s="7">
@@ -4942,7 +4941,7 @@
       </c>
     </row>
     <row r="553" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A553" s="3">
+      <c r="A553" s="1">
         <v>275.51</v>
       </c>
       <c r="B553" s="8">
@@ -4950,7 +4949,7 @@
       </c>
     </row>
     <row r="554" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A554" s="3">
+      <c r="A554" s="1">
         <v>276.01</v>
       </c>
       <c r="B554" s="7">
@@ -4958,7 +4957,7 @@
       </c>
     </row>
     <row r="555" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A555" s="3">
+      <c r="A555" s="1">
         <v>276.51</v>
       </c>
       <c r="B555" s="7">
@@ -4966,7 +4965,7 @@
       </c>
     </row>
     <row r="556" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A556" s="3">
+      <c r="A556" s="1">
         <v>277.01</v>
       </c>
       <c r="B556" s="7">
@@ -4974,7 +4973,7 @@
       </c>
     </row>
     <row r="557" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A557" s="3">
+      <c r="A557" s="1">
         <v>277.51</v>
       </c>
       <c r="B557" s="8">
@@ -4982,7 +4981,7 @@
       </c>
     </row>
     <row r="558" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A558" s="3">
+      <c r="A558" s="1">
         <v>278.01</v>
       </c>
       <c r="B558" s="7">
@@ -4990,7 +4989,7 @@
       </c>
     </row>
     <row r="559" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A559" s="3">
+      <c r="A559" s="1">
         <v>278.51</v>
       </c>
       <c r="B559" s="7">
@@ -4998,7 +4997,7 @@
       </c>
     </row>
     <row r="560" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A560" s="3">
+      <c r="A560" s="1">
         <v>279.01</v>
       </c>
       <c r="B560" s="7">
@@ -5006,7 +5005,7 @@
       </c>
     </row>
     <row r="561" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A561" s="3">
+      <c r="A561" s="1">
         <v>279.51</v>
       </c>
       <c r="B561" s="8">
@@ -5014,7 +5013,7 @@
       </c>
     </row>
     <row r="562" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A562" s="3">
+      <c r="A562" s="1">
         <v>280.01</v>
       </c>
       <c r="B562" s="7">
@@ -5022,7 +5021,7 @@
       </c>
     </row>
     <row r="563" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A563" s="3">
+      <c r="A563" s="1">
         <v>280.51</v>
       </c>
       <c r="B563" s="7">
@@ -5030,7 +5029,7 @@
       </c>
     </row>
     <row r="564" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A564" s="3">
+      <c r="A564" s="1">
         <v>281.01</v>
       </c>
       <c r="B564" s="7">
@@ -5038,7 +5037,7 @@
       </c>
     </row>
     <row r="565" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A565" s="3">
+      <c r="A565" s="1">
         <v>281.51</v>
       </c>
       <c r="B565" s="8">
@@ -5046,7 +5045,7 @@
       </c>
     </row>
     <row r="566" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A566" s="3">
+      <c r="A566" s="1">
         <v>282.01</v>
       </c>
       <c r="B566" s="7">
@@ -5054,7 +5053,7 @@
       </c>
     </row>
     <row r="567" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A567" s="3">
+      <c r="A567" s="1">
         <v>282.51</v>
       </c>
       <c r="B567" s="7">
@@ -5062,7 +5061,7 @@
       </c>
     </row>
     <row r="568" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A568" s="3">
+      <c r="A568" s="1">
         <v>283.01</v>
       </c>
       <c r="B568" s="7">
@@ -5070,7 +5069,7 @@
       </c>
     </row>
     <row r="569" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A569" s="3">
+      <c r="A569" s="1">
         <v>283.51</v>
       </c>
       <c r="B569" s="8">
@@ -5078,7 +5077,7 @@
       </c>
     </row>
     <row r="570" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A570" s="3">
+      <c r="A570" s="1">
         <v>284.01</v>
       </c>
       <c r="B570" s="7">
@@ -5086,7 +5085,7 @@
       </c>
     </row>
     <row r="571" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A571" s="3">
+      <c r="A571" s="1">
         <v>284.51</v>
       </c>
       <c r="B571" s="7">
@@ -5094,7 +5093,7 @@
       </c>
     </row>
     <row r="572" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A572" s="3">
+      <c r="A572" s="1">
         <v>285.01</v>
       </c>
       <c r="B572" s="7">
@@ -5102,7 +5101,7 @@
       </c>
     </row>
     <row r="573" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A573" s="3">
+      <c r="A573" s="1">
         <v>285.51</v>
       </c>
       <c r="B573" s="8">
@@ -5110,7 +5109,7 @@
       </c>
     </row>
     <row r="574" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A574" s="3">
+      <c r="A574" s="1">
         <v>286.01</v>
       </c>
       <c r="B574" s="7">
@@ -5118,7 +5117,7 @@
       </c>
     </row>
     <row r="575" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A575" s="3">
+      <c r="A575" s="1">
         <v>286.51</v>
       </c>
       <c r="B575" s="7">
@@ -5126,7 +5125,7 @@
       </c>
     </row>
     <row r="576" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A576" s="3">
+      <c r="A576" s="1">
         <v>287.01</v>
       </c>
       <c r="B576" s="7">
@@ -5134,7 +5133,7 @@
       </c>
     </row>
     <row r="577" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A577" s="3">
+      <c r="A577" s="1">
         <v>287.51</v>
       </c>
       <c r="B577" s="8">
@@ -5142,7 +5141,7 @@
       </c>
     </row>
     <row r="578" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A578" s="3">
+      <c r="A578" s="1">
         <v>288.01</v>
       </c>
       <c r="B578" s="7">
@@ -5150,7 +5149,7 @@
       </c>
     </row>
     <row r="579" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A579" s="3">
+      <c r="A579" s="1">
         <v>288.51</v>
       </c>
       <c r="B579" s="7">
@@ -5158,7 +5157,7 @@
       </c>
     </row>
     <row r="580" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A580" s="3">
+      <c r="A580" s="1">
         <v>289.01</v>
       </c>
       <c r="B580" s="7">
@@ -5166,7 +5165,7 @@
       </c>
     </row>
     <row r="581" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A581" s="3">
+      <c r="A581" s="1">
         <v>289.51</v>
       </c>
       <c r="B581" s="8">
@@ -5174,7 +5173,7 @@
       </c>
     </row>
     <row r="582" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A582" s="3">
+      <c r="A582" s="1">
         <v>290.01</v>
       </c>
       <c r="B582" s="7">
@@ -5182,7 +5181,7 @@
       </c>
     </row>
     <row r="583" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A583" s="3">
+      <c r="A583" s="1">
         <v>290.51</v>
       </c>
       <c r="B583" s="7">
@@ -5190,7 +5189,7 @@
       </c>
     </row>
     <row r="584" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A584" s="3">
+      <c r="A584" s="1">
         <v>291.01</v>
       </c>
       <c r="B584" s="7">
@@ -5198,7 +5197,7 @@
       </c>
     </row>
     <row r="585" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A585" s="3">
+      <c r="A585" s="1">
         <v>291.51</v>
       </c>
       <c r="B585" s="8">
@@ -5206,7 +5205,7 @@
       </c>
     </row>
     <row r="586" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A586" s="3">
+      <c r="A586" s="1">
         <v>292.01</v>
       </c>
       <c r="B586" s="7">
@@ -5214,7 +5213,7 @@
       </c>
     </row>
     <row r="587" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A587" s="3">
+      <c r="A587" s="1">
         <v>292.51</v>
       </c>
       <c r="B587" s="7">
@@ -5222,7 +5221,7 @@
       </c>
     </row>
     <row r="588" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A588" s="3">
+      <c r="A588" s="1">
         <v>293.01</v>
       </c>
       <c r="B588" s="7">
@@ -5230,7 +5229,7 @@
       </c>
     </row>
     <row r="589" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A589" s="3">
+      <c r="A589" s="1">
         <v>293.51</v>
       </c>
       <c r="B589" s="8">
@@ -5238,7 +5237,7 @@
       </c>
     </row>
     <row r="590" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A590" s="3">
+      <c r="A590" s="1">
         <v>294.01</v>
       </c>
       <c r="B590" s="7">
@@ -5246,7 +5245,7 @@
       </c>
     </row>
     <row r="591" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A591" s="3">
+      <c r="A591" s="1">
         <v>294.51</v>
       </c>
       <c r="B591" s="7">
@@ -5254,7 +5253,7 @@
       </c>
     </row>
     <row r="592" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A592" s="3">
+      <c r="A592" s="1">
         <v>295.01</v>
       </c>
       <c r="B592" s="7">
@@ -5262,7 +5261,7 @@
       </c>
     </row>
     <row r="593" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A593" s="3">
+      <c r="A593" s="1">
         <v>295.51</v>
       </c>
       <c r="B593" s="8">
@@ -5270,7 +5269,7 @@
       </c>
     </row>
     <row r="594" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A594" s="3">
+      <c r="A594" s="1">
         <v>296.01</v>
       </c>
       <c r="B594" s="7">
@@ -5278,7 +5277,7 @@
       </c>
     </row>
     <row r="595" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A595" s="3">
+      <c r="A595" s="1">
         <v>296.51</v>
       </c>
       <c r="B595" s="7">
@@ -5286,7 +5285,7 @@
       </c>
     </row>
     <row r="596" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A596" s="3">
+      <c r="A596" s="1">
         <v>297.01</v>
       </c>
       <c r="B596" s="7">
@@ -5294,7 +5293,7 @@
       </c>
     </row>
     <row r="597" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A597" s="3">
+      <c r="A597" s="1">
         <v>297.51</v>
       </c>
       <c r="B597" s="8">
@@ -5302,7 +5301,7 @@
       </c>
     </row>
     <row r="598" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A598" s="3">
+      <c r="A598" s="1">
         <v>298.01</v>
       </c>
       <c r="B598" s="7">
@@ -5310,7 +5309,7 @@
       </c>
     </row>
     <row r="599" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A599" s="3">
+      <c r="A599" s="1">
         <v>298.51</v>
       </c>
       <c r="B599" s="7">
@@ -5318,7 +5317,7 @@
       </c>
     </row>
     <row r="600" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A600" s="3">
+      <c r="A600" s="1">
         <v>299.01</v>
       </c>
       <c r="B600" s="7">
@@ -5326,7 +5325,7 @@
       </c>
     </row>
     <row r="601" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A601" s="3">
+      <c r="A601" s="1">
         <v>299.51</v>
       </c>
       <c r="B601" s="8">
@@ -5335,5 +5334,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/public/file/International Standard Rates Upload Template.xlsx
+++ b/public/file/International Standard Rates Upload Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23901"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FDE8F72-4131-496C-B10C-5DB9BDC38F2D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6CCC74F-726F-47A5-869D-5F4E893FCCB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="348" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,12 +20,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Range Down</t>
   </si>
@@ -64,6 +75,12 @@
   </si>
   <si>
     <t>Range Up</t>
+  </si>
+  <si>
+    <t>Zone 12</t>
+  </si>
+  <si>
+    <t>Zone 13</t>
   </si>
 </sst>
 </file>
@@ -488,10 +505,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M601"/>
+  <dimension ref="A1:O601"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>12</v>
       </c>
@@ -531,8 +548,14 @@
       <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0.01</v>
       </c>
@@ -540,7 +563,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>0.51</v>
       </c>
@@ -548,7 +571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1.01</v>
       </c>
@@ -556,7 +579,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1.51</v>
       </c>
@@ -564,7 +587,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>2.0099999999999998</v>
       </c>
@@ -572,7 +595,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>2.5099999999999998</v>
       </c>
@@ -580,7 +603,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>3.01</v>
       </c>
@@ -588,7 +611,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>3.51</v>
       </c>
@@ -596,7 +619,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>4.01</v>
       </c>
@@ -604,7 +627,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>4.51</v>
       </c>
@@ -612,7 +635,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>5.01</v>
       </c>
@@ -620,7 +643,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>5.51</v>
       </c>
@@ -628,7 +651,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>6.01</v>
       </c>
@@ -636,7 +659,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>6.51</v>
       </c>
@@ -644,7 +667,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>7.01</v>
       </c>

--- a/public/file/International Standard Rates Upload Template.xlsx
+++ b/public/file/International Standard Rates Upload Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6CCC74F-726F-47A5-869D-5F4E893FCCB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{039D1586-5C43-4351-AACC-3490679C0CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,9 +41,6 @@
     <t>Range Down</t>
   </si>
   <si>
-    <t>Zone 1</t>
-  </si>
-  <si>
     <t>Zone 2</t>
   </si>
   <si>
@@ -62,9 +59,6 @@
     <t>Zone 7</t>
   </si>
   <si>
-    <t>Zone 8</t>
-  </si>
-  <si>
     <t>Zone 9</t>
   </si>
   <si>
@@ -77,10 +71,16 @@
     <t>Range Up</t>
   </si>
   <si>
-    <t>Zone 12</t>
+    <t>Zone 8B</t>
   </si>
   <si>
-    <t>Zone 13</t>
+    <t>Zone 1B</t>
+  </si>
+  <si>
+    <t>Zone 1A</t>
+  </si>
+  <si>
+    <t>Zone 8A</t>
   </si>
 </sst>
 </file>
@@ -510,49 +510,49 @@
   <sheetData>
     <row r="1" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>9</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">

--- a/public/file/International Standard Rates Upload Template.xlsx
+++ b/public/file/International Standard Rates Upload Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23901"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FDE8F72-4131-496C-B10C-5DB9BDC38F2D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{039D1586-5C43-4351-AACC-3490679C0CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="348" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,17 +20,25 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Range Down</t>
-  </si>
-  <si>
-    <t>Zone 1</t>
   </si>
   <si>
     <t>Zone 2</t>
@@ -51,9 +59,6 @@
     <t>Zone 7</t>
   </si>
   <si>
-    <t>Zone 8</t>
-  </si>
-  <si>
     <t>Zone 9</t>
   </si>
   <si>
@@ -64,6 +69,18 @@
   </si>
   <si>
     <t>Range Up</t>
+  </si>
+  <si>
+    <t>Zone 8B</t>
+  </si>
+  <si>
+    <t>Zone 1B</t>
+  </si>
+  <si>
+    <t>Zone 1A</t>
+  </si>
+  <si>
+    <t>Zone 8A</t>
   </si>
 </sst>
 </file>
@@ -488,51 +505,57 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M601"/>
+  <dimension ref="A1:O601"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="K1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0.01</v>
       </c>
@@ -540,7 +563,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>0.51</v>
       </c>
@@ -548,7 +571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1.01</v>
       </c>
@@ -556,7 +579,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1.51</v>
       </c>
@@ -564,7 +587,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>2.0099999999999998</v>
       </c>
@@ -572,7 +595,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>2.5099999999999998</v>
       </c>
@@ -580,7 +603,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>3.01</v>
       </c>
@@ -588,7 +611,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>3.51</v>
       </c>
@@ -596,7 +619,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>4.01</v>
       </c>
@@ -604,7 +627,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>4.51</v>
       </c>
@@ -612,7 +635,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>5.01</v>
       </c>
@@ -620,7 +643,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>5.51</v>
       </c>
@@ -628,7 +651,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>6.01</v>
       </c>
@@ -636,7 +659,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>6.51</v>
       </c>
@@ -644,7 +667,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>7.01</v>
       </c>

--- a/public/file/International Standard Rates Upload Template.xlsx
+++ b/public/file/International Standard Rates Upload Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\laragon\www\sonic\public\file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\sonic_3\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{039D1586-5C43-4351-AACC-3490679C0CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8C1B73E-41E4-405E-BECF-3178E14E3DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,23 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Range Down</t>
   </si>
@@ -71,16 +60,10 @@
     <t>Range Up</t>
   </si>
   <si>
-    <t>Zone 8B</t>
+    <t>Zone 1</t>
   </si>
   <si>
-    <t>Zone 1B</t>
-  </si>
-  <si>
-    <t>Zone 1A</t>
-  </si>
-  <si>
-    <t>Zone 8A</t>
+    <t>Zone 8</t>
   </si>
 </sst>
 </file>
@@ -505,10 +488,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O601"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M601"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
@@ -516,46 +499,40 @@
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="K1" s="2" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O1" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>0.01</v>
       </c>
@@ -563,7 +540,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>0.51</v>
       </c>
@@ -571,7 +548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1.01</v>
       </c>
@@ -579,7 +556,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>1.51</v>
       </c>
@@ -587,7 +564,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>2.0099999999999998</v>
       </c>
@@ -595,7 +572,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>2.5099999999999998</v>
       </c>
@@ -603,7 +580,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>3.01</v>
       </c>
@@ -611,7 +588,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>3.51</v>
       </c>
@@ -619,7 +596,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>4.01</v>
       </c>
@@ -627,7 +604,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>4.51</v>
       </c>
@@ -635,7 +612,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>5.01</v>
       </c>
@@ -643,7 +620,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>5.51</v>
       </c>
@@ -651,7 +628,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>6.01</v>
       </c>
@@ -659,7 +636,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>6.51</v>
       </c>
@@ -667,7 +644,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>7.01</v>
       </c>
@@ -675,7 +652,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>7.51</v>
       </c>
@@ -683,7 +660,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>8.01</v>
       </c>
@@ -691,7 +668,7 @@
         <v>8.5</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>8.51</v>
       </c>
@@ -699,7 +676,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>9.01</v>
       </c>
@@ -707,7 +684,7 @@
         <v>9.5</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>9.51</v>
       </c>
@@ -715,7 +692,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>10.01</v>
       </c>
@@ -723,7 +700,7 @@
         <v>10.5</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>10.51</v>
       </c>
@@ -731,7 +708,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>11.01</v>
       </c>
@@ -739,7 +716,7 @@
         <v>11.5</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>11.51</v>
       </c>
@@ -747,7 +724,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>12.01</v>
       </c>
@@ -755,7 +732,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>12.51</v>
       </c>
@@ -763,7 +740,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>13.01</v>
       </c>
@@ -771,7 +748,7 @@
         <v>13.5</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>13.51</v>
       </c>
@@ -779,7 +756,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>14.01</v>
       </c>
@@ -787,7 +764,7 @@
         <v>14.5</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>14.51</v>
       </c>
@@ -795,7 +772,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>15.01</v>
       </c>
@@ -803,7 +780,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>15.51</v>
       </c>
@@ -811,7 +788,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>16.010000000000002</v>
       </c>
@@ -819,7 +796,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>16.510000000000002</v>
       </c>
@@ -827,7 +804,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>17.010000000000002</v>
       </c>
@@ -835,7 +812,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>17.510000000000002</v>
       </c>
@@ -843,7 +820,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>18.010000000000002</v>
       </c>
@@ -851,7 +828,7 @@
         <v>18.5</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>18.510000000000002</v>
       </c>
@@ -859,7 +836,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>19.010000000000002</v>
       </c>
@@ -867,7 +844,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>19.510000000000002</v>
       </c>
@@ -875,7 +852,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>20.010000000000002</v>
       </c>
@@ -883,7 +860,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>20.51</v>
       </c>
@@ -891,7 +868,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>21.01</v>
       </c>
@@ -899,7 +876,7 @@
         <v>21.5</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>21.51</v>
       </c>
@@ -907,7 +884,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>22.01</v>
       </c>
@@ -915,7 +892,7 @@
         <v>22.5</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>22.51</v>
       </c>
@@ -923,7 +900,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>23.01</v>
       </c>
@@ -931,7 +908,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>23.51</v>
       </c>
@@ -939,7 +916,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>24.01</v>
       </c>
@@ -947,7 +924,7 @@
         <v>24.5</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>24.51</v>
       </c>
@@ -955,7 +932,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>25.01</v>
       </c>
@@ -963,7 +940,7 @@
         <v>25.5</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>25.51</v>
       </c>
@@ -971,7 +948,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>26.01</v>
       </c>
@@ -979,7 +956,7 @@
         <v>26.5</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>26.51</v>
       </c>
@@ -987,7 +964,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>27.01</v>
       </c>
@@ -995,7 +972,7 @@
         <v>27.5</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>27.51</v>
       </c>
@@ -1003,7 +980,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>28.01</v>
       </c>
@@ -1011,7 +988,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>28.51</v>
       </c>
@@ -1019,7 +996,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>29.01</v>
       </c>
@@ -1027,7 +1004,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>29.51</v>
       </c>
@@ -1035,7 +1012,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>30.01</v>
       </c>
@@ -1043,7 +1020,7 @@
         <v>30.5</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>30.51</v>
       </c>
@@ -1051,7 +1028,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>31.01</v>
       </c>
@@ -1059,7 +1036,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>31.51</v>
       </c>
@@ -1067,7 +1044,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>32.01</v>
       </c>
@@ -1075,7 +1052,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>32.51</v>
       </c>
@@ -1083,7 +1060,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>33.01</v>
       </c>
@@ -1091,7 +1068,7 @@
         <v>33.5</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
         <v>33.51</v>
       </c>
@@ -1099,7 +1076,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
         <v>34.01</v>
       </c>
@@ -1107,7 +1084,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
         <v>34.51</v>
       </c>
@@ -1115,7 +1092,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
         <v>35.01</v>
       </c>
@@ -1123,7 +1100,7 @@
         <v>35.5</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>35.51</v>
       </c>
@@ -1131,7 +1108,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>36.01</v>
       </c>
@@ -1139,7 +1116,7 @@
         <v>36.5</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>36.51</v>
       </c>
@@ -1147,7 +1124,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>37.01</v>
       </c>
@@ -1155,7 +1132,7 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>37.51</v>
       </c>
@@ -1163,7 +1140,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>38.01</v>
       </c>
@@ -1171,7 +1148,7 @@
         <v>38.5</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>38.51</v>
       </c>
@@ -1179,7 +1156,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>39.01</v>
       </c>
@@ -1187,7 +1164,7 @@
         <v>39.5</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>39.51</v>
       </c>
@@ -1195,7 +1172,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>40.01</v>
       </c>
@@ -1203,7 +1180,7 @@
         <v>40.5</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>40.51</v>
       </c>
@@ -1211,7 +1188,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>41.01</v>
       </c>
@@ -1219,7 +1196,7 @@
         <v>41.5</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>41.51</v>
       </c>
@@ -1227,7 +1204,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
         <v>42.01</v>
       </c>
@@ -1235,7 +1212,7 @@
         <v>42.5</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
         <v>42.51</v>
       </c>
@@ -1243,7 +1220,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
         <v>43.01</v>
       </c>
@@ -1251,7 +1228,7 @@
         <v>43.5</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
         <v>43.51</v>
       </c>
@@ -1259,7 +1236,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
         <v>44.01</v>
       </c>
@@ -1267,7 +1244,7 @@
         <v>44.5</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
         <v>44.51</v>
       </c>
@@ -1275,7 +1252,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
         <v>45.01</v>
       </c>
@@ -1283,7 +1260,7 @@
         <v>45.5</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
         <v>45.51</v>
       </c>
@@ -1291,7 +1268,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
         <v>46.01</v>
       </c>
@@ -1299,7 +1276,7 @@
         <v>46.5</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
         <v>46.51</v>
       </c>
@@ -1307,7 +1284,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
         <v>47.01</v>
       </c>
@@ -1315,7 +1292,7 @@
         <v>47.5</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
         <v>47.51</v>
       </c>
@@ -1323,7 +1300,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
         <v>48.01</v>
       </c>
@@ -1331,7 +1308,7 @@
         <v>48.5</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
         <v>48.51</v>
       </c>
@@ -1339,7 +1316,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
         <v>49.01</v>
       </c>
@@ -1347,7 +1324,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
         <v>49.51</v>
       </c>
@@ -1355,7 +1332,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
         <v>50.01</v>
       </c>
@@ -1363,7 +1340,7 @@
         <v>50.5</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
         <v>50.51</v>
       </c>
@@ -1371,7 +1348,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
         <v>51.01</v>
       </c>
@@ -1379,7 +1356,7 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
         <v>51.51</v>
       </c>
@@ -1387,7 +1364,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
         <v>52.01</v>
       </c>
@@ -1395,7 +1372,7 @@
         <v>52.5</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
         <v>52.51</v>
       </c>
@@ -1403,7 +1380,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
         <v>53.01</v>
       </c>
@@ -1411,7 +1388,7 @@
         <v>53.5</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
         <v>53.51</v>
       </c>
@@ -1419,7 +1396,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
         <v>54.01</v>
       </c>
@@ -1427,7 +1404,7 @@
         <v>54.5</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
         <v>54.51</v>
       </c>
@@ -1435,7 +1412,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
         <v>55.01</v>
       </c>
@@ -1443,7 +1420,7 @@
         <v>55.5</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
         <v>55.51</v>
       </c>
@@ -1451,7 +1428,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
         <v>56.01</v>
       </c>
@@ -1459,7 +1436,7 @@
         <v>56.5</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
         <v>56.51</v>
       </c>
@@ -1467,7 +1444,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
         <v>57.01</v>
       </c>
@@ -1475,7 +1452,7 @@
         <v>57.5</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
         <v>57.51</v>
       </c>
@@ -1483,7 +1460,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
         <v>58.01</v>
       </c>
@@ -1491,7 +1468,7 @@
         <v>58.5</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
         <v>58.51</v>
       </c>
@@ -1499,7 +1476,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
         <v>59.01</v>
       </c>
@@ -1507,7 +1484,7 @@
         <v>59.5</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
         <v>59.51</v>
       </c>
@@ -1515,7 +1492,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
         <v>60.01</v>
       </c>
@@ -1523,7 +1500,7 @@
         <v>60.5</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
         <v>60.51</v>
       </c>
@@ -1531,7 +1508,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
         <v>61.01</v>
       </c>
@@ -1539,7 +1516,7 @@
         <v>61.5</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
         <v>61.51</v>
       </c>
@@ -1547,7 +1524,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
         <v>62.01</v>
       </c>
@@ -1555,7 +1532,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
         <v>62.51</v>
       </c>
@@ -1563,7 +1540,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
         <v>63.01</v>
       </c>
@@ -1571,7 +1548,7 @@
         <v>63.5</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
         <v>63.51</v>
       </c>
@@ -1579,7 +1556,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
         <v>64.010000000000005</v>
       </c>
@@ -1587,7 +1564,7 @@
         <v>64.5</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
         <v>64.510000000000005</v>
       </c>
@@ -1595,7 +1572,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
         <v>65.010000000000005</v>
       </c>
@@ -1603,7 +1580,7 @@
         <v>65.5</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
         <v>65.510000000000005</v>
       </c>
@@ -1611,7 +1588,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
         <v>66.010000000000005</v>
       </c>
@@ -1619,7 +1596,7 @@
         <v>66.5</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
         <v>66.510000000000005</v>
       </c>
@@ -1627,7 +1604,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
         <v>67.010000000000005</v>
       </c>
@@ -1635,7 +1612,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
         <v>67.510000000000005</v>
       </c>
@@ -1643,7 +1620,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
         <v>68.010000000000005</v>
       </c>
@@ -1651,7 +1628,7 @@
         <v>68.5</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" s="1">
         <v>68.510000000000005</v>
       </c>
@@ -1659,7 +1636,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" s="1">
         <v>69.010000000000005</v>
       </c>
@@ -1667,7 +1644,7 @@
         <v>69.5</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" s="1">
         <v>69.510000000000005</v>
       </c>
@@ -1675,7 +1652,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" s="1">
         <v>70.010000000000005</v>
       </c>
@@ -1683,7 +1660,7 @@
         <v>70.5</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" s="1">
         <v>70.510000000000005</v>
       </c>
@@ -1691,7 +1668,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" s="1">
         <v>71.010000000000005</v>
       </c>
@@ -1699,7 +1676,7 @@
         <v>71.5</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" s="1">
         <v>71.510000000000005</v>
       </c>
@@ -1707,7 +1684,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" s="1">
         <v>72.010000000000005</v>
       </c>
@@ -1715,7 +1692,7 @@
         <v>72.5</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" s="1">
         <v>72.510000000000005</v>
       </c>
@@ -1723,7 +1700,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" s="1">
         <v>73.010000000000005</v>
       </c>
@@ -1731,7 +1708,7 @@
         <v>73.5</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" s="1">
         <v>73.510000000000005</v>
       </c>
@@ -1739,7 +1716,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
         <v>74.010000000000005</v>
       </c>
@@ -1747,7 +1724,7 @@
         <v>74.5</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" s="1">
         <v>74.510000000000005</v>
       </c>
@@ -1755,7 +1732,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
         <v>75.010000000000005</v>
       </c>
@@ -1763,7 +1740,7 @@
         <v>75.5</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
         <v>75.510000000000005</v>
       </c>
@@ -1771,7 +1748,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
         <v>76.010000000000005</v>
       </c>
@@ -1779,7 +1756,7 @@
         <v>76.5</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" s="1">
         <v>76.510000000000005</v>
       </c>
@@ -1787,7 +1764,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" s="1">
         <v>77.010000000000005</v>
       </c>
@@ -1795,7 +1772,7 @@
         <v>77.5</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
         <v>77.510000000000005</v>
       </c>
@@ -1803,7 +1780,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
         <v>78.010000000000005</v>
       </c>
@@ -1811,7 +1788,7 @@
         <v>78.5</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
         <v>78.510000000000005</v>
       </c>
@@ -1819,7 +1796,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
         <v>79.010000000000005</v>
       </c>
@@ -1827,7 +1804,7 @@
         <v>79.5</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" s="1">
         <v>79.510000000000005</v>
       </c>
@@ -1835,7 +1812,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" s="1">
         <v>80.010000000000005</v>
       </c>
@@ -1843,7 +1820,7 @@
         <v>80.5</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" s="1">
         <v>80.510000000000005</v>
       </c>
@@ -1851,7 +1828,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" s="1">
         <v>81.010000000000005</v>
       </c>
@@ -1859,7 +1836,7 @@
         <v>81.5</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" s="1">
         <v>81.510000000000005</v>
       </c>
@@ -1867,7 +1844,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" s="1">
         <v>82.01</v>
       </c>
@@ -1875,7 +1852,7 @@
         <v>82.5</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" s="1">
         <v>82.51</v>
       </c>
@@ -1883,7 +1860,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
         <v>83.01</v>
       </c>
@@ -1891,7 +1868,7 @@
         <v>83.5</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
         <v>83.51</v>
       </c>
@@ -1899,7 +1876,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" s="1">
         <v>84.01</v>
       </c>
@@ -1907,7 +1884,7 @@
         <v>84.5</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" s="1">
         <v>84.51</v>
       </c>
@@ -1915,7 +1892,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" s="1">
         <v>85.01</v>
       </c>
@@ -1923,7 +1900,7 @@
         <v>85.5</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" s="1">
         <v>85.51</v>
       </c>
@@ -1931,7 +1908,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" s="1">
         <v>86.01</v>
       </c>
@@ -1939,7 +1916,7 @@
         <v>86.5</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" s="1">
         <v>86.51</v>
       </c>
@@ -1947,7 +1924,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" s="1">
         <v>87.01</v>
       </c>
@@ -1955,7 +1932,7 @@
         <v>87.5</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" s="1">
         <v>87.51</v>
       </c>
@@ -1963,7 +1940,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" s="1">
         <v>88.01</v>
       </c>
@@ -1971,7 +1948,7 @@
         <v>88.5</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" s="1">
         <v>88.51</v>
       </c>
@@ -1979,7 +1956,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" s="1">
         <v>89.01</v>
       </c>
@@ -1987,7 +1964,7 @@
         <v>89.5</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" s="1">
         <v>89.51</v>
       </c>
@@ -1995,7 +1972,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182" s="1">
         <v>90.01</v>
       </c>
@@ -2003,7 +1980,7 @@
         <v>90.5</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183" s="1">
         <v>90.51</v>
       </c>
@@ -2011,7 +1988,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A184" s="1">
         <v>91.01</v>
       </c>
@@ -2019,7 +1996,7 @@
         <v>91.5</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185" s="1">
         <v>91.51</v>
       </c>
@@ -2027,7 +2004,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A186" s="1">
         <v>92.01</v>
       </c>
@@ -2035,7 +2012,7 @@
         <v>92.5</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A187" s="1">
         <v>92.51</v>
       </c>
@@ -2043,7 +2020,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A188" s="1">
         <v>93.01</v>
       </c>
@@ -2051,7 +2028,7 @@
         <v>93.5</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A189" s="1">
         <v>93.51</v>
       </c>
@@ -2059,7 +2036,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A190" s="1">
         <v>94.01</v>
       </c>
@@ -2067,7 +2044,7 @@
         <v>94.5</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A191" s="1">
         <v>94.51</v>
       </c>
@@ -2075,7 +2052,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A192" s="1">
         <v>95.01</v>
       </c>
@@ -2083,7 +2060,7 @@
         <v>95.5</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A193" s="1">
         <v>95.51</v>
       </c>
@@ -2091,7 +2068,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A194" s="1">
         <v>96.01</v>
       </c>
@@ -2099,7 +2076,7 @@
         <v>96.5</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A195" s="1">
         <v>96.51</v>
       </c>
@@ -2107,7 +2084,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A196" s="1">
         <v>97.01</v>
       </c>
@@ -2115,7 +2092,7 @@
         <v>97.5</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A197" s="1">
         <v>97.51</v>
       </c>
@@ -2123,7 +2100,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A198" s="1">
         <v>98.01</v>
       </c>
@@ -2131,7 +2108,7 @@
         <v>98.5</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A199" s="1">
         <v>98.51</v>
       </c>
@@ -2139,7 +2116,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A200" s="1">
         <v>99.01</v>
       </c>
@@ -2147,7 +2124,7 @@
         <v>99.5</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A201" s="1">
         <v>99.51</v>
       </c>
@@ -2155,7 +2132,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A202" s="1">
         <v>100.01</v>
       </c>
@@ -2163,7 +2140,7 @@
         <v>100.5</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A203" s="1">
         <v>100.51</v>
       </c>
@@ -2171,7 +2148,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A204" s="1">
         <v>101.01</v>
       </c>
@@ -2179,7 +2156,7 @@
         <v>101.5</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" s="1">
         <v>101.51</v>
       </c>
@@ -2187,7 +2164,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" s="1">
         <v>102.01</v>
       </c>
@@ -2195,7 +2172,7 @@
         <v>102.5</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" s="1">
         <v>102.51</v>
       </c>
@@ -2203,7 +2180,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A208" s="1">
         <v>103.01</v>
       </c>
@@ -2211,7 +2188,7 @@
         <v>103.5</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209" s="1">
         <v>103.51</v>
       </c>
@@ -2219,7 +2196,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" s="1">
         <v>104.01</v>
       </c>
@@ -2227,7 +2204,7 @@
         <v>104.5</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211" s="1">
         <v>104.51</v>
       </c>
@@ -2235,7 +2212,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A212" s="1">
         <v>105.01</v>
       </c>
@@ -2243,7 +2220,7 @@
         <v>105.5</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213" s="1">
         <v>105.51</v>
       </c>
@@ -2251,7 +2228,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A214" s="1">
         <v>106.01</v>
       </c>
@@ -2259,7 +2236,7 @@
         <v>106.5</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A215" s="1">
         <v>106.51</v>
       </c>
@@ -2267,7 +2244,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216" s="1">
         <v>107.01</v>
       </c>
@@ -2275,7 +2252,7 @@
         <v>107.5</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" s="1">
         <v>107.51</v>
       </c>
@@ -2283,7 +2260,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" s="1">
         <v>108.01</v>
       </c>
@@ -2291,7 +2268,7 @@
         <v>108.5</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219" s="1">
         <v>108.51</v>
       </c>
@@ -2299,7 +2276,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" s="1">
         <v>109.01</v>
       </c>
@@ -2307,7 +2284,7 @@
         <v>109.5</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" s="1">
         <v>109.51</v>
       </c>
@@ -2315,7 +2292,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222" s="1">
         <v>110.01</v>
       </c>
@@ -2323,7 +2300,7 @@
         <v>110.5</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223" s="1">
         <v>110.51</v>
       </c>
@@ -2331,7 +2308,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" s="1">
         <v>111.01</v>
       </c>
@@ -2339,7 +2316,7 @@
         <v>111.5</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" s="1">
         <v>111.51</v>
       </c>
@@ -2347,7 +2324,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" s="1">
         <v>112.01</v>
       </c>
@@ -2355,7 +2332,7 @@
         <v>112.5</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" s="1">
         <v>112.51</v>
       </c>
@@ -2363,7 +2340,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" s="1">
         <v>113.01</v>
       </c>
@@ -2371,7 +2348,7 @@
         <v>113.5</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A229" s="1">
         <v>113.51</v>
       </c>
@@ -2379,7 +2356,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" s="1">
         <v>114.01</v>
       </c>
@@ -2387,7 +2364,7 @@
         <v>114.5</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A231" s="1">
         <v>114.51</v>
       </c>
@@ -2395,7 +2372,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" s="1">
         <v>115.01</v>
       </c>
@@ -2403,7 +2380,7 @@
         <v>115.5</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" s="1">
         <v>115.51</v>
       </c>
@@ -2411,7 +2388,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" s="1">
         <v>116.01</v>
       </c>
@@ -2419,7 +2396,7 @@
         <v>116.5</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" s="1">
         <v>116.51</v>
       </c>
@@ -2427,7 +2404,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A236" s="1">
         <v>117.01</v>
       </c>
@@ -2435,7 +2412,7 @@
         <v>117.5</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A237" s="1">
         <v>117.51</v>
       </c>
@@ -2443,7 +2420,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" s="1">
         <v>118.01</v>
       </c>
@@ -2451,7 +2428,7 @@
         <v>118.5</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239" s="1">
         <v>118.51</v>
       </c>
@@ -2459,7 +2436,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A240" s="1">
         <v>119.01</v>
       </c>
@@ -2467,7 +2444,7 @@
         <v>119.5</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A241" s="1">
         <v>119.51</v>
       </c>
@@ -2475,7 +2452,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A242" s="1">
         <v>120.01</v>
       </c>
@@ -2483,7 +2460,7 @@
         <v>120.5</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" s="1">
         <v>120.51</v>
       </c>
@@ -2491,7 +2468,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" s="1">
         <v>121.01</v>
       </c>
@@ -2499,7 +2476,7 @@
         <v>121.5</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" s="1">
         <v>121.51</v>
       </c>
@@ -2507,7 +2484,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" s="1">
         <v>122.01</v>
       </c>
@@ -2515,7 +2492,7 @@
         <v>122.5</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" s="1">
         <v>122.51</v>
       </c>
@@ -2523,7 +2500,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" s="1">
         <v>123.01</v>
       </c>
@@ -2531,7 +2508,7 @@
         <v>123.5</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" s="1">
         <v>123.51</v>
       </c>
@@ -2539,7 +2516,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" s="1">
         <v>124.01</v>
       </c>
@@ -2547,7 +2524,7 @@
         <v>124.5</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" s="1">
         <v>124.51</v>
       </c>
@@ -2555,7 +2532,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" s="1">
         <v>125.01</v>
       </c>
@@ -2563,7 +2540,7 @@
         <v>125.5</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" s="1">
         <v>125.51</v>
       </c>
@@ -2571,7 +2548,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" s="1">
         <v>126.01</v>
       </c>
@@ -2579,7 +2556,7 @@
         <v>126.5</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" s="1">
         <v>126.51</v>
       </c>
@@ -2587,7 +2564,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" s="1">
         <v>127.01</v>
       </c>
@@ -2595,7 +2572,7 @@
         <v>127.5</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" s="1">
         <v>127.51</v>
       </c>
@@ -2603,7 +2580,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" s="1">
         <v>128.01</v>
       </c>
@@ -2611,7 +2588,7 @@
         <v>128.5</v>
       </c>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" s="1">
         <v>128.51</v>
       </c>
@@ -2619,7 +2596,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" s="1">
         <v>129.01</v>
       </c>
@@ -2627,7 +2604,7 @@
         <v>129.5</v>
       </c>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" s="1">
         <v>129.51</v>
       </c>
@@ -2635,7 +2612,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" s="1">
         <v>130.01</v>
       </c>
@@ -2643,7 +2620,7 @@
         <v>130.5</v>
       </c>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" s="1">
         <v>130.51</v>
       </c>
@@ -2651,7 +2628,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" s="1">
         <v>131.01</v>
       </c>
@@ -2659,7 +2636,7 @@
         <v>131.5</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" s="1">
         <v>131.51</v>
       </c>
@@ -2667,7 +2644,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" s="1">
         <v>132.01</v>
       </c>
@@ -2675,7 +2652,7 @@
         <v>132.5</v>
       </c>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" s="1">
         <v>132.51</v>
       </c>
@@ -2683,7 +2660,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" s="1">
         <v>133.01</v>
       </c>
@@ -2691,7 +2668,7 @@
         <v>133.5</v>
       </c>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" s="1">
         <v>133.51</v>
       </c>
@@ -2699,7 +2676,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" s="1">
         <v>134.01</v>
       </c>
@@ -2707,7 +2684,7 @@
         <v>134.5</v>
       </c>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" s="1">
         <v>134.51</v>
       </c>
@@ -2715,7 +2692,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" s="1">
         <v>135.01</v>
       </c>
@@ -2723,7 +2700,7 @@
         <v>135.5</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" s="1">
         <v>135.51</v>
       </c>
@@ -2731,7 +2708,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" s="1">
         <v>136.01</v>
       </c>
@@ -2739,7 +2716,7 @@
         <v>136.5</v>
       </c>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" s="1">
         <v>136.51</v>
       </c>
@@ -2747,7 +2724,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" s="1">
         <v>137.01</v>
       </c>
@@ -2755,7 +2732,7 @@
         <v>137.5</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" s="1">
         <v>137.51</v>
       </c>
@@ -2763,7 +2740,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" s="1">
         <v>138.01</v>
       </c>
@@ -2771,7 +2748,7 @@
         <v>138.5</v>
       </c>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" s="1">
         <v>138.51</v>
       </c>
@@ -2779,7 +2756,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" s="1">
         <v>139.01</v>
       </c>
@@ -2787,7 +2764,7 @@
         <v>139.5</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" s="1">
         <v>139.51</v>
       </c>
@@ -2795,7 +2772,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" s="1">
         <v>140.01</v>
       </c>
@@ -2803,7 +2780,7 @@
         <v>140.5</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" s="1">
         <v>140.51</v>
       </c>
@@ -2811,7 +2788,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" s="1">
         <v>141.01</v>
       </c>
@@ -2819,7 +2796,7 @@
         <v>141.5</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" s="1">
         <v>141.51</v>
       </c>
@@ -2827,7 +2804,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" s="1">
         <v>142.01</v>
       </c>
@@ -2835,7 +2812,7 @@
         <v>142.5</v>
       </c>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" s="1">
         <v>142.51</v>
       </c>
@@ -2843,7 +2820,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" s="1">
         <v>143.01</v>
       </c>
@@ -2851,7 +2828,7 @@
         <v>143.5</v>
       </c>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" s="1">
         <v>143.51</v>
       </c>
@@ -2859,7 +2836,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" s="1">
         <v>144.01</v>
       </c>
@@ -2867,7 +2844,7 @@
         <v>144.5</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" s="1">
         <v>144.51</v>
       </c>
@@ -2875,7 +2852,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" s="1">
         <v>145.01</v>
       </c>
@@ -2883,7 +2860,7 @@
         <v>145.5</v>
       </c>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" s="1">
         <v>145.51</v>
       </c>
@@ -2891,7 +2868,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" s="1">
         <v>146.01</v>
       </c>
@@ -2899,7 +2876,7 @@
         <v>146.5</v>
       </c>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" s="1">
         <v>146.51</v>
       </c>
@@ -2907,7 +2884,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" s="1">
         <v>147.01</v>
       </c>
@@ -2915,7 +2892,7 @@
         <v>147.5</v>
       </c>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" s="1">
         <v>147.51</v>
       </c>
@@ -2923,7 +2900,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" s="1">
         <v>148.01</v>
       </c>
@@ -2931,7 +2908,7 @@
         <v>148.5</v>
       </c>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" s="1">
         <v>148.51</v>
       </c>
@@ -2939,7 +2916,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" s="1">
         <v>149.01</v>
       </c>
@@ -2947,7 +2924,7 @@
         <v>149.5</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" s="1">
         <v>149.51</v>
       </c>
@@ -2955,7 +2932,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" s="1">
         <v>150.01</v>
       </c>
@@ -2963,7 +2940,7 @@
         <v>150.5</v>
       </c>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" s="1">
         <v>150.51</v>
       </c>
@@ -2971,7 +2948,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" s="1">
         <v>151.01</v>
       </c>
@@ -2979,7 +2956,7 @@
         <v>151.5</v>
       </c>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" s="1">
         <v>151.51</v>
       </c>
@@ -2987,7 +2964,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" s="1">
         <v>152.01</v>
       </c>
@@ -2995,7 +2972,7 @@
         <v>152.5</v>
       </c>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" s="1">
         <v>152.51</v>
       </c>
@@ -3003,7 +2980,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" s="1">
         <v>153.01</v>
       </c>
@@ -3011,7 +2988,7 @@
         <v>153.5</v>
       </c>
     </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" s="1">
         <v>153.51</v>
       </c>
@@ -3019,7 +2996,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" s="1">
         <v>154.01</v>
       </c>
@@ -3027,7 +3004,7 @@
         <v>154.5</v>
       </c>
     </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" s="1">
         <v>154.51</v>
       </c>
@@ -3035,7 +3012,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" s="1">
         <v>155.01</v>
       </c>
@@ -3043,7 +3020,7 @@
         <v>155.5</v>
       </c>
     </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" s="1">
         <v>155.51</v>
       </c>
@@ -3051,7 +3028,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" s="1">
         <v>156.01</v>
       </c>
@@ -3059,7 +3036,7 @@
         <v>156.5</v>
       </c>
     </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" s="1">
         <v>156.51</v>
       </c>
@@ -3067,7 +3044,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" s="1">
         <v>157.01</v>
       </c>
@@ -3075,7 +3052,7 @@
         <v>157.5</v>
       </c>
     </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" s="1">
         <v>157.51</v>
       </c>
@@ -3083,7 +3060,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" s="1">
         <v>158.01</v>
       </c>
@@ -3091,7 +3068,7 @@
         <v>158.5</v>
       </c>
     </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" s="1">
         <v>158.51</v>
       </c>
@@ -3099,7 +3076,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" s="1">
         <v>159.01</v>
       </c>
@@ -3107,7 +3084,7 @@
         <v>159.5</v>
       </c>
     </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" s="1">
         <v>159.51</v>
       </c>
@@ -3115,7 +3092,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" s="1">
         <v>160.01</v>
       </c>
@@ -3123,7 +3100,7 @@
         <v>160.5</v>
       </c>
     </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" s="1">
         <v>160.51</v>
       </c>
@@ -3131,7 +3108,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" s="1">
         <v>161.01</v>
       </c>
@@ -3139,7 +3116,7 @@
         <v>161.5</v>
       </c>
     </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" s="1">
         <v>161.51</v>
       </c>
@@ -3147,7 +3124,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" s="1">
         <v>162.01</v>
       </c>
@@ -3155,7 +3132,7 @@
         <v>162.5</v>
       </c>
     </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" s="1">
         <v>162.51</v>
       </c>
@@ -3163,7 +3140,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" s="1">
         <v>163.01</v>
       </c>
@@ -3171,7 +3148,7 @@
         <v>163.5</v>
       </c>
     </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" s="1">
         <v>163.51</v>
       </c>
@@ -3179,7 +3156,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" s="1">
         <v>164.01</v>
       </c>
@@ -3187,7 +3164,7 @@
         <v>164.5</v>
       </c>
     </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331" s="1">
         <v>164.51</v>
       </c>
@@ -3195,7 +3172,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" s="1">
         <v>165.01</v>
       </c>
@@ -3203,7 +3180,7 @@
         <v>165.5</v>
       </c>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333" s="1">
         <v>165.51</v>
       </c>
@@ -3211,7 +3188,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" s="1">
         <v>166.01</v>
       </c>
@@ -3219,7 +3196,7 @@
         <v>166.5</v>
       </c>
     </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" s="1">
         <v>166.51</v>
       </c>
@@ -3227,7 +3204,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" s="1">
         <v>167.01</v>
       </c>
@@ -3235,7 +3212,7 @@
         <v>167.5</v>
       </c>
     </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337" s="1">
         <v>167.51</v>
       </c>
@@ -3243,7 +3220,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" s="1">
         <v>168.01</v>
       </c>
@@ -3251,7 +3228,7 @@
         <v>168.5</v>
       </c>
     </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" s="1">
         <v>168.51</v>
       </c>
@@ -3259,7 +3236,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" s="1">
         <v>169.01</v>
       </c>
@@ -3267,7 +3244,7 @@
         <v>169.5</v>
       </c>
     </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" s="1">
         <v>169.51</v>
       </c>
@@ -3275,7 +3252,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" s="1">
         <v>170.01</v>
       </c>
@@ -3283,7 +3260,7 @@
         <v>170.5</v>
       </c>
     </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" s="1">
         <v>170.51</v>
       </c>
@@ -3291,7 +3268,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" s="1">
         <v>171.01</v>
       </c>
@@ -3299,7 +3276,7 @@
         <v>171.5</v>
       </c>
     </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" s="1">
         <v>171.51</v>
       </c>
@@ -3307,7 +3284,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" s="1">
         <v>172.01</v>
       </c>
@@ -3315,7 +3292,7 @@
         <v>172.5</v>
       </c>
     </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" s="1">
         <v>172.51</v>
       </c>
@@ -3323,7 +3300,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" s="1">
         <v>173.01</v>
       </c>
@@ -3331,7 +3308,7 @@
         <v>173.5</v>
       </c>
     </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" s="1">
         <v>173.51</v>
       </c>
@@ -3339,7 +3316,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" s="1">
         <v>174.01</v>
       </c>
@@ -3347,7 +3324,7 @@
         <v>174.5</v>
       </c>
     </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" s="1">
         <v>174.51</v>
       </c>
@@ -3355,7 +3332,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="352" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" s="1">
         <v>175.01</v>
       </c>
@@ -3363,7 +3340,7 @@
         <v>175.5</v>
       </c>
     </row>
-    <row r="353" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" s="1">
         <v>175.51</v>
       </c>
@@ -3371,7 +3348,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="354" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" s="1">
         <v>176.01</v>
       </c>
@@ -3379,7 +3356,7 @@
         <v>176.5</v>
       </c>
     </row>
-    <row r="355" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" s="1">
         <v>176.51</v>
       </c>
@@ -3387,7 +3364,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" s="1">
         <v>177.01</v>
       </c>
@@ -3395,7 +3372,7 @@
         <v>177.5</v>
       </c>
     </row>
-    <row r="357" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" s="1">
         <v>177.51</v>
       </c>
@@ -3403,7 +3380,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="358" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" s="1">
         <v>178.01</v>
       </c>
@@ -3411,7 +3388,7 @@
         <v>178.5</v>
       </c>
     </row>
-    <row r="359" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" s="1">
         <v>178.51</v>
       </c>
@@ -3419,7 +3396,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="360" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" s="1">
         <v>179.01</v>
       </c>
@@ -3427,7 +3404,7 @@
         <v>179.5</v>
       </c>
     </row>
-    <row r="361" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" s="1">
         <v>179.51</v>
       </c>
@@ -3435,7 +3412,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="362" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" s="1">
         <v>180.01</v>
       </c>
@@ -3443,7 +3420,7 @@
         <v>180.5</v>
       </c>
     </row>
-    <row r="363" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" s="1">
         <v>180.51</v>
       </c>
@@ -3451,7 +3428,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="364" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" s="1">
         <v>181.01</v>
       </c>
@@ -3459,7 +3436,7 @@
         <v>181.5</v>
       </c>
     </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" s="1">
         <v>181.51</v>
       </c>
@@ -3467,7 +3444,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" s="1">
         <v>182.01</v>
       </c>
@@ -3475,7 +3452,7 @@
         <v>182.5</v>
       </c>
     </row>
-    <row r="367" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" s="1">
         <v>182.51</v>
       </c>
@@ -3483,7 +3460,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="368" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" s="1">
         <v>183.01</v>
       </c>
@@ -3491,7 +3468,7 @@
         <v>183.5</v>
       </c>
     </row>
-    <row r="369" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" s="1">
         <v>183.51</v>
       </c>
@@ -3499,7 +3476,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="370" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" s="1">
         <v>184.01</v>
       </c>
@@ -3507,7 +3484,7 @@
         <v>184.5</v>
       </c>
     </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" s="1">
         <v>184.51</v>
       </c>
@@ -3515,7 +3492,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" s="1">
         <v>185.01</v>
       </c>
@@ -3523,7 +3500,7 @@
         <v>185.5</v>
       </c>
     </row>
-    <row r="373" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" s="1">
         <v>185.51</v>
       </c>
@@ -3531,7 +3508,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" s="1">
         <v>186.01</v>
       </c>
@@ -3539,7 +3516,7 @@
         <v>186.5</v>
       </c>
     </row>
-    <row r="375" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" s="1">
         <v>186.51</v>
       </c>
@@ -3547,7 +3524,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" s="1">
         <v>187.01</v>
       </c>
@@ -3555,7 +3532,7 @@
         <v>187.5</v>
       </c>
     </row>
-    <row r="377" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" s="1">
         <v>187.51</v>
       </c>
@@ -3563,7 +3540,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="378" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" s="1">
         <v>188.01</v>
       </c>
@@ -3571,7 +3548,7 @@
         <v>188.5</v>
       </c>
     </row>
-    <row r="379" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" s="1">
         <v>188.51</v>
       </c>
@@ -3579,7 +3556,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="380" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380" s="1">
         <v>189.01</v>
       </c>
@@ -3587,7 +3564,7 @@
         <v>189.5</v>
       </c>
     </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" s="1">
         <v>189.51</v>
       </c>
@@ -3595,7 +3572,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="382" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382" s="1">
         <v>190.01</v>
       </c>
@@ -3603,7 +3580,7 @@
         <v>190.5</v>
       </c>
     </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" s="1">
         <v>190.51</v>
       </c>
@@ -3611,7 +3588,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" s="1">
         <v>191.01</v>
       </c>
@@ -3619,7 +3596,7 @@
         <v>191.5</v>
       </c>
     </row>
-    <row r="385" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" s="1">
         <v>191.51</v>
       </c>
@@ -3627,7 +3604,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="386" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" s="1">
         <v>192.01</v>
       </c>
@@ -3635,7 +3612,7 @@
         <v>192.5</v>
       </c>
     </row>
-    <row r="387" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" s="1">
         <v>192.51</v>
       </c>
@@ -3643,7 +3620,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="388" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" s="1">
         <v>193.01</v>
       </c>
@@ -3651,7 +3628,7 @@
         <v>193.5</v>
       </c>
     </row>
-    <row r="389" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" s="1">
         <v>193.51</v>
       </c>
@@ -3659,7 +3636,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="390" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" s="1">
         <v>194.01</v>
       </c>
@@ -3667,7 +3644,7 @@
         <v>194.5</v>
       </c>
     </row>
-    <row r="391" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" s="1">
         <v>194.51</v>
       </c>
@@ -3675,7 +3652,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="392" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" s="1">
         <v>195.01</v>
       </c>
@@ -3683,7 +3660,7 @@
         <v>195.5</v>
       </c>
     </row>
-    <row r="393" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393" s="1">
         <v>195.51</v>
       </c>
@@ -3691,7 +3668,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="394" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394" s="1">
         <v>196.01</v>
       </c>
@@ -3699,7 +3676,7 @@
         <v>196.5</v>
       </c>
     </row>
-    <row r="395" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" s="1">
         <v>196.51</v>
       </c>
@@ -3707,7 +3684,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="396" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" s="1">
         <v>197.01</v>
       </c>
@@ -3715,7 +3692,7 @@
         <v>197.5</v>
       </c>
     </row>
-    <row r="397" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397" s="1">
         <v>197.51</v>
       </c>
@@ -3723,7 +3700,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="398" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" s="1">
         <v>198.01</v>
       </c>
@@ -3731,7 +3708,7 @@
         <v>198.5</v>
       </c>
     </row>
-    <row r="399" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" s="1">
         <v>198.51</v>
       </c>
@@ -3739,7 +3716,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="400" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" s="1">
         <v>199.01</v>
       </c>
@@ -3747,7 +3724,7 @@
         <v>199.5</v>
       </c>
     </row>
-    <row r="401" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" s="1">
         <v>199.51</v>
       </c>
@@ -3755,7 +3732,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="402" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" s="1">
         <v>200.01</v>
       </c>
@@ -3763,7 +3740,7 @@
         <v>200.5</v>
       </c>
     </row>
-    <row r="403" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" s="1">
         <v>200.51</v>
       </c>
@@ -3771,7 +3748,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="404" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" s="1">
         <v>201.01</v>
       </c>
@@ -3779,7 +3756,7 @@
         <v>201.5</v>
       </c>
     </row>
-    <row r="405" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" s="1">
         <v>201.51</v>
       </c>
@@ -3787,7 +3764,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="406" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" s="1">
         <v>202.01</v>
       </c>
@@ -3795,7 +3772,7 @@
         <v>202.5</v>
       </c>
     </row>
-    <row r="407" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" s="1">
         <v>202.51</v>
       </c>
@@ -3803,7 +3780,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="408" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" s="1">
         <v>203.01</v>
       </c>
@@ -3811,7 +3788,7 @@
         <v>203.5</v>
       </c>
     </row>
-    <row r="409" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" s="1">
         <v>203.51</v>
       </c>
@@ -3819,7 +3796,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="410" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" s="1">
         <v>204.01</v>
       </c>
@@ -3827,7 +3804,7 @@
         <v>204.5</v>
       </c>
     </row>
-    <row r="411" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" s="1">
         <v>204.51</v>
       </c>
@@ -3835,7 +3812,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="412" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" s="1">
         <v>205.01</v>
       </c>
@@ -3843,7 +3820,7 @@
         <v>205.5</v>
       </c>
     </row>
-    <row r="413" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" s="1">
         <v>205.51</v>
       </c>
@@ -3851,7 +3828,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="414" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" s="1">
         <v>206.01</v>
       </c>
@@ -3859,7 +3836,7 @@
         <v>206.5</v>
       </c>
     </row>
-    <row r="415" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" s="1">
         <v>206.51</v>
       </c>
@@ -3867,7 +3844,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="416" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" s="1">
         <v>207.01</v>
       </c>
@@ -3875,7 +3852,7 @@
         <v>207.5</v>
       </c>
     </row>
-    <row r="417" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" s="1">
         <v>207.51</v>
       </c>
@@ -3883,7 +3860,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="418" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" s="1">
         <v>208.01</v>
       </c>
@@ -3891,7 +3868,7 @@
         <v>208.5</v>
       </c>
     </row>
-    <row r="419" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" s="1">
         <v>208.51</v>
       </c>
@@ -3899,7 +3876,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="420" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" s="1">
         <v>209.01</v>
       </c>
@@ -3907,7 +3884,7 @@
         <v>209.5</v>
       </c>
     </row>
-    <row r="421" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" s="1">
         <v>209.51</v>
       </c>
@@ -3915,7 +3892,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="422" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" s="1">
         <v>210.01</v>
       </c>
@@ -3923,7 +3900,7 @@
         <v>210.5</v>
       </c>
     </row>
-    <row r="423" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" s="1">
         <v>210.51</v>
       </c>
@@ -3931,7 +3908,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="424" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" s="1">
         <v>211.01</v>
       </c>
@@ -3939,7 +3916,7 @@
         <v>211.5</v>
       </c>
     </row>
-    <row r="425" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" s="1">
         <v>211.51</v>
       </c>
@@ -3947,7 +3924,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="426" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" s="1">
         <v>212.01</v>
       </c>
@@ -3955,7 +3932,7 @@
         <v>212.5</v>
       </c>
     </row>
-    <row r="427" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" s="1">
         <v>212.51</v>
       </c>
@@ -3963,7 +3940,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="428" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" s="1">
         <v>213.01</v>
       </c>
@@ -3971,7 +3948,7 @@
         <v>213.5</v>
       </c>
     </row>
-    <row r="429" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" s="1">
         <v>213.51</v>
       </c>
@@ -3979,7 +3956,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="430" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" s="1">
         <v>214.01</v>
       </c>
@@ -3987,7 +3964,7 @@
         <v>214.5</v>
       </c>
     </row>
-    <row r="431" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" s="1">
         <v>214.51</v>
       </c>
@@ -3995,7 +3972,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="432" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" s="1">
         <v>215.01</v>
       </c>
@@ -4003,7 +3980,7 @@
         <v>215.5</v>
       </c>
     </row>
-    <row r="433" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" s="1">
         <v>215.51</v>
       </c>
@@ -4011,7 +3988,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="434" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" s="1">
         <v>216.01</v>
       </c>
@@ -4019,7 +3996,7 @@
         <v>216.5</v>
       </c>
     </row>
-    <row r="435" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" s="1">
         <v>216.51</v>
       </c>
@@ -4027,7 +4004,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="436" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" s="1">
         <v>217.01</v>
       </c>
@@ -4035,7 +4012,7 @@
         <v>217.5</v>
       </c>
     </row>
-    <row r="437" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" s="1">
         <v>217.51</v>
       </c>
@@ -4043,7 +4020,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="438" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" s="1">
         <v>218.01</v>
       </c>
@@ -4051,7 +4028,7 @@
         <v>218.5</v>
       </c>
     </row>
-    <row r="439" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" s="1">
         <v>218.51</v>
       </c>
@@ -4059,7 +4036,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="440" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" s="1">
         <v>219.01</v>
       </c>
@@ -4067,7 +4044,7 @@
         <v>219.5</v>
       </c>
     </row>
-    <row r="441" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" s="1">
         <v>219.51</v>
       </c>
@@ -4075,7 +4052,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="442" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" s="1">
         <v>220.01</v>
       </c>
@@ -4083,7 +4060,7 @@
         <v>220.5</v>
       </c>
     </row>
-    <row r="443" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" s="1">
         <v>220.51</v>
       </c>
@@ -4091,7 +4068,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="444" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" s="1">
         <v>221.01</v>
       </c>
@@ -4099,7 +4076,7 @@
         <v>221.5</v>
       </c>
     </row>
-    <row r="445" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" s="1">
         <v>221.51</v>
       </c>
@@ -4107,7 +4084,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="446" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" s="1">
         <v>222.01</v>
       </c>
@@ -4115,7 +4092,7 @@
         <v>222.5</v>
       </c>
     </row>
-    <row r="447" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" s="1">
         <v>222.51</v>
       </c>
@@ -4123,7 +4100,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="448" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" s="1">
         <v>223.01</v>
       </c>
@@ -4131,7 +4108,7 @@
         <v>223.5</v>
       </c>
     </row>
-    <row r="449" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" s="1">
         <v>223.51</v>
       </c>
@@ -4139,7 +4116,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="450" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" s="1">
         <v>224.01</v>
       </c>
@@ -4147,7 +4124,7 @@
         <v>224.5</v>
       </c>
     </row>
-    <row r="451" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" s="1">
         <v>224.51</v>
       </c>
@@ -4155,7 +4132,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="452" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" s="1">
         <v>225.01</v>
       </c>
@@ -4163,7 +4140,7 @@
         <v>225.5</v>
       </c>
     </row>
-    <row r="453" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" s="1">
         <v>225.51</v>
       </c>
@@ -4171,7 +4148,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="454" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" s="1">
         <v>226.01</v>
       </c>
@@ -4179,7 +4156,7 @@
         <v>226.5</v>
       </c>
     </row>
-    <row r="455" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" s="1">
         <v>226.51</v>
       </c>
@@ -4187,7 +4164,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="456" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" s="1">
         <v>227.01</v>
       </c>
@@ -4195,7 +4172,7 @@
         <v>227.5</v>
       </c>
     </row>
-    <row r="457" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" s="1">
         <v>227.51</v>
       </c>
@@ -4203,7 +4180,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="458" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" s="1">
         <v>228.01</v>
       </c>
@@ -4211,7 +4188,7 @@
         <v>228.5</v>
       </c>
     </row>
-    <row r="459" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" s="1">
         <v>228.51</v>
       </c>
@@ -4219,7 +4196,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="460" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" s="1">
         <v>229.01</v>
       </c>
@@ -4227,7 +4204,7 @@
         <v>229.5</v>
       </c>
     </row>
-    <row r="461" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" s="1">
         <v>229.51</v>
       </c>
@@ -4235,7 +4212,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="462" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" s="1">
         <v>230.01</v>
       </c>
@@ -4243,7 +4220,7 @@
         <v>230.5</v>
       </c>
     </row>
-    <row r="463" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" s="1">
         <v>230.51</v>
       </c>
@@ -4251,7 +4228,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="464" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" s="1">
         <v>231.01</v>
       </c>
@@ -4259,7 +4236,7 @@
         <v>231.5</v>
       </c>
     </row>
-    <row r="465" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" s="1">
         <v>231.51</v>
       </c>
@@ -4267,7 +4244,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="466" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" s="1">
         <v>232.01</v>
       </c>
@@ -4275,7 +4252,7 @@
         <v>232.5</v>
       </c>
     </row>
-    <row r="467" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" s="1">
         <v>232.51</v>
       </c>
@@ -4283,7 +4260,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="468" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" s="1">
         <v>233.01</v>
       </c>
@@ -4291,7 +4268,7 @@
         <v>233.5</v>
       </c>
     </row>
-    <row r="469" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" s="1">
         <v>233.51</v>
       </c>
@@ -4299,7 +4276,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="470" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" s="1">
         <v>234.01</v>
       </c>
@@ -4307,7 +4284,7 @@
         <v>234.5</v>
       </c>
     </row>
-    <row r="471" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" s="1">
         <v>234.51</v>
       </c>
@@ -4315,7 +4292,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="472" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" s="1">
         <v>235.01</v>
       </c>
@@ -4323,7 +4300,7 @@
         <v>235.5</v>
       </c>
     </row>
-    <row r="473" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" s="1">
         <v>235.51</v>
       </c>
@@ -4331,7 +4308,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="474" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" s="1">
         <v>236.01</v>
       </c>
@@ -4339,7 +4316,7 @@
         <v>236.5</v>
       </c>
     </row>
-    <row r="475" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" s="1">
         <v>236.51</v>
       </c>
@@ -4347,7 +4324,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="476" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" s="1">
         <v>237.01</v>
       </c>
@@ -4355,7 +4332,7 @@
         <v>237.5</v>
       </c>
     </row>
-    <row r="477" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" s="1">
         <v>237.51</v>
       </c>
@@ -4363,7 +4340,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="478" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" s="1">
         <v>238.01</v>
       </c>
@@ -4371,7 +4348,7 @@
         <v>238.5</v>
       </c>
     </row>
-    <row r="479" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" s="1">
         <v>238.51</v>
       </c>
@@ -4379,7 +4356,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="480" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" s="1">
         <v>239.01</v>
       </c>
@@ -4387,7 +4364,7 @@
         <v>239.5</v>
       </c>
     </row>
-    <row r="481" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" s="1">
         <v>239.51</v>
       </c>
@@ -4395,7 +4372,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="482" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" s="1">
         <v>240.01</v>
       </c>
@@ -4403,7 +4380,7 @@
         <v>240.5</v>
       </c>
     </row>
-    <row r="483" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" s="1">
         <v>240.51</v>
       </c>
@@ -4411,7 +4388,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="484" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" s="1">
         <v>241.01</v>
       </c>
@@ -4419,7 +4396,7 @@
         <v>241.5</v>
       </c>
     </row>
-    <row r="485" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" s="1">
         <v>241.51</v>
       </c>
@@ -4427,7 +4404,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="486" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" s="1">
         <v>242.01</v>
       </c>
@@ -4435,7 +4412,7 @@
         <v>242.5</v>
       </c>
     </row>
-    <row r="487" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" s="1">
         <v>242.51</v>
       </c>
@@ -4443,7 +4420,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="488" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" s="1">
         <v>243.01</v>
       </c>
@@ -4451,7 +4428,7 @@
         <v>243.5</v>
       </c>
     </row>
-    <row r="489" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" s="1">
         <v>243.51</v>
       </c>
@@ -4459,7 +4436,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="490" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" s="1">
         <v>244.01</v>
       </c>
@@ -4467,7 +4444,7 @@
         <v>244.5</v>
       </c>
     </row>
-    <row r="491" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" s="1">
         <v>244.51</v>
       </c>
@@ -4475,7 +4452,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="492" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" s="1">
         <v>245.01</v>
       </c>
@@ -4483,7 +4460,7 @@
         <v>245.5</v>
       </c>
     </row>
-    <row r="493" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" s="1">
         <v>245.51</v>
       </c>
@@ -4491,7 +4468,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="494" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" s="1">
         <v>246.01</v>
       </c>
@@ -4499,7 +4476,7 @@
         <v>246.5</v>
       </c>
     </row>
-    <row r="495" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" s="1">
         <v>246.51</v>
       </c>
@@ -4507,7 +4484,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="496" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" s="1">
         <v>247.01</v>
       </c>
@@ -4515,7 +4492,7 @@
         <v>247.5</v>
       </c>
     </row>
-    <row r="497" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" s="1">
         <v>247.51</v>
       </c>
@@ -4523,7 +4500,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="498" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" s="1">
         <v>248.01</v>
       </c>
@@ -4531,7 +4508,7 @@
         <v>248.5</v>
       </c>
     </row>
-    <row r="499" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" s="1">
         <v>248.51</v>
       </c>
@@ -4539,7 +4516,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="500" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" s="1">
         <v>249.01</v>
       </c>
@@ -4547,7 +4524,7 @@
         <v>249.5</v>
       </c>
     </row>
-    <row r="501" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" s="1">
         <v>249.51</v>
       </c>
@@ -4555,7 +4532,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="502" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" s="1">
         <v>250.01</v>
       </c>
@@ -4563,7 +4540,7 @@
         <v>250.5</v>
       </c>
     </row>
-    <row r="503" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" s="1">
         <v>250.51</v>
       </c>
@@ -4571,7 +4548,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="504" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" s="1">
         <v>251.01</v>
       </c>
@@ -4579,7 +4556,7 @@
         <v>251.5</v>
       </c>
     </row>
-    <row r="505" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" s="1">
         <v>251.51</v>
       </c>
@@ -4587,7 +4564,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="506" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" s="1">
         <v>252.01</v>
       </c>
@@ -4595,7 +4572,7 @@
         <v>252.5</v>
       </c>
     </row>
-    <row r="507" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" s="1">
         <v>252.51</v>
       </c>
@@ -4603,7 +4580,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="508" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" s="1">
         <v>253.01</v>
       </c>
@@ -4611,7 +4588,7 @@
         <v>253.5</v>
       </c>
     </row>
-    <row r="509" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" s="1">
         <v>253.51</v>
       </c>
@@ -4619,7 +4596,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="510" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" s="1">
         <v>254.01</v>
       </c>
@@ -4627,7 +4604,7 @@
         <v>254.5</v>
       </c>
     </row>
-    <row r="511" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" s="1">
         <v>254.51</v>
       </c>
@@ -4635,7 +4612,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="512" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" s="1">
         <v>255.01</v>
       </c>
@@ -4643,7 +4620,7 @@
         <v>255.5</v>
       </c>
     </row>
-    <row r="513" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" s="1">
         <v>255.51</v>
       </c>
@@ -4651,7 +4628,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="514" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" s="1">
         <v>256.01</v>
       </c>
@@ -4659,7 +4636,7 @@
         <v>256.5</v>
       </c>
     </row>
-    <row r="515" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" s="1">
         <v>256.51</v>
       </c>
@@ -4667,7 +4644,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="516" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" s="1">
         <v>257.01</v>
       </c>
@@ -4675,7 +4652,7 @@
         <v>257.5</v>
       </c>
     </row>
-    <row r="517" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" s="1">
         <v>257.51</v>
       </c>
@@ -4683,7 +4660,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="518" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" s="1">
         <v>258.01</v>
       </c>
@@ -4691,7 +4668,7 @@
         <v>258.5</v>
       </c>
     </row>
-    <row r="519" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" s="1">
         <v>258.51</v>
       </c>
@@ -4699,7 +4676,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="520" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" s="1">
         <v>259.01</v>
       </c>
@@ -4707,7 +4684,7 @@
         <v>259.5</v>
       </c>
     </row>
-    <row r="521" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" s="1">
         <v>259.51</v>
       </c>
@@ -4715,7 +4692,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="522" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" s="1">
         <v>260.01</v>
       </c>
@@ -4723,7 +4700,7 @@
         <v>260.5</v>
       </c>
     </row>
-    <row r="523" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" s="1">
         <v>260.51</v>
       </c>
@@ -4731,7 +4708,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="524" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" s="1">
         <v>261.01</v>
       </c>
@@ -4739,7 +4716,7 @@
         <v>261.5</v>
       </c>
     </row>
-    <row r="525" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" s="1">
         <v>261.51</v>
       </c>
@@ -4747,7 +4724,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="526" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" s="1">
         <v>262.01</v>
       </c>
@@ -4755,7 +4732,7 @@
         <v>262.5</v>
       </c>
     </row>
-    <row r="527" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" s="1">
         <v>262.51</v>
       </c>
@@ -4763,7 +4740,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="528" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" s="1">
         <v>263.01</v>
       </c>
@@ -4771,7 +4748,7 @@
         <v>263.5</v>
       </c>
     </row>
-    <row r="529" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" s="1">
         <v>263.51</v>
       </c>
@@ -4779,7 +4756,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="530" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" s="1">
         <v>264.01</v>
       </c>
@@ -4787,7 +4764,7 @@
         <v>264.5</v>
       </c>
     </row>
-    <row r="531" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" s="1">
         <v>264.51</v>
       </c>
@@ -4795,7 +4772,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="532" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" s="1">
         <v>265.01</v>
       </c>
@@ -4803,7 +4780,7 @@
         <v>265.5</v>
       </c>
     </row>
-    <row r="533" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" s="1">
         <v>265.51</v>
       </c>
@@ -4811,7 +4788,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="534" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" s="1">
         <v>266.01</v>
       </c>
@@ -4819,7 +4796,7 @@
         <v>266.5</v>
       </c>
     </row>
-    <row r="535" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" s="1">
         <v>266.51</v>
       </c>
@@ -4827,7 +4804,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="536" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" s="1">
         <v>267.01</v>
       </c>
@@ -4835,7 +4812,7 @@
         <v>267.5</v>
       </c>
     </row>
-    <row r="537" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" s="1">
         <v>267.51</v>
       </c>
@@ -4843,7 +4820,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="538" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" s="1">
         <v>268.01</v>
       </c>
@@ -4851,7 +4828,7 @@
         <v>268.5</v>
       </c>
     </row>
-    <row r="539" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" s="1">
         <v>268.51</v>
       </c>
@@ -4859,7 +4836,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="540" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" s="1">
         <v>269.01</v>
       </c>
@@ -4867,7 +4844,7 @@
         <v>269.5</v>
       </c>
     </row>
-    <row r="541" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" s="1">
         <v>269.51</v>
       </c>
@@ -4875,7 +4852,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="542" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" s="1">
         <v>270.01</v>
       </c>
@@ -4883,7 +4860,7 @@
         <v>270.5</v>
       </c>
     </row>
-    <row r="543" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" s="1">
         <v>270.51</v>
       </c>
@@ -4891,7 +4868,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="544" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" s="1">
         <v>271.01</v>
       </c>
@@ -4899,7 +4876,7 @@
         <v>271.5</v>
       </c>
     </row>
-    <row r="545" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" s="1">
         <v>271.51</v>
       </c>
@@ -4907,7 +4884,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="546" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" s="1">
         <v>272.01</v>
       </c>
@@ -4915,7 +4892,7 @@
         <v>272.5</v>
       </c>
     </row>
-    <row r="547" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" s="1">
         <v>272.51</v>
       </c>
@@ -4923,7 +4900,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="548" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" s="1">
         <v>273.01</v>
       </c>
@@ -4931,7 +4908,7 @@
         <v>273.5</v>
       </c>
     </row>
-    <row r="549" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" s="1">
         <v>273.51</v>
       </c>
@@ -4939,7 +4916,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="550" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" s="1">
         <v>274.01</v>
       </c>
@@ -4947,7 +4924,7 @@
         <v>274.5</v>
       </c>
     </row>
-    <row r="551" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" s="1">
         <v>274.51</v>
       </c>
@@ -4955,7 +4932,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="552" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" s="1">
         <v>275.01</v>
       </c>
@@ -4963,7 +4940,7 @@
         <v>275.5</v>
       </c>
     </row>
-    <row r="553" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" s="1">
         <v>275.51</v>
       </c>
@@ -4971,7 +4948,7 @@
         <v>276</v>
       </c>
     </row>
-    <row r="554" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" s="1">
         <v>276.01</v>
       </c>
@@ -4979,7 +4956,7 @@
         <v>276.5</v>
       </c>
     </row>
-    <row r="555" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" s="1">
         <v>276.51</v>
       </c>
@@ -4987,7 +4964,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="556" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" s="1">
         <v>277.01</v>
       </c>
@@ -4995,7 +4972,7 @@
         <v>277.5</v>
       </c>
     </row>
-    <row r="557" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" s="1">
         <v>277.51</v>
       </c>
@@ -5003,7 +4980,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="558" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" s="1">
         <v>278.01</v>
       </c>
@@ -5011,7 +4988,7 @@
         <v>278.5</v>
       </c>
     </row>
-    <row r="559" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" s="1">
         <v>278.51</v>
       </c>
@@ -5019,7 +4996,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="560" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" s="1">
         <v>279.01</v>
       </c>
@@ -5027,7 +5004,7 @@
         <v>279.5</v>
       </c>
     </row>
-    <row r="561" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" s="1">
         <v>279.51</v>
       </c>
@@ -5035,7 +5012,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="562" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" s="1">
         <v>280.01</v>
       </c>
@@ -5043,7 +5020,7 @@
         <v>280.5</v>
       </c>
     </row>
-    <row r="563" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" s="1">
         <v>280.51</v>
       </c>
@@ -5051,7 +5028,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="564" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" s="1">
         <v>281.01</v>
       </c>
@@ -5059,7 +5036,7 @@
         <v>281.5</v>
       </c>
     </row>
-    <row r="565" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" s="1">
         <v>281.51</v>
       </c>
@@ -5067,7 +5044,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="566" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" s="1">
         <v>282.01</v>
       </c>
@@ -5075,7 +5052,7 @@
         <v>282.5</v>
       </c>
     </row>
-    <row r="567" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" s="1">
         <v>282.51</v>
       </c>
@@ -5083,7 +5060,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="568" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" s="1">
         <v>283.01</v>
       </c>
@@ -5091,7 +5068,7 @@
         <v>283.5</v>
       </c>
     </row>
-    <row r="569" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" s="1">
         <v>283.51</v>
       </c>
@@ -5099,7 +5076,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="570" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" s="1">
         <v>284.01</v>
       </c>
@@ -5107,7 +5084,7 @@
         <v>284.5</v>
       </c>
     </row>
-    <row r="571" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" s="1">
         <v>284.51</v>
       </c>
@@ -5115,7 +5092,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="572" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" s="1">
         <v>285.01</v>
       </c>
@@ -5123,7 +5100,7 @@
         <v>285.5</v>
       </c>
     </row>
-    <row r="573" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" s="1">
         <v>285.51</v>
       </c>
@@ -5131,7 +5108,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="574" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" s="1">
         <v>286.01</v>
       </c>
@@ -5139,7 +5116,7 @@
         <v>286.5</v>
       </c>
     </row>
-    <row r="575" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" s="1">
         <v>286.51</v>
       </c>
@@ -5147,7 +5124,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="576" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" s="1">
         <v>287.01</v>
       </c>
@@ -5155,7 +5132,7 @@
         <v>287.5</v>
       </c>
     </row>
-    <row r="577" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" s="1">
         <v>287.51</v>
       </c>
@@ -5163,7 +5140,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="578" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" s="1">
         <v>288.01</v>
       </c>
@@ -5171,7 +5148,7 @@
         <v>288.5</v>
       </c>
     </row>
-    <row r="579" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" s="1">
         <v>288.51</v>
       </c>
@@ -5179,7 +5156,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="580" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" s="1">
         <v>289.01</v>
       </c>
@@ -5187,7 +5164,7 @@
         <v>289.5</v>
       </c>
     </row>
-    <row r="581" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" s="1">
         <v>289.51</v>
       </c>
@@ -5195,7 +5172,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="582" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" s="1">
         <v>290.01</v>
       </c>
@@ -5203,7 +5180,7 @@
         <v>290.5</v>
       </c>
     </row>
-    <row r="583" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" s="1">
         <v>290.51</v>
       </c>
@@ -5211,7 +5188,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="584" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" s="1">
         <v>291.01</v>
       </c>
@@ -5219,7 +5196,7 @@
         <v>291.5</v>
       </c>
     </row>
-    <row r="585" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" s="1">
         <v>291.51</v>
       </c>
@@ -5227,7 +5204,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="586" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" s="1">
         <v>292.01</v>
       </c>
@@ -5235,7 +5212,7 @@
         <v>292.5</v>
       </c>
     </row>
-    <row r="587" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" s="1">
         <v>292.51</v>
       </c>
@@ -5243,7 +5220,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="588" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" s="1">
         <v>293.01</v>
       </c>
@@ -5251,7 +5228,7 @@
         <v>293.5</v>
       </c>
     </row>
-    <row r="589" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" s="1">
         <v>293.51</v>
       </c>
@@ -5259,7 +5236,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="590" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" s="1">
         <v>294.01</v>
       </c>
@@ -5267,7 +5244,7 @@
         <v>294.5</v>
       </c>
     </row>
-    <row r="591" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" s="1">
         <v>294.51</v>
       </c>
@@ -5275,7 +5252,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="592" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" s="1">
         <v>295.01</v>
       </c>
@@ -5283,7 +5260,7 @@
         <v>295.5</v>
       </c>
     </row>
-    <row r="593" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" s="1">
         <v>295.51</v>
       </c>
@@ -5291,7 +5268,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="594" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594" s="1">
         <v>296.01</v>
       </c>
@@ -5299,7 +5276,7 @@
         <v>296.5</v>
       </c>
     </row>
-    <row r="595" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" s="1">
         <v>296.51</v>
       </c>
@@ -5307,7 +5284,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="596" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A596" s="1">
         <v>297.01</v>
       </c>
@@ -5315,7 +5292,7 @@
         <v>297.5</v>
       </c>
     </row>
-    <row r="597" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A597" s="1">
         <v>297.51</v>
       </c>
@@ -5323,7 +5300,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="598" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A598" s="1">
         <v>298.01</v>
       </c>
@@ -5331,7 +5308,7 @@
         <v>298.5</v>
       </c>
     </row>
-    <row r="599" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A599" s="1">
         <v>298.51</v>
       </c>
@@ -5339,7 +5316,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="600" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A600" s="1">
         <v>299.01</v>
       </c>
@@ -5347,7 +5324,7 @@
         <v>299.5</v>
       </c>
     </row>
-    <row r="601" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A601" s="1">
         <v>299.51</v>
       </c>

--- a/public/file/International Standard Rates Upload Template.xlsx
+++ b/public/file/International Standard Rates Upload Template.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23901"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\laragon\www\sonic\public\file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\sonic\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{039D1586-5C43-4351-AACC-3490679C0CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FDE8F72-4131-496C-B10C-5DB9BDC38F2D}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="348" windowWidth="23256" windowHeight="12720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,25 +20,17 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Range Down</t>
+  </si>
+  <si>
+    <t>Zone 1</t>
   </si>
   <si>
     <t>Zone 2</t>
@@ -59,6 +51,9 @@
     <t>Zone 7</t>
   </si>
   <si>
+    <t>Zone 8</t>
+  </si>
+  <si>
     <t>Zone 9</t>
   </si>
   <si>
@@ -69,18 +64,6 @@
   </si>
   <si>
     <t>Range Up</t>
-  </si>
-  <si>
-    <t>Zone 8B</t>
-  </si>
-  <si>
-    <t>Zone 1B</t>
-  </si>
-  <si>
-    <t>Zone 1A</t>
-  </si>
-  <si>
-    <t>Zone 8A</t>
   </si>
 </sst>
 </file>
@@ -505,57 +488,51 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O601"/>
+  <dimension ref="A1:M601"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:15" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:13" ht="18" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="L1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>0.01</v>
       </c>
@@ -563,7 +540,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>0.51</v>
       </c>
@@ -571,7 +548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>1.01</v>
       </c>
@@ -579,7 +556,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>1.51</v>
       </c>
@@ -587,7 +564,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>2.0099999999999998</v>
       </c>
@@ -595,7 +572,7 @@
         <v>2.5</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>2.5099999999999998</v>
       </c>
@@ -603,7 +580,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>3.01</v>
       </c>
@@ -611,7 +588,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>3.51</v>
       </c>
@@ -619,7 +596,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>4.01</v>
       </c>
@@ -627,7 +604,7 @@
         <v>4.5</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>4.51</v>
       </c>
@@ -635,7 +612,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>5.01</v>
       </c>
@@ -643,7 +620,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>5.51</v>
       </c>
@@ -651,7 +628,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>6.01</v>
       </c>
@@ -659,7 +636,7 @@
         <v>6.5</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>6.51</v>
       </c>
@@ -667,7 +644,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>7.01</v>
       </c>

--- a/public/file/International Standard Rates Upload Template.xlsx
+++ b/public/file/International Standard Rates Upload Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\sonic_3\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B65E4410-757C-44DA-9A60-73DC4E74B1F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B3D0AB-B1CF-4B45-828B-2721B1E84F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,19 +60,19 @@
     <t>Range Up</t>
   </si>
   <si>
-    <t>Zone 8B</t>
+    <t>Zone 1a</t>
   </si>
   <si>
-    <t>Zone 8C</t>
+    <t>Zone 1b</t>
   </si>
   <si>
-    <t>Zone 8A</t>
+    <t>Zone 8a</t>
   </si>
   <si>
-    <t>Zone 1A</t>
+    <t>Zone 8b</t>
   </si>
   <si>
-    <t>Zone 1B</t>
+    <t>Zone 8c</t>
   </si>
 </sst>
 </file>
@@ -508,10 +508,10 @@
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>1</v>
@@ -535,10 +535,10 @@
         <v>13</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>7</v>

--- a/public/file/International Standard Rates Upload Template.xlsx
+++ b/public/file/International Standard Rates Upload Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\sonic_3\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4B3D0AB-B1CF-4B45-828B-2721B1E84F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62DB5763-0289-4D8F-8E91-3D71D2B22BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Range Down</t>
   </si>
@@ -60,19 +60,16 @@
     <t>Range Up</t>
   </si>
   <si>
-    <t>Zone 1a</t>
-  </si>
-  <si>
-    <t>Zone 1b</t>
-  </si>
-  <si>
     <t>Zone 8a</t>
   </si>
   <si>
-    <t>Zone 8b</t>
+    <t>Zone 1</t>
   </si>
   <si>
-    <t>Zone 8c</t>
+    <t>Zone 12</t>
+  </si>
+  <si>
+    <t>Zone 13</t>
   </si>
 </sst>
 </file>
@@ -497,10 +494,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P601"/>
+  <dimension ref="A1:O601"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="14" max="14" width="8.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" ht="17.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>10</v>
       </c>
@@ -508,49 +508,46 @@
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="K1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>0.01</v>
       </c>
@@ -570,9 +567,8 @@
       <c r="M2" s="4"/>
       <c r="N2" s="4"/>
       <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>0.51</v>
       </c>
@@ -592,9 +588,8 @@
       <c r="M3" s="4"/>
       <c r="N3" s="4"/>
       <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>1.01</v>
       </c>
@@ -614,9 +609,8 @@
       <c r="M4" s="4"/>
       <c r="N4" s="4"/>
       <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>1.51</v>
       </c>
@@ -636,9 +630,8 @@
       <c r="M5" s="4"/>
       <c r="N5" s="4"/>
       <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>2.0099999999999998</v>
       </c>
@@ -658,9 +651,8 @@
       <c r="M6" s="4"/>
       <c r="N6" s="4"/>
       <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>2.5099999999999998</v>
       </c>
@@ -680,9 +672,8 @@
       <c r="M7" s="4"/>
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>3.01</v>
       </c>
@@ -702,9 +693,8 @@
       <c r="M8" s="4"/>
       <c r="N8" s="4"/>
       <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>3.51</v>
       </c>
@@ -724,9 +714,8 @@
       <c r="M9" s="4"/>
       <c r="N9" s="4"/>
       <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="1">
         <v>4.01</v>
       </c>
@@ -746,9 +735,8 @@
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
       <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="1">
         <v>4.51</v>
       </c>
@@ -768,9 +756,8 @@
       <c r="M11" s="4"/>
       <c r="N11" s="4"/>
       <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="1">
         <v>5.01</v>
       </c>
@@ -790,9 +777,8 @@
       <c r="M12" s="4"/>
       <c r="N12" s="4"/>
       <c r="O12" s="4"/>
-      <c r="P12" s="4"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="1">
         <v>5.51</v>
       </c>
@@ -812,9 +798,8 @@
       <c r="M13" s="4"/>
       <c r="N13" s="4"/>
       <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A14" s="1">
         <v>6.01</v>
       </c>
@@ -834,9 +819,8 @@
       <c r="M14" s="4"/>
       <c r="N14" s="4"/>
       <c r="O14" s="4"/>
-      <c r="P14" s="4"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>6.51</v>
       </c>
@@ -856,9 +840,8 @@
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
       <c r="O15" s="4"/>
-      <c r="P15" s="4"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A16" s="1">
         <v>7.01</v>
       </c>
@@ -878,9 +861,8 @@
       <c r="M16" s="4"/>
       <c r="N16" s="4"/>
       <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" s="1">
         <v>7.51</v>
       </c>
@@ -900,9 +882,8 @@
       <c r="M17" s="4"/>
       <c r="N17" s="4"/>
       <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" s="1">
         <v>8.01</v>
       </c>
@@ -922,9 +903,8 @@
       <c r="M18" s="4"/>
       <c r="N18" s="4"/>
       <c r="O18" s="4"/>
-      <c r="P18" s="4"/>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>8.51</v>
       </c>
@@ -944,9 +924,8 @@
       <c r="M19" s="4"/>
       <c r="N19" s="4"/>
       <c r="O19" s="4"/>
-      <c r="P19" s="4"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>9.01</v>
       </c>
@@ -966,9 +945,8 @@
       <c r="M20" s="4"/>
       <c r="N20" s="4"/>
       <c r="O20" s="4"/>
-      <c r="P20" s="4"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A21" s="1">
         <v>9.51</v>
       </c>
@@ -988,9 +966,8 @@
       <c r="M21" s="4"/>
       <c r="N21" s="4"/>
       <c r="O21" s="4"/>
-      <c r="P21" s="4"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A22" s="1">
         <v>10.01</v>
       </c>
@@ -1010,9 +987,8 @@
       <c r="M22" s="4"/>
       <c r="N22" s="4"/>
       <c r="O22" s="4"/>
-      <c r="P22" s="4"/>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A23" s="1">
         <v>10.51</v>
       </c>
@@ -1032,9 +1008,8 @@
       <c r="M23" s="4"/>
       <c r="N23" s="4"/>
       <c r="O23" s="4"/>
-      <c r="P23" s="4"/>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A24" s="1">
         <v>11.01</v>
       </c>
@@ -1054,9 +1029,8 @@
       <c r="M24" s="4"/>
       <c r="N24" s="4"/>
       <c r="O24" s="4"/>
-      <c r="P24" s="4"/>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A25" s="1">
         <v>11.51</v>
       </c>
@@ -1076,9 +1050,8 @@
       <c r="M25" s="4"/>
       <c r="N25" s="4"/>
       <c r="O25" s="4"/>
-      <c r="P25" s="4"/>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A26" s="1">
         <v>12.01</v>
       </c>
@@ -1098,9 +1071,8 @@
       <c r="M26" s="4"/>
       <c r="N26" s="4"/>
       <c r="O26" s="4"/>
-      <c r="P26" s="4"/>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A27" s="1">
         <v>12.51</v>
       </c>
@@ -1120,9 +1092,8 @@
       <c r="M27" s="4"/>
       <c r="N27" s="4"/>
       <c r="O27" s="4"/>
-      <c r="P27" s="4"/>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A28" s="1">
         <v>13.01</v>
       </c>
@@ -1142,9 +1113,8 @@
       <c r="M28" s="4"/>
       <c r="N28" s="4"/>
       <c r="O28" s="4"/>
-      <c r="P28" s="4"/>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A29" s="1">
         <v>13.51</v>
       </c>
@@ -1164,9 +1134,8 @@
       <c r="M29" s="4"/>
       <c r="N29" s="4"/>
       <c r="O29" s="4"/>
-      <c r="P29" s="4"/>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>14.01</v>
       </c>
@@ -1186,9 +1155,8 @@
       <c r="M30" s="4"/>
       <c r="N30" s="4"/>
       <c r="O30" s="4"/>
-      <c r="P30" s="4"/>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>14.51</v>
       </c>
@@ -1208,9 +1176,8 @@
       <c r="M31" s="4"/>
       <c r="N31" s="4"/>
       <c r="O31" s="4"/>
-      <c r="P31" s="4"/>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>15.01</v>
       </c>
@@ -1230,9 +1197,8 @@
       <c r="M32" s="4"/>
       <c r="N32" s="4"/>
       <c r="O32" s="4"/>
-      <c r="P32" s="4"/>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>15.51</v>
       </c>
@@ -1252,9 +1218,8 @@
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
       <c r="O33" s="4"/>
-      <c r="P33" s="4"/>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>16.010000000000002</v>
       </c>
@@ -1274,9 +1239,8 @@
       <c r="M34" s="4"/>
       <c r="N34" s="4"/>
       <c r="O34" s="4"/>
-      <c r="P34" s="4"/>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>16.510000000000002</v>
       </c>
@@ -1296,9 +1260,8 @@
       <c r="M35" s="4"/>
       <c r="N35" s="4"/>
       <c r="O35" s="4"/>
-      <c r="P35" s="4"/>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>17.010000000000002</v>
       </c>
@@ -1318,9 +1281,8 @@
       <c r="M36" s="4"/>
       <c r="N36" s="4"/>
       <c r="O36" s="4"/>
-      <c r="P36" s="4"/>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>17.510000000000002</v>
       </c>
@@ -1340,9 +1302,8 @@
       <c r="M37" s="4"/>
       <c r="N37" s="4"/>
       <c r="O37" s="4"/>
-      <c r="P37" s="4"/>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>18.010000000000002</v>
       </c>
@@ -1362,9 +1323,8 @@
       <c r="M38" s="4"/>
       <c r="N38" s="4"/>
       <c r="O38" s="4"/>
-      <c r="P38" s="4"/>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>18.510000000000002</v>
       </c>
@@ -1384,9 +1344,8 @@
       <c r="M39" s="4"/>
       <c r="N39" s="4"/>
       <c r="O39" s="4"/>
-      <c r="P39" s="4"/>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A40" s="1">
         <v>19.010000000000002</v>
       </c>
@@ -1406,9 +1365,8 @@
       <c r="M40" s="4"/>
       <c r="N40" s="4"/>
       <c r="O40" s="4"/>
-      <c r="P40" s="4"/>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A41" s="1">
         <v>19.510000000000002</v>
       </c>
@@ -1428,9 +1386,8 @@
       <c r="M41" s="4"/>
       <c r="N41" s="4"/>
       <c r="O41" s="4"/>
-      <c r="P41" s="4"/>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A42" s="1">
         <v>20.010000000000002</v>
       </c>
@@ -1450,9 +1407,8 @@
       <c r="M42" s="4"/>
       <c r="N42" s="4"/>
       <c r="O42" s="4"/>
-      <c r="P42" s="4"/>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A43" s="1">
         <v>20.51</v>
       </c>
@@ -1472,9 +1428,8 @@
       <c r="M43" s="4"/>
       <c r="N43" s="4"/>
       <c r="O43" s="4"/>
-      <c r="P43" s="4"/>
-    </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A44" s="1">
         <v>21.01</v>
       </c>
@@ -1494,9 +1449,8 @@
       <c r="M44" s="4"/>
       <c r="N44" s="4"/>
       <c r="O44" s="4"/>
-      <c r="P44" s="4"/>
-    </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A45" s="1">
         <v>21.51</v>
       </c>
@@ -1516,9 +1470,8 @@
       <c r="M45" s="4"/>
       <c r="N45" s="4"/>
       <c r="O45" s="4"/>
-      <c r="P45" s="4"/>
-    </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A46" s="1">
         <v>22.01</v>
       </c>
@@ -1538,9 +1491,8 @@
       <c r="M46" s="4"/>
       <c r="N46" s="4"/>
       <c r="O46" s="4"/>
-      <c r="P46" s="4"/>
-    </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A47" s="1">
         <v>22.51</v>
       </c>
@@ -1560,9 +1512,8 @@
       <c r="M47" s="4"/>
       <c r="N47" s="4"/>
       <c r="O47" s="4"/>
-      <c r="P47" s="4"/>
-    </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A48" s="1">
         <v>23.01</v>
       </c>
@@ -1582,9 +1533,8 @@
       <c r="M48" s="4"/>
       <c r="N48" s="4"/>
       <c r="O48" s="4"/>
-      <c r="P48" s="4"/>
-    </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A49" s="1">
         <v>23.51</v>
       </c>
@@ -1604,9 +1554,8 @@
       <c r="M49" s="4"/>
       <c r="N49" s="4"/>
       <c r="O49" s="4"/>
-      <c r="P49" s="4"/>
-    </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A50" s="1">
         <v>24.01</v>
       </c>
@@ -1626,9 +1575,8 @@
       <c r="M50" s="4"/>
       <c r="N50" s="4"/>
       <c r="O50" s="4"/>
-      <c r="P50" s="4"/>
-    </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A51" s="1">
         <v>24.51</v>
       </c>
@@ -1648,9 +1596,8 @@
       <c r="M51" s="4"/>
       <c r="N51" s="4"/>
       <c r="O51" s="4"/>
-      <c r="P51" s="4"/>
-    </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="52" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A52" s="1">
         <v>25.01</v>
       </c>
@@ -1670,9 +1617,8 @@
       <c r="M52" s="4"/>
       <c r="N52" s="4"/>
       <c r="O52" s="4"/>
-      <c r="P52" s="4"/>
-    </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="53" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A53" s="1">
         <v>25.51</v>
       </c>
@@ -1692,9 +1638,8 @@
       <c r="M53" s="4"/>
       <c r="N53" s="4"/>
       <c r="O53" s="4"/>
-      <c r="P53" s="4"/>
-    </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A54" s="1">
         <v>26.01</v>
       </c>
@@ -1714,9 +1659,8 @@
       <c r="M54" s="4"/>
       <c r="N54" s="4"/>
       <c r="O54" s="4"/>
-      <c r="P54" s="4"/>
-    </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A55" s="1">
         <v>26.51</v>
       </c>
@@ -1736,9 +1680,8 @@
       <c r="M55" s="4"/>
       <c r="N55" s="4"/>
       <c r="O55" s="4"/>
-      <c r="P55" s="4"/>
-    </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A56" s="1">
         <v>27.01</v>
       </c>
@@ -1758,9 +1701,8 @@
       <c r="M56" s="4"/>
       <c r="N56" s="4"/>
       <c r="O56" s="4"/>
-      <c r="P56" s="4"/>
-    </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A57" s="1">
         <v>27.51</v>
       </c>
@@ -1780,9 +1722,8 @@
       <c r="M57" s="4"/>
       <c r="N57" s="4"/>
       <c r="O57" s="4"/>
-      <c r="P57" s="4"/>
-    </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A58" s="1">
         <v>28.01</v>
       </c>
@@ -1802,9 +1743,8 @@
       <c r="M58" s="4"/>
       <c r="N58" s="4"/>
       <c r="O58" s="4"/>
-      <c r="P58" s="4"/>
-    </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A59" s="1">
         <v>28.51</v>
       </c>
@@ -1824,9 +1764,8 @@
       <c r="M59" s="4"/>
       <c r="N59" s="4"/>
       <c r="O59" s="4"/>
-      <c r="P59" s="4"/>
-    </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="60" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A60" s="1">
         <v>29.01</v>
       </c>
@@ -1846,9 +1785,8 @@
       <c r="M60" s="4"/>
       <c r="N60" s="4"/>
       <c r="O60" s="4"/>
-      <c r="P60" s="4"/>
-    </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A61" s="1">
         <v>29.51</v>
       </c>
@@ -1868,9 +1806,8 @@
       <c r="M61" s="4"/>
       <c r="N61" s="4"/>
       <c r="O61" s="4"/>
-      <c r="P61" s="4"/>
-    </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A62" s="1">
         <v>30.01</v>
       </c>
@@ -1890,9 +1827,8 @@
       <c r="M62" s="4"/>
       <c r="N62" s="4"/>
       <c r="O62" s="4"/>
-      <c r="P62" s="4"/>
-    </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A63" s="1">
         <v>30.51</v>
       </c>
@@ -1912,9 +1848,8 @@
       <c r="M63" s="4"/>
       <c r="N63" s="4"/>
       <c r="O63" s="4"/>
-      <c r="P63" s="4"/>
-    </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A64" s="1">
         <v>31.01</v>
       </c>
@@ -1934,9 +1869,8 @@
       <c r="M64" s="4"/>
       <c r="N64" s="4"/>
       <c r="O64" s="4"/>
-      <c r="P64" s="4"/>
-    </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="65" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A65" s="1">
         <v>31.51</v>
       </c>
@@ -1956,9 +1890,8 @@
       <c r="M65" s="4"/>
       <c r="N65" s="4"/>
       <c r="O65" s="4"/>
-      <c r="P65" s="4"/>
-    </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A66" s="1">
         <v>32.01</v>
       </c>
@@ -1978,9 +1911,8 @@
       <c r="M66" s="4"/>
       <c r="N66" s="4"/>
       <c r="O66" s="4"/>
-      <c r="P66" s="4"/>
-    </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A67" s="1">
         <v>32.51</v>
       </c>
@@ -2000,9 +1932,8 @@
       <c r="M67" s="4"/>
       <c r="N67" s="4"/>
       <c r="O67" s="4"/>
-      <c r="P67" s="4"/>
-    </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A68" s="1">
         <v>33.01</v>
       </c>
@@ -2022,9 +1953,8 @@
       <c r="M68" s="4"/>
       <c r="N68" s="4"/>
       <c r="O68" s="4"/>
-      <c r="P68" s="4"/>
-    </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A69" s="1">
         <v>33.51</v>
       </c>
@@ -2044,9 +1974,8 @@
       <c r="M69" s="4"/>
       <c r="N69" s="4"/>
       <c r="O69" s="4"/>
-      <c r="P69" s="4"/>
-    </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A70" s="1">
         <v>34.01</v>
       </c>
@@ -2066,9 +1995,8 @@
       <c r="M70" s="4"/>
       <c r="N70" s="4"/>
       <c r="O70" s="4"/>
-      <c r="P70" s="4"/>
-    </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="71" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A71" s="1">
         <v>34.51</v>
       </c>
@@ -2088,9 +2016,8 @@
       <c r="M71" s="4"/>
       <c r="N71" s="4"/>
       <c r="O71" s="4"/>
-      <c r="P71" s="4"/>
-    </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="72" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A72" s="1">
         <v>35.01</v>
       </c>
@@ -2110,9 +2037,8 @@
       <c r="M72" s="4"/>
       <c r="N72" s="4"/>
       <c r="O72" s="4"/>
-      <c r="P72" s="4"/>
-    </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="73" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A73" s="1">
         <v>35.51</v>
       </c>
@@ -2132,9 +2058,8 @@
       <c r="M73" s="4"/>
       <c r="N73" s="4"/>
       <c r="O73" s="4"/>
-      <c r="P73" s="4"/>
-    </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A74" s="1">
         <v>36.01</v>
       </c>
@@ -2154,9 +2079,8 @@
       <c r="M74" s="4"/>
       <c r="N74" s="4"/>
       <c r="O74" s="4"/>
-      <c r="P74" s="4"/>
-    </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="75" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A75" s="1">
         <v>36.51</v>
       </c>
@@ -2176,9 +2100,8 @@
       <c r="M75" s="4"/>
       <c r="N75" s="4"/>
       <c r="O75" s="4"/>
-      <c r="P75" s="4"/>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A76" s="1">
         <v>37.01</v>
       </c>
@@ -2198,9 +2121,8 @@
       <c r="M76" s="4"/>
       <c r="N76" s="4"/>
       <c r="O76" s="4"/>
-      <c r="P76" s="4"/>
-    </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A77" s="1">
         <v>37.51</v>
       </c>
@@ -2220,9 +2142,8 @@
       <c r="M77" s="4"/>
       <c r="N77" s="4"/>
       <c r="O77" s="4"/>
-      <c r="P77" s="4"/>
-    </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="78" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A78" s="1">
         <v>38.01</v>
       </c>
@@ -2242,9 +2163,8 @@
       <c r="M78" s="4"/>
       <c r="N78" s="4"/>
       <c r="O78" s="4"/>
-      <c r="P78" s="4"/>
-    </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="79" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A79" s="1">
         <v>38.51</v>
       </c>
@@ -2264,9 +2184,8 @@
       <c r="M79" s="4"/>
       <c r="N79" s="4"/>
       <c r="O79" s="4"/>
-      <c r="P79" s="4"/>
-    </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A80" s="1">
         <v>39.01</v>
       </c>
@@ -2286,9 +2205,8 @@
       <c r="M80" s="4"/>
       <c r="N80" s="4"/>
       <c r="O80" s="4"/>
-      <c r="P80" s="4"/>
-    </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="81" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A81" s="1">
         <v>39.51</v>
       </c>
@@ -2308,9 +2226,8 @@
       <c r="M81" s="4"/>
       <c r="N81" s="4"/>
       <c r="O81" s="4"/>
-      <c r="P81" s="4"/>
-    </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="82" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A82" s="1">
         <v>40.01</v>
       </c>
@@ -2330,9 +2247,8 @@
       <c r="M82" s="4"/>
       <c r="N82" s="4"/>
       <c r="O82" s="4"/>
-      <c r="P82" s="4"/>
-    </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="83" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A83" s="1">
         <v>40.51</v>
       </c>
@@ -2352,9 +2268,8 @@
       <c r="M83" s="4"/>
       <c r="N83" s="4"/>
       <c r="O83" s="4"/>
-      <c r="P83" s="4"/>
-    </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="84" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A84" s="1">
         <v>41.01</v>
       </c>
@@ -2374,9 +2289,8 @@
       <c r="M84" s="4"/>
       <c r="N84" s="4"/>
       <c r="O84" s="4"/>
-      <c r="P84" s="4"/>
-    </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="85" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A85" s="1">
         <v>41.51</v>
       </c>
@@ -2396,9 +2310,8 @@
       <c r="M85" s="4"/>
       <c r="N85" s="4"/>
       <c r="O85" s="4"/>
-      <c r="P85" s="4"/>
-    </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="86" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A86" s="1">
         <v>42.01</v>
       </c>
@@ -2418,9 +2331,8 @@
       <c r="M86" s="4"/>
       <c r="N86" s="4"/>
       <c r="O86" s="4"/>
-      <c r="P86" s="4"/>
-    </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="87" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A87" s="1">
         <v>42.51</v>
       </c>
@@ -2440,9 +2352,8 @@
       <c r="M87" s="4"/>
       <c r="N87" s="4"/>
       <c r="O87" s="4"/>
-      <c r="P87" s="4"/>
-    </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="88" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A88" s="1">
         <v>43.01</v>
       </c>
@@ -2462,9 +2373,8 @@
       <c r="M88" s="4"/>
       <c r="N88" s="4"/>
       <c r="O88" s="4"/>
-      <c r="P88" s="4"/>
-    </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="89" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A89" s="1">
         <v>43.51</v>
       </c>
@@ -2484,9 +2394,8 @@
       <c r="M89" s="4"/>
       <c r="N89" s="4"/>
       <c r="O89" s="4"/>
-      <c r="P89" s="4"/>
-    </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="90" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A90" s="1">
         <v>44.01</v>
       </c>
@@ -2506,9 +2415,8 @@
       <c r="M90" s="4"/>
       <c r="N90" s="4"/>
       <c r="O90" s="4"/>
-      <c r="P90" s="4"/>
-    </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A91" s="1">
         <v>44.51</v>
       </c>
@@ -2528,9 +2436,8 @@
       <c r="M91" s="4"/>
       <c r="N91" s="4"/>
       <c r="O91" s="4"/>
-      <c r="P91" s="4"/>
-    </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="92" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A92" s="1">
         <v>45.01</v>
       </c>
@@ -2550,9 +2457,8 @@
       <c r="M92" s="4"/>
       <c r="N92" s="4"/>
       <c r="O92" s="4"/>
-      <c r="P92" s="4"/>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="93" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A93" s="1">
         <v>45.51</v>
       </c>
@@ -2572,9 +2478,8 @@
       <c r="M93" s="4"/>
       <c r="N93" s="4"/>
       <c r="O93" s="4"/>
-      <c r="P93" s="4"/>
-    </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="94" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A94" s="1">
         <v>46.01</v>
       </c>
@@ -2594,9 +2499,8 @@
       <c r="M94" s="4"/>
       <c r="N94" s="4"/>
       <c r="O94" s="4"/>
-      <c r="P94" s="4"/>
-    </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="95" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A95" s="1">
         <v>46.51</v>
       </c>
@@ -2616,9 +2520,8 @@
       <c r="M95" s="4"/>
       <c r="N95" s="4"/>
       <c r="O95" s="4"/>
-      <c r="P95" s="4"/>
-    </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A96" s="1">
         <v>47.01</v>
       </c>
@@ -2638,9 +2541,8 @@
       <c r="M96" s="4"/>
       <c r="N96" s="4"/>
       <c r="O96" s="4"/>
-      <c r="P96" s="4"/>
-    </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="97" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A97" s="1">
         <v>47.51</v>
       </c>
@@ -2660,9 +2562,8 @@
       <c r="M97" s="4"/>
       <c r="N97" s="4"/>
       <c r="O97" s="4"/>
-      <c r="P97" s="4"/>
-    </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A98" s="1">
         <v>48.01</v>
       </c>
@@ -2682,9 +2583,8 @@
       <c r="M98" s="4"/>
       <c r="N98" s="4"/>
       <c r="O98" s="4"/>
-      <c r="P98" s="4"/>
-    </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A99" s="1">
         <v>48.51</v>
       </c>
@@ -2704,9 +2604,8 @@
       <c r="M99" s="4"/>
       <c r="N99" s="4"/>
       <c r="O99" s="4"/>
-      <c r="P99" s="4"/>
-    </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="100" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A100" s="1">
         <v>49.01</v>
       </c>
@@ -2726,9 +2625,8 @@
       <c r="M100" s="4"/>
       <c r="N100" s="4"/>
       <c r="O100" s="4"/>
-      <c r="P100" s="4"/>
-    </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="101" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A101" s="1">
         <v>49.51</v>
       </c>
@@ -2748,9 +2646,8 @@
       <c r="M101" s="4"/>
       <c r="N101" s="4"/>
       <c r="O101" s="4"/>
-      <c r="P101" s="4"/>
-    </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="102" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A102" s="1">
         <v>50.01</v>
       </c>
@@ -2770,9 +2667,8 @@
       <c r="M102" s="4"/>
       <c r="N102" s="4"/>
       <c r="O102" s="4"/>
-      <c r="P102" s="4"/>
-    </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="103" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
         <v>50.51</v>
       </c>
@@ -2792,9 +2688,8 @@
       <c r="M103" s="4"/>
       <c r="N103" s="4"/>
       <c r="O103" s="4"/>
-      <c r="P103" s="4"/>
-    </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="104" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
         <v>51.01</v>
       </c>
@@ -2814,9 +2709,8 @@
       <c r="M104" s="4"/>
       <c r="N104" s="4"/>
       <c r="O104" s="4"/>
-      <c r="P104" s="4"/>
-    </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="105" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
         <v>51.51</v>
       </c>
@@ -2836,9 +2730,8 @@
       <c r="M105" s="4"/>
       <c r="N105" s="4"/>
       <c r="O105" s="4"/>
-      <c r="P105" s="4"/>
-    </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="106" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
         <v>52.01</v>
       </c>
@@ -2858,9 +2751,8 @@
       <c r="M106" s="4"/>
       <c r="N106" s="4"/>
       <c r="O106" s="4"/>
-      <c r="P106" s="4"/>
-    </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="107" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
         <v>52.51</v>
       </c>
@@ -2880,9 +2772,8 @@
       <c r="M107" s="4"/>
       <c r="N107" s="4"/>
       <c r="O107" s="4"/>
-      <c r="P107" s="4"/>
-    </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="108" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
         <v>53.01</v>
       </c>
@@ -2902,9 +2793,8 @@
       <c r="M108" s="4"/>
       <c r="N108" s="4"/>
       <c r="O108" s="4"/>
-      <c r="P108" s="4"/>
-    </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="109" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
         <v>53.51</v>
       </c>
@@ -2924,9 +2814,8 @@
       <c r="M109" s="4"/>
       <c r="N109" s="4"/>
       <c r="O109" s="4"/>
-      <c r="P109" s="4"/>
-    </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="110" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
         <v>54.01</v>
       </c>
@@ -2946,9 +2835,8 @@
       <c r="M110" s="4"/>
       <c r="N110" s="4"/>
       <c r="O110" s="4"/>
-      <c r="P110" s="4"/>
-    </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="111" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
         <v>54.51</v>
       </c>
@@ -2968,9 +2856,8 @@
       <c r="M111" s="4"/>
       <c r="N111" s="4"/>
       <c r="O111" s="4"/>
-      <c r="P111" s="4"/>
-    </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="112" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
         <v>55.01</v>
       </c>
@@ -2990,9 +2877,8 @@
       <c r="M112" s="4"/>
       <c r="N112" s="4"/>
       <c r="O112" s="4"/>
-      <c r="P112" s="4"/>
-    </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="113" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A113" s="1">
         <v>55.51</v>
       </c>
@@ -3012,9 +2898,8 @@
       <c r="M113" s="4"/>
       <c r="N113" s="4"/>
       <c r="O113" s="4"/>
-      <c r="P113" s="4"/>
-    </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="114" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A114" s="1">
         <v>56.01</v>
       </c>
@@ -3034,9 +2919,8 @@
       <c r="M114" s="4"/>
       <c r="N114" s="4"/>
       <c r="O114" s="4"/>
-      <c r="P114" s="4"/>
-    </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="115" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A115" s="1">
         <v>56.51</v>
       </c>
@@ -3056,9 +2940,8 @@
       <c r="M115" s="4"/>
       <c r="N115" s="4"/>
       <c r="O115" s="4"/>
-      <c r="P115" s="4"/>
-    </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="116" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A116" s="1">
         <v>57.01</v>
       </c>
@@ -3078,9 +2961,8 @@
       <c r="M116" s="4"/>
       <c r="N116" s="4"/>
       <c r="O116" s="4"/>
-      <c r="P116" s="4"/>
-    </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="117" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A117" s="1">
         <v>57.51</v>
       </c>
@@ -3100,9 +2982,8 @@
       <c r="M117" s="4"/>
       <c r="N117" s="4"/>
       <c r="O117" s="4"/>
-      <c r="P117" s="4"/>
-    </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="118" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A118" s="1">
         <v>58.01</v>
       </c>
@@ -3122,9 +3003,8 @@
       <c r="M118" s="4"/>
       <c r="N118" s="4"/>
       <c r="O118" s="4"/>
-      <c r="P118" s="4"/>
-    </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="119" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A119" s="1">
         <v>58.51</v>
       </c>
@@ -3144,9 +3024,8 @@
       <c r="M119" s="4"/>
       <c r="N119" s="4"/>
       <c r="O119" s="4"/>
-      <c r="P119" s="4"/>
-    </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="120" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A120" s="1">
         <v>59.01</v>
       </c>
@@ -3166,9 +3045,8 @@
       <c r="M120" s="4"/>
       <c r="N120" s="4"/>
       <c r="O120" s="4"/>
-      <c r="P120" s="4"/>
-    </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="121" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A121" s="1">
         <v>59.51</v>
       </c>
@@ -3188,9 +3066,8 @@
       <c r="M121" s="4"/>
       <c r="N121" s="4"/>
       <c r="O121" s="4"/>
-      <c r="P121" s="4"/>
-    </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="122" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A122" s="1">
         <v>60.01</v>
       </c>
@@ -3210,9 +3087,8 @@
       <c r="M122" s="4"/>
       <c r="N122" s="4"/>
       <c r="O122" s="4"/>
-      <c r="P122" s="4"/>
-    </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="123" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A123" s="1">
         <v>60.51</v>
       </c>
@@ -3232,9 +3108,8 @@
       <c r="M123" s="4"/>
       <c r="N123" s="4"/>
       <c r="O123" s="4"/>
-      <c r="P123" s="4"/>
-    </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="124" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A124" s="1">
         <v>61.01</v>
       </c>
@@ -3254,9 +3129,8 @@
       <c r="M124" s="4"/>
       <c r="N124" s="4"/>
       <c r="O124" s="4"/>
-      <c r="P124" s="4"/>
-    </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="125" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A125" s="1">
         <v>61.51</v>
       </c>
@@ -3276,9 +3150,8 @@
       <c r="M125" s="4"/>
       <c r="N125" s="4"/>
       <c r="O125" s="4"/>
-      <c r="P125" s="4"/>
-    </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="126" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A126" s="1">
         <v>62.01</v>
       </c>
@@ -3298,9 +3171,8 @@
       <c r="M126" s="4"/>
       <c r="N126" s="4"/>
       <c r="O126" s="4"/>
-      <c r="P126" s="4"/>
-    </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="127" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A127" s="1">
         <v>62.51</v>
       </c>
@@ -3320,9 +3192,8 @@
       <c r="M127" s="4"/>
       <c r="N127" s="4"/>
       <c r="O127" s="4"/>
-      <c r="P127" s="4"/>
-    </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="128" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A128" s="1">
         <v>63.01</v>
       </c>
@@ -3342,9 +3213,8 @@
       <c r="M128" s="4"/>
       <c r="N128" s="4"/>
       <c r="O128" s="4"/>
-      <c r="P128" s="4"/>
-    </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="129" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A129" s="1">
         <v>63.51</v>
       </c>
@@ -3364,9 +3234,8 @@
       <c r="M129" s="4"/>
       <c r="N129" s="4"/>
       <c r="O129" s="4"/>
-      <c r="P129" s="4"/>
-    </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="130" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A130" s="1">
         <v>64.010000000000005</v>
       </c>
@@ -3386,9 +3255,8 @@
       <c r="M130" s="4"/>
       <c r="N130" s="4"/>
       <c r="O130" s="4"/>
-      <c r="P130" s="4"/>
-    </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="131" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A131" s="1">
         <v>64.510000000000005</v>
       </c>
@@ -3408,9 +3276,8 @@
       <c r="M131" s="4"/>
       <c r="N131" s="4"/>
       <c r="O131" s="4"/>
-      <c r="P131" s="4"/>
-    </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="132" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A132" s="1">
         <v>65.010000000000005</v>
       </c>
@@ -3430,9 +3297,8 @@
       <c r="M132" s="4"/>
       <c r="N132" s="4"/>
       <c r="O132" s="4"/>
-      <c r="P132" s="4"/>
-    </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="133" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A133" s="1">
         <v>65.510000000000005</v>
       </c>
@@ -3452,9 +3318,8 @@
       <c r="M133" s="4"/>
       <c r="N133" s="4"/>
       <c r="O133" s="4"/>
-      <c r="P133" s="4"/>
-    </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="134" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A134" s="1">
         <v>66.010000000000005</v>
       </c>
@@ -3474,9 +3339,8 @@
       <c r="M134" s="4"/>
       <c r="N134" s="4"/>
       <c r="O134" s="4"/>
-      <c r="P134" s="4"/>
-    </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="135" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A135" s="1">
         <v>66.510000000000005</v>
       </c>
@@ -3496,9 +3360,8 @@
       <c r="M135" s="4"/>
       <c r="N135" s="4"/>
       <c r="O135" s="4"/>
-      <c r="P135" s="4"/>
-    </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="136" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A136" s="1">
         <v>67.010000000000005</v>
       </c>
@@ -3518,9 +3381,8 @@
       <c r="M136" s="4"/>
       <c r="N136" s="4"/>
       <c r="O136" s="4"/>
-      <c r="P136" s="4"/>
-    </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="137" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A137" s="1">
         <v>67.510000000000005</v>
       </c>
@@ -3540,9 +3402,8 @@
       <c r="M137" s="4"/>
       <c r="N137" s="4"/>
       <c r="O137" s="4"/>
-      <c r="P137" s="4"/>
-    </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="138" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A138" s="1">
         <v>68.010000000000005</v>
       </c>
@@ -3562,9 +3423,8 @@
       <c r="M138" s="4"/>
       <c r="N138" s="4"/>
       <c r="O138" s="4"/>
-      <c r="P138" s="4"/>
-    </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="139" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A139" s="1">
         <v>68.510000000000005</v>
       </c>
@@ -3584,9 +3444,8 @@
       <c r="M139" s="4"/>
       <c r="N139" s="4"/>
       <c r="O139" s="4"/>
-      <c r="P139" s="4"/>
-    </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="140" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A140" s="1">
         <v>69.010000000000005</v>
       </c>
@@ -3606,9 +3465,8 @@
       <c r="M140" s="4"/>
       <c r="N140" s="4"/>
       <c r="O140" s="4"/>
-      <c r="P140" s="4"/>
-    </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="141" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A141" s="1">
         <v>69.510000000000005</v>
       </c>
@@ -3628,9 +3486,8 @@
       <c r="M141" s="4"/>
       <c r="N141" s="4"/>
       <c r="O141" s="4"/>
-      <c r="P141" s="4"/>
-    </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="142" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A142" s="1">
         <v>70.010000000000005</v>
       </c>
@@ -3650,9 +3507,8 @@
       <c r="M142" s="4"/>
       <c r="N142" s="4"/>
       <c r="O142" s="4"/>
-      <c r="P142" s="4"/>
-    </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="143" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A143" s="1">
         <v>70.510000000000005</v>
       </c>
@@ -3672,9 +3528,8 @@
       <c r="M143" s="4"/>
       <c r="N143" s="4"/>
       <c r="O143" s="4"/>
-      <c r="P143" s="4"/>
-    </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="144" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A144" s="1">
         <v>71.010000000000005</v>
       </c>
@@ -3694,9 +3549,8 @@
       <c r="M144" s="4"/>
       <c r="N144" s="4"/>
       <c r="O144" s="4"/>
-      <c r="P144" s="4"/>
-    </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="145" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A145" s="1">
         <v>71.510000000000005</v>
       </c>
@@ -3716,9 +3570,8 @@
       <c r="M145" s="4"/>
       <c r="N145" s="4"/>
       <c r="O145" s="4"/>
-      <c r="P145" s="4"/>
-    </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="146" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A146" s="1">
         <v>72.010000000000005</v>
       </c>
@@ -3738,9 +3591,8 @@
       <c r="M146" s="4"/>
       <c r="N146" s="4"/>
       <c r="O146" s="4"/>
-      <c r="P146" s="4"/>
-    </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="147" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A147" s="1">
         <v>72.510000000000005</v>
       </c>
@@ -3760,9 +3612,8 @@
       <c r="M147" s="4"/>
       <c r="N147" s="4"/>
       <c r="O147" s="4"/>
-      <c r="P147" s="4"/>
-    </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="148" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A148" s="1">
         <v>73.010000000000005</v>
       </c>
@@ -3782,9 +3633,8 @@
       <c r="M148" s="4"/>
       <c r="N148" s="4"/>
       <c r="O148" s="4"/>
-      <c r="P148" s="4"/>
-    </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="149" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A149" s="1">
         <v>73.510000000000005</v>
       </c>
@@ -3804,9 +3654,8 @@
       <c r="M149" s="4"/>
       <c r="N149" s="4"/>
       <c r="O149" s="4"/>
-      <c r="P149" s="4"/>
-    </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A150" s="1">
         <v>74.010000000000005</v>
       </c>
@@ -3826,9 +3675,8 @@
       <c r="M150" s="4"/>
       <c r="N150" s="4"/>
       <c r="O150" s="4"/>
-      <c r="P150" s="4"/>
-    </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A151" s="1">
         <v>74.510000000000005</v>
       </c>
@@ -3848,9 +3696,8 @@
       <c r="M151" s="4"/>
       <c r="N151" s="4"/>
       <c r="O151" s="4"/>
-      <c r="P151" s="4"/>
-    </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A152" s="1">
         <v>75.010000000000005</v>
       </c>
@@ -3870,9 +3717,8 @@
       <c r="M152" s="4"/>
       <c r="N152" s="4"/>
       <c r="O152" s="4"/>
-      <c r="P152" s="4"/>
-    </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="153" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A153" s="1">
         <v>75.510000000000005</v>
       </c>
@@ -3892,9 +3738,8 @@
       <c r="M153" s="4"/>
       <c r="N153" s="4"/>
       <c r="O153" s="4"/>
-      <c r="P153" s="4"/>
-    </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="154" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A154" s="1">
         <v>76.010000000000005</v>
       </c>
@@ -3914,9 +3759,8 @@
       <c r="M154" s="4"/>
       <c r="N154" s="4"/>
       <c r="O154" s="4"/>
-      <c r="P154" s="4"/>
-    </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="155" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A155" s="1">
         <v>76.510000000000005</v>
       </c>
@@ -3936,9 +3780,8 @@
       <c r="M155" s="4"/>
       <c r="N155" s="4"/>
       <c r="O155" s="4"/>
-      <c r="P155" s="4"/>
-    </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="156" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A156" s="1">
         <v>77.010000000000005</v>
       </c>
@@ -3958,9 +3801,8 @@
       <c r="M156" s="4"/>
       <c r="N156" s="4"/>
       <c r="O156" s="4"/>
-      <c r="P156" s="4"/>
-    </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="157" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A157" s="1">
         <v>77.510000000000005</v>
       </c>
@@ -3980,9 +3822,8 @@
       <c r="M157" s="4"/>
       <c r="N157" s="4"/>
       <c r="O157" s="4"/>
-      <c r="P157" s="4"/>
-    </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="158" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A158" s="1">
         <v>78.010000000000005</v>
       </c>
@@ -4002,9 +3843,8 @@
       <c r="M158" s="4"/>
       <c r="N158" s="4"/>
       <c r="O158" s="4"/>
-      <c r="P158" s="4"/>
-    </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="159" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A159" s="1">
         <v>78.510000000000005</v>
       </c>
@@ -4024,9 +3864,8 @@
       <c r="M159" s="4"/>
       <c r="N159" s="4"/>
       <c r="O159" s="4"/>
-      <c r="P159" s="4"/>
-    </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="160" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A160" s="1">
         <v>79.010000000000005</v>
       </c>
@@ -4046,9 +3885,8 @@
       <c r="M160" s="4"/>
       <c r="N160" s="4"/>
       <c r="O160" s="4"/>
-      <c r="P160" s="4"/>
-    </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="161" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A161" s="1">
         <v>79.510000000000005</v>
       </c>
@@ -4068,9 +3906,8 @@
       <c r="M161" s="4"/>
       <c r="N161" s="4"/>
       <c r="O161" s="4"/>
-      <c r="P161" s="4"/>
-    </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="162" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A162" s="1">
         <v>80.010000000000005</v>
       </c>
@@ -4090,9 +3927,8 @@
       <c r="M162" s="4"/>
       <c r="N162" s="4"/>
       <c r="O162" s="4"/>
-      <c r="P162" s="4"/>
-    </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="163" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A163" s="1">
         <v>80.510000000000005</v>
       </c>
@@ -4112,9 +3948,8 @@
       <c r="M163" s="4"/>
       <c r="N163" s="4"/>
       <c r="O163" s="4"/>
-      <c r="P163" s="4"/>
-    </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="164" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A164" s="1">
         <v>81.010000000000005</v>
       </c>
@@ -4134,9 +3969,8 @@
       <c r="M164" s="4"/>
       <c r="N164" s="4"/>
       <c r="O164" s="4"/>
-      <c r="P164" s="4"/>
-    </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="165" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A165" s="1">
         <v>81.510000000000005</v>
       </c>
@@ -4156,9 +3990,8 @@
       <c r="M165" s="4"/>
       <c r="N165" s="4"/>
       <c r="O165" s="4"/>
-      <c r="P165" s="4"/>
-    </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="166" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A166" s="1">
         <v>82.01</v>
       </c>
@@ -4178,9 +4011,8 @@
       <c r="M166" s="4"/>
       <c r="N166" s="4"/>
       <c r="O166" s="4"/>
-      <c r="P166" s="4"/>
-    </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="167" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A167" s="1">
         <v>82.51</v>
       </c>
@@ -4200,9 +4032,8 @@
       <c r="M167" s="4"/>
       <c r="N167" s="4"/>
       <c r="O167" s="4"/>
-      <c r="P167" s="4"/>
-    </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="168" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A168" s="1">
         <v>83.01</v>
       </c>
@@ -4222,9 +4053,8 @@
       <c r="M168" s="4"/>
       <c r="N168" s="4"/>
       <c r="O168" s="4"/>
-      <c r="P168" s="4"/>
-    </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="169" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A169" s="1">
         <v>83.51</v>
       </c>
@@ -4244,9 +4074,8 @@
       <c r="M169" s="4"/>
       <c r="N169" s="4"/>
       <c r="O169" s="4"/>
-      <c r="P169" s="4"/>
-    </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="170" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A170" s="1">
         <v>84.01</v>
       </c>
@@ -4266,9 +4095,8 @@
       <c r="M170" s="4"/>
       <c r="N170" s="4"/>
       <c r="O170" s="4"/>
-      <c r="P170" s="4"/>
-    </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="171" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A171" s="1">
         <v>84.51</v>
       </c>
@@ -4288,9 +4116,8 @@
       <c r="M171" s="4"/>
       <c r="N171" s="4"/>
       <c r="O171" s="4"/>
-      <c r="P171" s="4"/>
-    </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="172" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A172" s="1">
         <v>85.01</v>
       </c>
@@ -4310,9 +4137,8 @@
       <c r="M172" s="4"/>
       <c r="N172" s="4"/>
       <c r="O172" s="4"/>
-      <c r="P172" s="4"/>
-    </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="173" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A173" s="1">
         <v>85.51</v>
       </c>
@@ -4332,9 +4158,8 @@
       <c r="M173" s="4"/>
       <c r="N173" s="4"/>
       <c r="O173" s="4"/>
-      <c r="P173" s="4"/>
-    </row>
-    <row r="174" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="174" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A174" s="1">
         <v>86.01</v>
       </c>
@@ -4354,9 +4179,8 @@
       <c r="M174" s="4"/>
       <c r="N174" s="4"/>
       <c r="O174" s="4"/>
-      <c r="P174" s="4"/>
-    </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="175" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A175" s="1">
         <v>86.51</v>
       </c>
@@ -4376,9 +4200,8 @@
       <c r="M175" s="4"/>
       <c r="N175" s="4"/>
       <c r="O175" s="4"/>
-      <c r="P175" s="4"/>
-    </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="176" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A176" s="1">
         <v>87.01</v>
       </c>
@@ -4398,9 +4221,8 @@
       <c r="M176" s="4"/>
       <c r="N176" s="4"/>
       <c r="O176" s="4"/>
-      <c r="P176" s="4"/>
-    </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="177" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A177" s="1">
         <v>87.51</v>
       </c>
@@ -4420,9 +4242,8 @@
       <c r="M177" s="4"/>
       <c r="N177" s="4"/>
       <c r="O177" s="4"/>
-      <c r="P177" s="4"/>
-    </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="178" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A178" s="1">
         <v>88.01</v>
       </c>
@@ -4442,9 +4263,8 @@
       <c r="M178" s="4"/>
       <c r="N178" s="4"/>
       <c r="O178" s="4"/>
-      <c r="P178" s="4"/>
-    </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="179" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A179" s="1">
         <v>88.51</v>
       </c>
@@ -4464,9 +4284,8 @@
       <c r="M179" s="4"/>
       <c r="N179" s="4"/>
       <c r="O179" s="4"/>
-      <c r="P179" s="4"/>
-    </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="180" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A180" s="1">
         <v>89.01</v>
       </c>
@@ -4486,9 +4305,8 @@
       <c r="M180" s="4"/>
       <c r="N180" s="4"/>
       <c r="O180" s="4"/>
-      <c r="P180" s="4"/>
-    </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="181" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A181" s="1">
         <v>89.51</v>
       </c>
@@ -4508,9 +4326,8 @@
       <c r="M181" s="4"/>
       <c r="N181" s="4"/>
       <c r="O181" s="4"/>
-      <c r="P181" s="4"/>
-    </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="182" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A182" s="1">
         <v>90.01</v>
       </c>
@@ -4530,9 +4347,8 @@
       <c r="M182" s="4"/>
       <c r="N182" s="4"/>
       <c r="O182" s="4"/>
-      <c r="P182" s="4"/>
-    </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="183" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A183" s="1">
         <v>90.51</v>
       </c>
@@ -4552,9 +4368,8 @@
       <c r="M183" s="4"/>
       <c r="N183" s="4"/>
       <c r="O183" s="4"/>
-      <c r="P183" s="4"/>
-    </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="184" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A184" s="1">
         <v>91.01</v>
       </c>
@@ -4574,9 +4389,8 @@
       <c r="M184" s="4"/>
       <c r="N184" s="4"/>
       <c r="O184" s="4"/>
-      <c r="P184" s="4"/>
-    </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="185" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A185" s="1">
         <v>91.51</v>
       </c>
@@ -4596,9 +4410,8 @@
       <c r="M185" s="4"/>
       <c r="N185" s="4"/>
       <c r="O185" s="4"/>
-      <c r="P185" s="4"/>
-    </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="186" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A186" s="1">
         <v>92.01</v>
       </c>
@@ -4618,9 +4431,8 @@
       <c r="M186" s="4"/>
       <c r="N186" s="4"/>
       <c r="O186" s="4"/>
-      <c r="P186" s="4"/>
-    </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="187" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A187" s="1">
         <v>92.51</v>
       </c>
@@ -4640,9 +4452,8 @@
       <c r="M187" s="4"/>
       <c r="N187" s="4"/>
       <c r="O187" s="4"/>
-      <c r="P187" s="4"/>
-    </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="188" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A188" s="1">
         <v>93.01</v>
       </c>
@@ -4662,9 +4473,8 @@
       <c r="M188" s="4"/>
       <c r="N188" s="4"/>
       <c r="O188" s="4"/>
-      <c r="P188" s="4"/>
-    </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="189" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A189" s="1">
         <v>93.51</v>
       </c>
@@ -4684,9 +4494,8 @@
       <c r="M189" s="4"/>
       <c r="N189" s="4"/>
       <c r="O189" s="4"/>
-      <c r="P189" s="4"/>
-    </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="190" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A190" s="1">
         <v>94.01</v>
       </c>
@@ -4706,9 +4515,8 @@
       <c r="M190" s="4"/>
       <c r="N190" s="4"/>
       <c r="O190" s="4"/>
-      <c r="P190" s="4"/>
-    </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="191" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A191" s="1">
         <v>94.51</v>
       </c>
@@ -4728,9 +4536,8 @@
       <c r="M191" s="4"/>
       <c r="N191" s="4"/>
       <c r="O191" s="4"/>
-      <c r="P191" s="4"/>
-    </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="192" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A192" s="1">
         <v>95.01</v>
       </c>
@@ -4750,9 +4557,8 @@
       <c r="M192" s="4"/>
       <c r="N192" s="4"/>
       <c r="O192" s="4"/>
-      <c r="P192" s="4"/>
-    </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="193" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A193" s="1">
         <v>95.51</v>
       </c>
@@ -4772,9 +4578,8 @@
       <c r="M193" s="4"/>
       <c r="N193" s="4"/>
       <c r="O193" s="4"/>
-      <c r="P193" s="4"/>
-    </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="194" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A194" s="1">
         <v>96.01</v>
       </c>
@@ -4794,9 +4599,8 @@
       <c r="M194" s="4"/>
       <c r="N194" s="4"/>
       <c r="O194" s="4"/>
-      <c r="P194" s="4"/>
-    </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="195" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A195" s="1">
         <v>96.51</v>
       </c>
@@ -4816,9 +4620,8 @@
       <c r="M195" s="4"/>
       <c r="N195" s="4"/>
       <c r="O195" s="4"/>
-      <c r="P195" s="4"/>
-    </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="196" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A196" s="1">
         <v>97.01</v>
       </c>
@@ -4838,9 +4641,8 @@
       <c r="M196" s="4"/>
       <c r="N196" s="4"/>
       <c r="O196" s="4"/>
-      <c r="P196" s="4"/>
-    </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="197" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A197" s="1">
         <v>97.51</v>
       </c>
@@ -4860,9 +4662,8 @@
       <c r="M197" s="4"/>
       <c r="N197" s="4"/>
       <c r="O197" s="4"/>
-      <c r="P197" s="4"/>
-    </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="198" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A198" s="1">
         <v>98.01</v>
       </c>
@@ -4882,9 +4683,8 @@
       <c r="M198" s="4"/>
       <c r="N198" s="4"/>
       <c r="O198" s="4"/>
-      <c r="P198" s="4"/>
-    </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="199" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A199" s="1">
         <v>98.51</v>
       </c>
@@ -4904,9 +4704,8 @@
       <c r="M199" s="4"/>
       <c r="N199" s="4"/>
       <c r="O199" s="4"/>
-      <c r="P199" s="4"/>
-    </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="200" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A200" s="1">
         <v>99.01</v>
       </c>
@@ -4926,9 +4725,8 @@
       <c r="M200" s="4"/>
       <c r="N200" s="4"/>
       <c r="O200" s="4"/>
-      <c r="P200" s="4"/>
-    </row>
-    <row r="201" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="201" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A201" s="1">
         <v>99.51</v>
       </c>
@@ -4948,9 +4746,8 @@
       <c r="M201" s="4"/>
       <c r="N201" s="4"/>
       <c r="O201" s="4"/>
-      <c r="P201" s="4"/>
-    </row>
-    <row r="202" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="202" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A202" s="1">
         <v>100.01</v>
       </c>
@@ -4970,9 +4767,8 @@
       <c r="M202" s="4"/>
       <c r="N202" s="4"/>
       <c r="O202" s="4"/>
-      <c r="P202" s="4"/>
-    </row>
-    <row r="203" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="203" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A203" s="1">
         <v>100.51</v>
       </c>
@@ -4992,9 +4788,8 @@
       <c r="M203" s="4"/>
       <c r="N203" s="4"/>
       <c r="O203" s="4"/>
-      <c r="P203" s="4"/>
-    </row>
-    <row r="204" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="204" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A204" s="1">
         <v>101.01</v>
       </c>
@@ -5014,9 +4809,8 @@
       <c r="M204" s="4"/>
       <c r="N204" s="4"/>
       <c r="O204" s="4"/>
-      <c r="P204" s="4"/>
-    </row>
-    <row r="205" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="205" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A205" s="1">
         <v>101.51</v>
       </c>
@@ -5036,9 +4830,8 @@
       <c r="M205" s="4"/>
       <c r="N205" s="4"/>
       <c r="O205" s="4"/>
-      <c r="P205" s="4"/>
-    </row>
-    <row r="206" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="206" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A206" s="1">
         <v>102.01</v>
       </c>
@@ -5058,9 +4851,8 @@
       <c r="M206" s="4"/>
       <c r="N206" s="4"/>
       <c r="O206" s="4"/>
-      <c r="P206" s="4"/>
-    </row>
-    <row r="207" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="207" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A207" s="1">
         <v>102.51</v>
       </c>
@@ -5080,9 +4872,8 @@
       <c r="M207" s="4"/>
       <c r="N207" s="4"/>
       <c r="O207" s="4"/>
-      <c r="P207" s="4"/>
-    </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="208" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A208" s="1">
         <v>103.01</v>
       </c>
@@ -5102,9 +4893,8 @@
       <c r="M208" s="4"/>
       <c r="N208" s="4"/>
       <c r="O208" s="4"/>
-      <c r="P208" s="4"/>
-    </row>
-    <row r="209" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="209" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A209" s="1">
         <v>103.51</v>
       </c>
@@ -5124,9 +4914,8 @@
       <c r="M209" s="4"/>
       <c r="N209" s="4"/>
       <c r="O209" s="4"/>
-      <c r="P209" s="4"/>
-    </row>
-    <row r="210" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="210" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A210" s="1">
         <v>104.01</v>
       </c>
@@ -5146,9 +4935,8 @@
       <c r="M210" s="4"/>
       <c r="N210" s="4"/>
       <c r="O210" s="4"/>
-      <c r="P210" s="4"/>
-    </row>
-    <row r="211" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="211" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A211" s="1">
         <v>104.51</v>
       </c>
@@ -5168,9 +4956,8 @@
       <c r="M211" s="4"/>
       <c r="N211" s="4"/>
       <c r="O211" s="4"/>
-      <c r="P211" s="4"/>
-    </row>
-    <row r="212" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="212" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A212" s="1">
         <v>105.01</v>
       </c>
@@ -5190,9 +4977,8 @@
       <c r="M212" s="4"/>
       <c r="N212" s="4"/>
       <c r="O212" s="4"/>
-      <c r="P212" s="4"/>
-    </row>
-    <row r="213" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="213" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A213" s="1">
         <v>105.51</v>
       </c>
@@ -5212,9 +4998,8 @@
       <c r="M213" s="4"/>
       <c r="N213" s="4"/>
       <c r="O213" s="4"/>
-      <c r="P213" s="4"/>
-    </row>
-    <row r="214" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="214" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A214" s="1">
         <v>106.01</v>
       </c>
@@ -5234,9 +5019,8 @@
       <c r="M214" s="4"/>
       <c r="N214" s="4"/>
       <c r="O214" s="4"/>
-      <c r="P214" s="4"/>
-    </row>
-    <row r="215" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="215" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A215" s="1">
         <v>106.51</v>
       </c>
@@ -5256,9 +5040,8 @@
       <c r="M215" s="4"/>
       <c r="N215" s="4"/>
       <c r="O215" s="4"/>
-      <c r="P215" s="4"/>
-    </row>
-    <row r="216" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="216" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A216" s="1">
         <v>107.01</v>
       </c>
@@ -5278,9 +5061,8 @@
       <c r="M216" s="4"/>
       <c r="N216" s="4"/>
       <c r="O216" s="4"/>
-      <c r="P216" s="4"/>
-    </row>
-    <row r="217" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="217" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A217" s="1">
         <v>107.51</v>
       </c>
@@ -5300,9 +5082,8 @@
       <c r="M217" s="4"/>
       <c r="N217" s="4"/>
       <c r="O217" s="4"/>
-      <c r="P217" s="4"/>
-    </row>
-    <row r="218" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="218" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A218" s="1">
         <v>108.01</v>
       </c>
@@ -5322,9 +5103,8 @@
       <c r="M218" s="4"/>
       <c r="N218" s="4"/>
       <c r="O218" s="4"/>
-      <c r="P218" s="4"/>
-    </row>
-    <row r="219" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="219" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A219" s="1">
         <v>108.51</v>
       </c>
@@ -5344,9 +5124,8 @@
       <c r="M219" s="4"/>
       <c r="N219" s="4"/>
       <c r="O219" s="4"/>
-      <c r="P219" s="4"/>
-    </row>
-    <row r="220" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="220" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A220" s="1">
         <v>109.01</v>
       </c>
@@ -5366,9 +5145,8 @@
       <c r="M220" s="4"/>
       <c r="N220" s="4"/>
       <c r="O220" s="4"/>
-      <c r="P220" s="4"/>
-    </row>
-    <row r="221" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="221" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A221" s="1">
         <v>109.51</v>
       </c>
@@ -5388,9 +5166,8 @@
       <c r="M221" s="4"/>
       <c r="N221" s="4"/>
       <c r="O221" s="4"/>
-      <c r="P221" s="4"/>
-    </row>
-    <row r="222" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="222" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A222" s="1">
         <v>110.01</v>
       </c>
@@ -5410,9 +5187,8 @@
       <c r="M222" s="4"/>
       <c r="N222" s="4"/>
       <c r="O222" s="4"/>
-      <c r="P222" s="4"/>
-    </row>
-    <row r="223" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="223" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A223" s="1">
         <v>110.51</v>
       </c>
@@ -5432,9 +5208,8 @@
       <c r="M223" s="4"/>
       <c r="N223" s="4"/>
       <c r="O223" s="4"/>
-      <c r="P223" s="4"/>
-    </row>
-    <row r="224" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="224" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A224" s="1">
         <v>111.01</v>
       </c>
@@ -5454,9 +5229,8 @@
       <c r="M224" s="4"/>
       <c r="N224" s="4"/>
       <c r="O224" s="4"/>
-      <c r="P224" s="4"/>
-    </row>
-    <row r="225" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="225" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A225" s="1">
         <v>111.51</v>
       </c>
@@ -5476,9 +5250,8 @@
       <c r="M225" s="4"/>
       <c r="N225" s="4"/>
       <c r="O225" s="4"/>
-      <c r="P225" s="4"/>
-    </row>
-    <row r="226" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="226" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A226" s="1">
         <v>112.01</v>
       </c>
@@ -5498,9 +5271,8 @@
       <c r="M226" s="4"/>
       <c r="N226" s="4"/>
       <c r="O226" s="4"/>
-      <c r="P226" s="4"/>
-    </row>
-    <row r="227" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="227" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A227" s="1">
         <v>112.51</v>
       </c>
@@ -5520,9 +5292,8 @@
       <c r="M227" s="4"/>
       <c r="N227" s="4"/>
       <c r="O227" s="4"/>
-      <c r="P227" s="4"/>
-    </row>
-    <row r="228" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="228" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A228" s="1">
         <v>113.01</v>
       </c>
@@ -5542,9 +5313,8 @@
       <c r="M228" s="4"/>
       <c r="N228" s="4"/>
       <c r="O228" s="4"/>
-      <c r="P228" s="4"/>
-    </row>
-    <row r="229" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="229" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A229" s="1">
         <v>113.51</v>
       </c>
@@ -5564,9 +5334,8 @@
       <c r="M229" s="4"/>
       <c r="N229" s="4"/>
       <c r="O229" s="4"/>
-      <c r="P229" s="4"/>
-    </row>
-    <row r="230" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="230" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A230" s="1">
         <v>114.01</v>
       </c>
@@ -5586,9 +5355,8 @@
       <c r="M230" s="4"/>
       <c r="N230" s="4"/>
       <c r="O230" s="4"/>
-      <c r="P230" s="4"/>
-    </row>
-    <row r="231" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="231" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A231" s="1">
         <v>114.51</v>
       </c>
@@ -5608,9 +5376,8 @@
       <c r="M231" s="4"/>
       <c r="N231" s="4"/>
       <c r="O231" s="4"/>
-      <c r="P231" s="4"/>
-    </row>
-    <row r="232" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="232" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A232" s="1">
         <v>115.01</v>
       </c>
@@ -5630,9 +5397,8 @@
       <c r="M232" s="4"/>
       <c r="N232" s="4"/>
       <c r="O232" s="4"/>
-      <c r="P232" s="4"/>
-    </row>
-    <row r="233" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="233" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A233" s="1">
         <v>115.51</v>
       </c>
@@ -5652,9 +5418,8 @@
       <c r="M233" s="4"/>
       <c r="N233" s="4"/>
       <c r="O233" s="4"/>
-      <c r="P233" s="4"/>
-    </row>
-    <row r="234" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="234" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A234" s="1">
         <v>116.01</v>
       </c>
@@ -5674,9 +5439,8 @@
       <c r="M234" s="4"/>
       <c r="N234" s="4"/>
       <c r="O234" s="4"/>
-      <c r="P234" s="4"/>
-    </row>
-    <row r="235" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="235" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A235" s="1">
         <v>116.51</v>
       </c>
@@ -5696,9 +5460,8 @@
       <c r="M235" s="4"/>
       <c r="N235" s="4"/>
       <c r="O235" s="4"/>
-      <c r="P235" s="4"/>
-    </row>
-    <row r="236" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="236" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A236" s="1">
         <v>117.01</v>
       </c>
@@ -5718,9 +5481,8 @@
       <c r="M236" s="4"/>
       <c r="N236" s="4"/>
       <c r="O236" s="4"/>
-      <c r="P236" s="4"/>
-    </row>
-    <row r="237" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="237" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A237" s="1">
         <v>117.51</v>
       </c>
@@ -5740,9 +5502,8 @@
       <c r="M237" s="4"/>
       <c r="N237" s="4"/>
       <c r="O237" s="4"/>
-      <c r="P237" s="4"/>
-    </row>
-    <row r="238" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="238" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A238" s="1">
         <v>118.01</v>
       </c>
@@ -5762,9 +5523,8 @@
       <c r="M238" s="4"/>
       <c r="N238" s="4"/>
       <c r="O238" s="4"/>
-      <c r="P238" s="4"/>
-    </row>
-    <row r="239" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="239" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A239" s="1">
         <v>118.51</v>
       </c>
@@ -5784,9 +5544,8 @@
       <c r="M239" s="4"/>
       <c r="N239" s="4"/>
       <c r="O239" s="4"/>
-      <c r="P239" s="4"/>
-    </row>
-    <row r="240" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="240" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A240" s="1">
         <v>119.01</v>
       </c>
@@ -5806,9 +5565,8 @@
       <c r="M240" s="4"/>
       <c r="N240" s="4"/>
       <c r="O240" s="4"/>
-      <c r="P240" s="4"/>
-    </row>
-    <row r="241" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="241" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A241" s="1">
         <v>119.51</v>
       </c>
@@ -5828,9 +5586,8 @@
       <c r="M241" s="4"/>
       <c r="N241" s="4"/>
       <c r="O241" s="4"/>
-      <c r="P241" s="4"/>
-    </row>
-    <row r="242" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="242" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A242" s="1">
         <v>120.01</v>
       </c>
@@ -5850,9 +5607,8 @@
       <c r="M242" s="4"/>
       <c r="N242" s="4"/>
       <c r="O242" s="4"/>
-      <c r="P242" s="4"/>
-    </row>
-    <row r="243" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="243" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A243" s="1">
         <v>120.51</v>
       </c>
@@ -5872,9 +5628,8 @@
       <c r="M243" s="4"/>
       <c r="N243" s="4"/>
       <c r="O243" s="4"/>
-      <c r="P243" s="4"/>
-    </row>
-    <row r="244" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="244" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A244" s="1">
         <v>121.01</v>
       </c>
@@ -5894,9 +5649,8 @@
       <c r="M244" s="4"/>
       <c r="N244" s="4"/>
       <c r="O244" s="4"/>
-      <c r="P244" s="4"/>
-    </row>
-    <row r="245" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="245" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A245" s="1">
         <v>121.51</v>
       </c>
@@ -5916,9 +5670,8 @@
       <c r="M245" s="4"/>
       <c r="N245" s="4"/>
       <c r="O245" s="4"/>
-      <c r="P245" s="4"/>
-    </row>
-    <row r="246" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="246" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A246" s="1">
         <v>122.01</v>
       </c>
@@ -5938,9 +5691,8 @@
       <c r="M246" s="4"/>
       <c r="N246" s="4"/>
       <c r="O246" s="4"/>
-      <c r="P246" s="4"/>
-    </row>
-    <row r="247" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="247" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A247" s="1">
         <v>122.51</v>
       </c>
@@ -5960,9 +5712,8 @@
       <c r="M247" s="4"/>
       <c r="N247" s="4"/>
       <c r="O247" s="4"/>
-      <c r="P247" s="4"/>
-    </row>
-    <row r="248" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="248" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A248" s="1">
         <v>123.01</v>
       </c>
@@ -5982,9 +5733,8 @@
       <c r="M248" s="4"/>
       <c r="N248" s="4"/>
       <c r="O248" s="4"/>
-      <c r="P248" s="4"/>
-    </row>
-    <row r="249" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="249" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A249" s="1">
         <v>123.51</v>
       </c>
@@ -6004,9 +5754,8 @@
       <c r="M249" s="4"/>
       <c r="N249" s="4"/>
       <c r="O249" s="4"/>
-      <c r="P249" s="4"/>
-    </row>
-    <row r="250" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="250" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A250" s="1">
         <v>124.01</v>
       </c>
@@ -6026,9 +5775,8 @@
       <c r="M250" s="4"/>
       <c r="N250" s="4"/>
       <c r="O250" s="4"/>
-      <c r="P250" s="4"/>
-    </row>
-    <row r="251" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="251" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A251" s="1">
         <v>124.51</v>
       </c>
@@ -6048,9 +5796,8 @@
       <c r="M251" s="4"/>
       <c r="N251" s="4"/>
       <c r="O251" s="4"/>
-      <c r="P251" s="4"/>
-    </row>
-    <row r="252" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="252" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A252" s="1">
         <v>125.01</v>
       </c>
@@ -6070,9 +5817,8 @@
       <c r="M252" s="4"/>
       <c r="N252" s="4"/>
       <c r="O252" s="4"/>
-      <c r="P252" s="4"/>
-    </row>
-    <row r="253" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="253" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A253" s="1">
         <v>125.51</v>
       </c>
@@ -6092,9 +5838,8 @@
       <c r="M253" s="4"/>
       <c r="N253" s="4"/>
       <c r="O253" s="4"/>
-      <c r="P253" s="4"/>
-    </row>
-    <row r="254" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="254" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A254" s="1">
         <v>126.01</v>
       </c>
@@ -6114,9 +5859,8 @@
       <c r="M254" s="4"/>
       <c r="N254" s="4"/>
       <c r="O254" s="4"/>
-      <c r="P254" s="4"/>
-    </row>
-    <row r="255" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="255" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A255" s="1">
         <v>126.51</v>
       </c>
@@ -6136,9 +5880,8 @@
       <c r="M255" s="4"/>
       <c r="N255" s="4"/>
       <c r="O255" s="4"/>
-      <c r="P255" s="4"/>
-    </row>
-    <row r="256" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="256" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A256" s="1">
         <v>127.01</v>
       </c>
@@ -6158,9 +5901,8 @@
       <c r="M256" s="4"/>
       <c r="N256" s="4"/>
       <c r="O256" s="4"/>
-      <c r="P256" s="4"/>
-    </row>
-    <row r="257" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="257" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A257" s="1">
         <v>127.51</v>
       </c>
@@ -6180,9 +5922,8 @@
       <c r="M257" s="4"/>
       <c r="N257" s="4"/>
       <c r="O257" s="4"/>
-      <c r="P257" s="4"/>
-    </row>
-    <row r="258" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="258" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A258" s="1">
         <v>128.01</v>
       </c>
@@ -6202,9 +5943,8 @@
       <c r="M258" s="4"/>
       <c r="N258" s="4"/>
       <c r="O258" s="4"/>
-      <c r="P258" s="4"/>
-    </row>
-    <row r="259" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="259" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A259" s="1">
         <v>128.51</v>
       </c>
@@ -6224,9 +5964,8 @@
       <c r="M259" s="4"/>
       <c r="N259" s="4"/>
       <c r="O259" s="4"/>
-      <c r="P259" s="4"/>
-    </row>
-    <row r="260" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="260" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A260" s="1">
         <v>129.01</v>
       </c>
@@ -6246,9 +5985,8 @@
       <c r="M260" s="4"/>
       <c r="N260" s="4"/>
       <c r="O260" s="4"/>
-      <c r="P260" s="4"/>
-    </row>
-    <row r="261" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="261" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A261" s="1">
         <v>129.51</v>
       </c>
@@ -6268,9 +6006,8 @@
       <c r="M261" s="4"/>
       <c r="N261" s="4"/>
       <c r="O261" s="4"/>
-      <c r="P261" s="4"/>
-    </row>
-    <row r="262" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="262" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A262" s="1">
         <v>130.01</v>
       </c>
@@ -6290,9 +6027,8 @@
       <c r="M262" s="4"/>
       <c r="N262" s="4"/>
       <c r="O262" s="4"/>
-      <c r="P262" s="4"/>
-    </row>
-    <row r="263" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="263" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A263" s="1">
         <v>130.51</v>
       </c>
@@ -6312,9 +6048,8 @@
       <c r="M263" s="4"/>
       <c r="N263" s="4"/>
       <c r="O263" s="4"/>
-      <c r="P263" s="4"/>
-    </row>
-    <row r="264" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="264" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A264" s="1">
         <v>131.01</v>
       </c>
@@ -6334,9 +6069,8 @@
       <c r="M264" s="4"/>
       <c r="N264" s="4"/>
       <c r="O264" s="4"/>
-      <c r="P264" s="4"/>
-    </row>
-    <row r="265" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="265" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A265" s="1">
         <v>131.51</v>
       </c>
@@ -6356,9 +6090,8 @@
       <c r="M265" s="4"/>
       <c r="N265" s="4"/>
       <c r="O265" s="4"/>
-      <c r="P265" s="4"/>
-    </row>
-    <row r="266" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="266" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A266" s="1">
         <v>132.01</v>
       </c>
@@ -6378,9 +6111,8 @@
       <c r="M266" s="4"/>
       <c r="N266" s="4"/>
       <c r="O266" s="4"/>
-      <c r="P266" s="4"/>
-    </row>
-    <row r="267" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="267" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A267" s="1">
         <v>132.51</v>
       </c>
@@ -6400,9 +6132,8 @@
       <c r="M267" s="4"/>
       <c r="N267" s="4"/>
       <c r="O267" s="4"/>
-      <c r="P267" s="4"/>
-    </row>
-    <row r="268" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="268" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A268" s="1">
         <v>133.01</v>
       </c>
@@ -6422,9 +6153,8 @@
       <c r="M268" s="4"/>
       <c r="N268" s="4"/>
       <c r="O268" s="4"/>
-      <c r="P268" s="4"/>
-    </row>
-    <row r="269" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="269" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A269" s="1">
         <v>133.51</v>
       </c>
@@ -6444,9 +6174,8 @@
       <c r="M269" s="4"/>
       <c r="N269" s="4"/>
       <c r="O269" s="4"/>
-      <c r="P269" s="4"/>
-    </row>
-    <row r="270" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="270" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A270" s="1">
         <v>134.01</v>
       </c>
@@ -6466,9 +6195,8 @@
       <c r="M270" s="4"/>
       <c r="N270" s="4"/>
       <c r="O270" s="4"/>
-      <c r="P270" s="4"/>
-    </row>
-    <row r="271" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="271" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A271" s="1">
         <v>134.51</v>
       </c>
@@ -6488,9 +6216,8 @@
       <c r="M271" s="4"/>
       <c r="N271" s="4"/>
       <c r="O271" s="4"/>
-      <c r="P271" s="4"/>
-    </row>
-    <row r="272" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="272" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A272" s="1">
         <v>135.01</v>
       </c>
@@ -6510,9 +6237,8 @@
       <c r="M272" s="4"/>
       <c r="N272" s="4"/>
       <c r="O272" s="4"/>
-      <c r="P272" s="4"/>
-    </row>
-    <row r="273" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="273" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A273" s="1">
         <v>135.51</v>
       </c>
@@ -6532,9 +6258,8 @@
       <c r="M273" s="4"/>
       <c r="N273" s="4"/>
       <c r="O273" s="4"/>
-      <c r="P273" s="4"/>
-    </row>
-    <row r="274" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="274" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A274" s="1">
         <v>136.01</v>
       </c>
@@ -6554,9 +6279,8 @@
       <c r="M274" s="4"/>
       <c r="N274" s="4"/>
       <c r="O274" s="4"/>
-      <c r="P274" s="4"/>
-    </row>
-    <row r="275" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="275" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A275" s="1">
         <v>136.51</v>
       </c>
@@ -6576,9 +6300,8 @@
       <c r="M275" s="4"/>
       <c r="N275" s="4"/>
       <c r="O275" s="4"/>
-      <c r="P275" s="4"/>
-    </row>
-    <row r="276" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="276" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A276" s="1">
         <v>137.01</v>
       </c>
@@ -6598,9 +6321,8 @@
       <c r="M276" s="4"/>
       <c r="N276" s="4"/>
       <c r="O276" s="4"/>
-      <c r="P276" s="4"/>
-    </row>
-    <row r="277" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="277" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A277" s="1">
         <v>137.51</v>
       </c>
@@ -6620,9 +6342,8 @@
       <c r="M277" s="4"/>
       <c r="N277" s="4"/>
       <c r="O277" s="4"/>
-      <c r="P277" s="4"/>
-    </row>
-    <row r="278" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="278" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A278" s="1">
         <v>138.01</v>
       </c>
@@ -6642,9 +6363,8 @@
       <c r="M278" s="4"/>
       <c r="N278" s="4"/>
       <c r="O278" s="4"/>
-      <c r="P278" s="4"/>
-    </row>
-    <row r="279" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="279" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A279" s="1">
         <v>138.51</v>
       </c>
@@ -6664,9 +6384,8 @@
       <c r="M279" s="4"/>
       <c r="N279" s="4"/>
       <c r="O279" s="4"/>
-      <c r="P279" s="4"/>
-    </row>
-    <row r="280" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="280" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A280" s="1">
         <v>139.01</v>
       </c>
@@ -6686,9 +6405,8 @@
       <c r="M280" s="4"/>
       <c r="N280" s="4"/>
       <c r="O280" s="4"/>
-      <c r="P280" s="4"/>
-    </row>
-    <row r="281" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="281" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A281" s="1">
         <v>139.51</v>
       </c>
@@ -6708,9 +6426,8 @@
       <c r="M281" s="4"/>
       <c r="N281" s="4"/>
       <c r="O281" s="4"/>
-      <c r="P281" s="4"/>
-    </row>
-    <row r="282" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="282" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A282" s="1">
         <v>140.01</v>
       </c>
@@ -6730,9 +6447,8 @@
       <c r="M282" s="4"/>
       <c r="N282" s="4"/>
       <c r="O282" s="4"/>
-      <c r="P282" s="4"/>
-    </row>
-    <row r="283" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="283" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A283" s="1">
         <v>140.51</v>
       </c>
@@ -6752,9 +6468,8 @@
       <c r="M283" s="4"/>
       <c r="N283" s="4"/>
       <c r="O283" s="4"/>
-      <c r="P283" s="4"/>
-    </row>
-    <row r="284" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="284" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A284" s="1">
         <v>141.01</v>
       </c>
@@ -6774,9 +6489,8 @@
       <c r="M284" s="4"/>
       <c r="N284" s="4"/>
       <c r="O284" s="4"/>
-      <c r="P284" s="4"/>
-    </row>
-    <row r="285" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="285" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A285" s="1">
         <v>141.51</v>
       </c>
@@ -6796,9 +6510,8 @@
       <c r="M285" s="4"/>
       <c r="N285" s="4"/>
       <c r="O285" s="4"/>
-      <c r="P285" s="4"/>
-    </row>
-    <row r="286" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="286" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A286" s="1">
         <v>142.01</v>
       </c>
@@ -6818,9 +6531,8 @@
       <c r="M286" s="4"/>
       <c r="N286" s="4"/>
       <c r="O286" s="4"/>
-      <c r="P286" s="4"/>
-    </row>
-    <row r="287" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="287" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A287" s="1">
         <v>142.51</v>
       </c>
@@ -6840,9 +6552,8 @@
       <c r="M287" s="4"/>
       <c r="N287" s="4"/>
       <c r="O287" s="4"/>
-      <c r="P287" s="4"/>
-    </row>
-    <row r="288" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="288" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A288" s="1">
         <v>143.01</v>
       </c>
@@ -6862,9 +6573,8 @@
       <c r="M288" s="4"/>
       <c r="N288" s="4"/>
       <c r="O288" s="4"/>
-      <c r="P288" s="4"/>
-    </row>
-    <row r="289" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="289" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A289" s="1">
         <v>143.51</v>
       </c>
@@ -6884,9 +6594,8 @@
       <c r="M289" s="4"/>
       <c r="N289" s="4"/>
       <c r="O289" s="4"/>
-      <c r="P289" s="4"/>
-    </row>
-    <row r="290" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="290" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A290" s="1">
         <v>144.01</v>
       </c>
@@ -6906,9 +6615,8 @@
       <c r="M290" s="4"/>
       <c r="N290" s="4"/>
       <c r="O290" s="4"/>
-      <c r="P290" s="4"/>
-    </row>
-    <row r="291" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="291" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A291" s="1">
         <v>144.51</v>
       </c>
@@ -6928,9 +6636,8 @@
       <c r="M291" s="4"/>
       <c r="N291" s="4"/>
       <c r="O291" s="4"/>
-      <c r="P291" s="4"/>
-    </row>
-    <row r="292" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="292" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A292" s="1">
         <v>145.01</v>
       </c>
@@ -6950,9 +6657,8 @@
       <c r="M292" s="4"/>
       <c r="N292" s="4"/>
       <c r="O292" s="4"/>
-      <c r="P292" s="4"/>
-    </row>
-    <row r="293" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="293" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A293" s="1">
         <v>145.51</v>
       </c>
@@ -6972,9 +6678,8 @@
       <c r="M293" s="4"/>
       <c r="N293" s="4"/>
       <c r="O293" s="4"/>
-      <c r="P293" s="4"/>
-    </row>
-    <row r="294" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="294" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A294" s="1">
         <v>146.01</v>
       </c>
@@ -6994,9 +6699,8 @@
       <c r="M294" s="4"/>
       <c r="N294" s="4"/>
       <c r="O294" s="4"/>
-      <c r="P294" s="4"/>
-    </row>
-    <row r="295" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="295" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A295" s="1">
         <v>146.51</v>
       </c>
@@ -7016,9 +6720,8 @@
       <c r="M295" s="4"/>
       <c r="N295" s="4"/>
       <c r="O295" s="4"/>
-      <c r="P295" s="4"/>
-    </row>
-    <row r="296" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="296" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A296" s="1">
         <v>147.01</v>
       </c>
@@ -7038,9 +6741,8 @@
       <c r="M296" s="4"/>
       <c r="N296" s="4"/>
       <c r="O296" s="4"/>
-      <c r="P296" s="4"/>
-    </row>
-    <row r="297" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="297" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A297" s="1">
         <v>147.51</v>
       </c>
@@ -7060,9 +6762,8 @@
       <c r="M297" s="4"/>
       <c r="N297" s="4"/>
       <c r="O297" s="4"/>
-      <c r="P297" s="4"/>
-    </row>
-    <row r="298" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="298" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A298" s="1">
         <v>148.01</v>
       </c>
@@ -7082,9 +6783,8 @@
       <c r="M298" s="4"/>
       <c r="N298" s="4"/>
       <c r="O298" s="4"/>
-      <c r="P298" s="4"/>
-    </row>
-    <row r="299" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="299" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A299" s="1">
         <v>148.51</v>
       </c>
@@ -7104,9 +6804,8 @@
       <c r="M299" s="4"/>
       <c r="N299" s="4"/>
       <c r="O299" s="4"/>
-      <c r="P299" s="4"/>
-    </row>
-    <row r="300" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="300" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A300" s="1">
         <v>149.01</v>
       </c>
@@ -7126,9 +6825,8 @@
       <c r="M300" s="4"/>
       <c r="N300" s="4"/>
       <c r="O300" s="4"/>
-      <c r="P300" s="4"/>
-    </row>
-    <row r="301" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="301" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A301" s="1">
         <v>149.51</v>
       </c>
@@ -7148,9 +6846,8 @@
       <c r="M301" s="4"/>
       <c r="N301" s="4"/>
       <c r="O301" s="4"/>
-      <c r="P301" s="4"/>
-    </row>
-    <row r="302" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="302" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A302" s="1">
         <v>150.01</v>
       </c>
@@ -7170,9 +6867,8 @@
       <c r="M302" s="4"/>
       <c r="N302" s="4"/>
       <c r="O302" s="4"/>
-      <c r="P302" s="4"/>
-    </row>
-    <row r="303" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="303" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A303" s="1">
         <v>150.51</v>
       </c>
@@ -7192,9 +6888,8 @@
       <c r="M303" s="4"/>
       <c r="N303" s="4"/>
       <c r="O303" s="4"/>
-      <c r="P303" s="4"/>
-    </row>
-    <row r="304" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="304" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A304" s="1">
         <v>151.01</v>
       </c>
@@ -7214,9 +6909,8 @@
       <c r="M304" s="4"/>
       <c r="N304" s="4"/>
       <c r="O304" s="4"/>
-      <c r="P304" s="4"/>
-    </row>
-    <row r="305" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="305" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A305" s="1">
         <v>151.51</v>
       </c>
@@ -7236,9 +6930,8 @@
       <c r="M305" s="4"/>
       <c r="N305" s="4"/>
       <c r="O305" s="4"/>
-      <c r="P305" s="4"/>
-    </row>
-    <row r="306" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="306" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A306" s="1">
         <v>152.01</v>
       </c>
@@ -7258,9 +6951,8 @@
       <c r="M306" s="4"/>
       <c r="N306" s="4"/>
       <c r="O306" s="4"/>
-      <c r="P306" s="4"/>
-    </row>
-    <row r="307" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="307" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A307" s="1">
         <v>152.51</v>
       </c>
@@ -7280,9 +6972,8 @@
       <c r="M307" s="4"/>
       <c r="N307" s="4"/>
       <c r="O307" s="4"/>
-      <c r="P307" s="4"/>
-    </row>
-    <row r="308" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="308" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A308" s="1">
         <v>153.01</v>
       </c>
@@ -7302,9 +6993,8 @@
       <c r="M308" s="4"/>
       <c r="N308" s="4"/>
       <c r="O308" s="4"/>
-      <c r="P308" s="4"/>
-    </row>
-    <row r="309" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="309" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A309" s="1">
         <v>153.51</v>
       </c>
@@ -7324,9 +7014,8 @@
       <c r="M309" s="4"/>
       <c r="N309" s="4"/>
       <c r="O309" s="4"/>
-      <c r="P309" s="4"/>
-    </row>
-    <row r="310" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="310" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A310" s="1">
         <v>154.01</v>
       </c>
@@ -7346,9 +7035,8 @@
       <c r="M310" s="4"/>
       <c r="N310" s="4"/>
       <c r="O310" s="4"/>
-      <c r="P310" s="4"/>
-    </row>
-    <row r="311" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="311" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A311" s="1">
         <v>154.51</v>
       </c>
@@ -7368,9 +7056,8 @@
       <c r="M311" s="4"/>
       <c r="N311" s="4"/>
       <c r="O311" s="4"/>
-      <c r="P311" s="4"/>
-    </row>
-    <row r="312" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="312" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A312" s="1">
         <v>155.01</v>
       </c>
@@ -7390,9 +7077,8 @@
       <c r="M312" s="4"/>
       <c r="N312" s="4"/>
       <c r="O312" s="4"/>
-      <c r="P312" s="4"/>
-    </row>
-    <row r="313" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="313" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A313" s="1">
         <v>155.51</v>
       </c>
@@ -7412,9 +7098,8 @@
       <c r="M313" s="4"/>
       <c r="N313" s="4"/>
       <c r="O313" s="4"/>
-      <c r="P313" s="4"/>
-    </row>
-    <row r="314" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="314" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A314" s="1">
         <v>156.01</v>
       </c>
@@ -7434,9 +7119,8 @@
       <c r="M314" s="4"/>
       <c r="N314" s="4"/>
       <c r="O314" s="4"/>
-      <c r="P314" s="4"/>
-    </row>
-    <row r="315" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="315" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A315" s="1">
         <v>156.51</v>
       </c>
@@ -7456,9 +7140,8 @@
       <c r="M315" s="4"/>
       <c r="N315" s="4"/>
       <c r="O315" s="4"/>
-      <c r="P315" s="4"/>
-    </row>
-    <row r="316" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="316" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A316" s="1">
         <v>157.01</v>
       </c>
@@ -7478,9 +7161,8 @@
       <c r="M316" s="4"/>
       <c r="N316" s="4"/>
       <c r="O316" s="4"/>
-      <c r="P316" s="4"/>
-    </row>
-    <row r="317" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="317" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A317" s="1">
         <v>157.51</v>
       </c>
@@ -7500,9 +7182,8 @@
       <c r="M317" s="4"/>
       <c r="N317" s="4"/>
       <c r="O317" s="4"/>
-      <c r="P317" s="4"/>
-    </row>
-    <row r="318" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="318" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A318" s="1">
         <v>158.01</v>
       </c>
@@ -7522,9 +7203,8 @@
       <c r="M318" s="4"/>
       <c r="N318" s="4"/>
       <c r="O318" s="4"/>
-      <c r="P318" s="4"/>
-    </row>
-    <row r="319" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="319" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A319" s="1">
         <v>158.51</v>
       </c>
@@ -7544,9 +7224,8 @@
       <c r="M319" s="4"/>
       <c r="N319" s="4"/>
       <c r="O319" s="4"/>
-      <c r="P319" s="4"/>
-    </row>
-    <row r="320" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="320" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A320" s="1">
         <v>159.01</v>
       </c>
@@ -7566,9 +7245,8 @@
       <c r="M320" s="4"/>
       <c r="N320" s="4"/>
       <c r="O320" s="4"/>
-      <c r="P320" s="4"/>
-    </row>
-    <row r="321" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="321" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A321" s="1">
         <v>159.51</v>
       </c>
@@ -7588,9 +7266,8 @@
       <c r="M321" s="4"/>
       <c r="N321" s="4"/>
       <c r="O321" s="4"/>
-      <c r="P321" s="4"/>
-    </row>
-    <row r="322" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="322" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A322" s="1">
         <v>160.01</v>
       </c>
@@ -7610,9 +7287,8 @@
       <c r="M322" s="4"/>
       <c r="N322" s="4"/>
       <c r="O322" s="4"/>
-      <c r="P322" s="4"/>
-    </row>
-    <row r="323" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="323" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A323" s="1">
         <v>160.51</v>
       </c>
@@ -7632,9 +7308,8 @@
       <c r="M323" s="4"/>
       <c r="N323" s="4"/>
       <c r="O323" s="4"/>
-      <c r="P323" s="4"/>
-    </row>
-    <row r="324" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="324" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A324" s="1">
         <v>161.01</v>
       </c>
@@ -7654,9 +7329,8 @@
       <c r="M324" s="4"/>
       <c r="N324" s="4"/>
       <c r="O324" s="4"/>
-      <c r="P324" s="4"/>
-    </row>
-    <row r="325" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="325" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A325" s="1">
         <v>161.51</v>
       </c>
@@ -7676,9 +7350,8 @@
       <c r="M325" s="4"/>
       <c r="N325" s="4"/>
       <c r="O325" s="4"/>
-      <c r="P325" s="4"/>
-    </row>
-    <row r="326" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="326" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A326" s="1">
         <v>162.01</v>
       </c>
@@ -7698,9 +7371,8 @@
       <c r="M326" s="4"/>
       <c r="N326" s="4"/>
       <c r="O326" s="4"/>
-      <c r="P326" s="4"/>
-    </row>
-    <row r="327" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="327" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A327" s="1">
         <v>162.51</v>
       </c>
@@ -7720,9 +7392,8 @@
       <c r="M327" s="4"/>
       <c r="N327" s="4"/>
       <c r="O327" s="4"/>
-      <c r="P327" s="4"/>
-    </row>
-    <row r="328" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="328" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A328" s="1">
         <v>163.01</v>
       </c>
@@ -7742,9 +7413,8 @@
       <c r="M328" s="4"/>
       <c r="N328" s="4"/>
       <c r="O328" s="4"/>
-      <c r="P328" s="4"/>
-    </row>
-    <row r="329" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="329" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A329" s="1">
         <v>163.51</v>
       </c>
@@ -7764,9 +7434,8 @@
       <c r="M329" s="4"/>
       <c r="N329" s="4"/>
       <c r="O329" s="4"/>
-      <c r="P329" s="4"/>
-    </row>
-    <row r="330" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="330" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A330" s="1">
         <v>164.01</v>
       </c>
@@ -7786,9 +7455,8 @@
       <c r="M330" s="4"/>
       <c r="N330" s="4"/>
       <c r="O330" s="4"/>
-      <c r="P330" s="4"/>
-    </row>
-    <row r="331" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="331" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A331" s="1">
         <v>164.51</v>
       </c>
@@ -7808,9 +7476,8 @@
       <c r="M331" s="4"/>
       <c r="N331" s="4"/>
       <c r="O331" s="4"/>
-      <c r="P331" s="4"/>
-    </row>
-    <row r="332" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="332" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A332" s="1">
         <v>165.01</v>
       </c>
@@ -7830,9 +7497,8 @@
       <c r="M332" s="4"/>
       <c r="N332" s="4"/>
       <c r="O332" s="4"/>
-      <c r="P332" s="4"/>
-    </row>
-    <row r="333" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="333" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A333" s="1">
         <v>165.51</v>
       </c>
@@ -7852,9 +7518,8 @@
       <c r="M333" s="4"/>
       <c r="N333" s="4"/>
       <c r="O333" s="4"/>
-      <c r="P333" s="4"/>
-    </row>
-    <row r="334" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="334" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A334" s="1">
         <v>166.01</v>
       </c>
@@ -7874,9 +7539,8 @@
       <c r="M334" s="4"/>
       <c r="N334" s="4"/>
       <c r="O334" s="4"/>
-      <c r="P334" s="4"/>
-    </row>
-    <row r="335" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="335" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A335" s="1">
         <v>166.51</v>
       </c>
@@ -7896,9 +7560,8 @@
       <c r="M335" s="4"/>
       <c r="N335" s="4"/>
       <c r="O335" s="4"/>
-      <c r="P335" s="4"/>
-    </row>
-    <row r="336" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="336" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A336" s="1">
         <v>167.01</v>
       </c>
@@ -7918,9 +7581,8 @@
       <c r="M336" s="4"/>
       <c r="N336" s="4"/>
       <c r="O336" s="4"/>
-      <c r="P336" s="4"/>
-    </row>
-    <row r="337" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="337" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A337" s="1">
         <v>167.51</v>
       </c>
@@ -7940,9 +7602,8 @@
       <c r="M337" s="4"/>
       <c r="N337" s="4"/>
       <c r="O337" s="4"/>
-      <c r="P337" s="4"/>
-    </row>
-    <row r="338" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="338" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A338" s="1">
         <v>168.01</v>
       </c>
@@ -7962,9 +7623,8 @@
       <c r="M338" s="4"/>
       <c r="N338" s="4"/>
       <c r="O338" s="4"/>
-      <c r="P338" s="4"/>
-    </row>
-    <row r="339" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="339" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A339" s="1">
         <v>168.51</v>
       </c>
@@ -7984,9 +7644,8 @@
       <c r="M339" s="4"/>
       <c r="N339" s="4"/>
       <c r="O339" s="4"/>
-      <c r="P339" s="4"/>
-    </row>
-    <row r="340" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="340" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A340" s="1">
         <v>169.01</v>
       </c>
@@ -8006,9 +7665,8 @@
       <c r="M340" s="4"/>
       <c r="N340" s="4"/>
       <c r="O340" s="4"/>
-      <c r="P340" s="4"/>
-    </row>
-    <row r="341" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="341" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A341" s="1">
         <v>169.51</v>
       </c>
@@ -8028,9 +7686,8 @@
       <c r="M341" s="4"/>
       <c r="N341" s="4"/>
       <c r="O341" s="4"/>
-      <c r="P341" s="4"/>
-    </row>
-    <row r="342" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="342" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A342" s="1">
         <v>170.01</v>
       </c>
@@ -8050,9 +7707,8 @@
       <c r="M342" s="4"/>
       <c r="N342" s="4"/>
       <c r="O342" s="4"/>
-      <c r="P342" s="4"/>
-    </row>
-    <row r="343" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="343" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A343" s="1">
         <v>170.51</v>
       </c>
@@ -8072,9 +7728,8 @@
       <c r="M343" s="4"/>
       <c r="N343" s="4"/>
       <c r="O343" s="4"/>
-      <c r="P343" s="4"/>
-    </row>
-    <row r="344" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="344" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A344" s="1">
         <v>171.01</v>
       </c>
@@ -8094,9 +7749,8 @@
       <c r="M344" s="4"/>
       <c r="N344" s="4"/>
       <c r="O344" s="4"/>
-      <c r="P344" s="4"/>
-    </row>
-    <row r="345" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="345" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A345" s="1">
         <v>171.51</v>
       </c>
@@ -8116,9 +7770,8 @@
       <c r="M345" s="4"/>
       <c r="N345" s="4"/>
       <c r="O345" s="4"/>
-      <c r="P345" s="4"/>
-    </row>
-    <row r="346" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="346" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A346" s="1">
         <v>172.01</v>
       </c>
@@ -8138,9 +7791,8 @@
       <c r="M346" s="4"/>
       <c r="N346" s="4"/>
       <c r="O346" s="4"/>
-      <c r="P346" s="4"/>
-    </row>
-    <row r="347" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="347" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A347" s="1">
         <v>172.51</v>
       </c>
@@ -8160,9 +7812,8 @@
       <c r="M347" s="4"/>
       <c r="N347" s="4"/>
       <c r="O347" s="4"/>
-      <c r="P347" s="4"/>
-    </row>
-    <row r="348" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="348" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A348" s="1">
         <v>173.01</v>
       </c>
@@ -8182,9 +7833,8 @@
       <c r="M348" s="4"/>
       <c r="N348" s="4"/>
       <c r="O348" s="4"/>
-      <c r="P348" s="4"/>
-    </row>
-    <row r="349" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="349" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A349" s="1">
         <v>173.51</v>
       </c>
@@ -8204,9 +7854,8 @@
       <c r="M349" s="4"/>
       <c r="N349" s="4"/>
       <c r="O349" s="4"/>
-      <c r="P349" s="4"/>
-    </row>
-    <row r="350" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="350" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A350" s="1">
         <v>174.01</v>
       </c>
@@ -8226,9 +7875,8 @@
       <c r="M350" s="4"/>
       <c r="N350" s="4"/>
       <c r="O350" s="4"/>
-      <c r="P350" s="4"/>
-    </row>
-    <row r="351" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="351" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A351" s="1">
         <v>174.51</v>
       </c>
@@ -8248,9 +7896,8 @@
       <c r="M351" s="4"/>
       <c r="N351" s="4"/>
       <c r="O351" s="4"/>
-      <c r="P351" s="4"/>
-    </row>
-    <row r="352" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="352" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A352" s="1">
         <v>175.01</v>
       </c>
@@ -8270,9 +7917,8 @@
       <c r="M352" s="4"/>
       <c r="N352" s="4"/>
       <c r="O352" s="4"/>
-      <c r="P352" s="4"/>
-    </row>
-    <row r="353" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="353" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A353" s="1">
         <v>175.51</v>
       </c>
@@ -8292,9 +7938,8 @@
       <c r="M353" s="4"/>
       <c r="N353" s="4"/>
       <c r="O353" s="4"/>
-      <c r="P353" s="4"/>
-    </row>
-    <row r="354" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="354" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A354" s="1">
         <v>176.01</v>
       </c>
@@ -8314,9 +7959,8 @@
       <c r="M354" s="4"/>
       <c r="N354" s="4"/>
       <c r="O354" s="4"/>
-      <c r="P354" s="4"/>
-    </row>
-    <row r="355" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="355" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A355" s="1">
         <v>176.51</v>
       </c>
@@ -8336,9 +7980,8 @@
       <c r="M355" s="4"/>
       <c r="N355" s="4"/>
       <c r="O355" s="4"/>
-      <c r="P355" s="4"/>
-    </row>
-    <row r="356" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="356" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A356" s="1">
         <v>177.01</v>
       </c>
@@ -8358,9 +8001,8 @@
       <c r="M356" s="4"/>
       <c r="N356" s="4"/>
       <c r="O356" s="4"/>
-      <c r="P356" s="4"/>
-    </row>
-    <row r="357" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="357" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A357" s="1">
         <v>177.51</v>
       </c>
@@ -8380,9 +8022,8 @@
       <c r="M357" s="4"/>
       <c r="N357" s="4"/>
       <c r="O357" s="4"/>
-      <c r="P357" s="4"/>
-    </row>
-    <row r="358" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="358" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A358" s="1">
         <v>178.01</v>
       </c>
@@ -8402,9 +8043,8 @@
       <c r="M358" s="4"/>
       <c r="N358" s="4"/>
       <c r="O358" s="4"/>
-      <c r="P358" s="4"/>
-    </row>
-    <row r="359" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="359" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A359" s="1">
         <v>178.51</v>
       </c>
@@ -8424,9 +8064,8 @@
       <c r="M359" s="4"/>
       <c r="N359" s="4"/>
       <c r="O359" s="4"/>
-      <c r="P359" s="4"/>
-    </row>
-    <row r="360" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="360" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A360" s="1">
         <v>179.01</v>
       </c>
@@ -8446,9 +8085,8 @@
       <c r="M360" s="4"/>
       <c r="N360" s="4"/>
       <c r="O360" s="4"/>
-      <c r="P360" s="4"/>
-    </row>
-    <row r="361" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="361" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A361" s="1">
         <v>179.51</v>
       </c>
@@ -8468,9 +8106,8 @@
       <c r="M361" s="4"/>
       <c r="N361" s="4"/>
       <c r="O361" s="4"/>
-      <c r="P361" s="4"/>
-    </row>
-    <row r="362" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="362" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A362" s="1">
         <v>180.01</v>
       </c>
@@ -8490,9 +8127,8 @@
       <c r="M362" s="4"/>
       <c r="N362" s="4"/>
       <c r="O362" s="4"/>
-      <c r="P362" s="4"/>
-    </row>
-    <row r="363" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="363" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A363" s="1">
         <v>180.51</v>
       </c>
@@ -8512,9 +8148,8 @@
       <c r="M363" s="4"/>
       <c r="N363" s="4"/>
       <c r="O363" s="4"/>
-      <c r="P363" s="4"/>
-    </row>
-    <row r="364" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="364" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A364" s="1">
         <v>181.01</v>
       </c>
@@ -8534,9 +8169,8 @@
       <c r="M364" s="4"/>
       <c r="N364" s="4"/>
       <c r="O364" s="4"/>
-      <c r="P364" s="4"/>
-    </row>
-    <row r="365" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="365" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A365" s="1">
         <v>181.51</v>
       </c>
@@ -8556,9 +8190,8 @@
       <c r="M365" s="4"/>
       <c r="N365" s="4"/>
       <c r="O365" s="4"/>
-      <c r="P365" s="4"/>
-    </row>
-    <row r="366" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="366" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A366" s="1">
         <v>182.01</v>
       </c>
@@ -8578,9 +8211,8 @@
       <c r="M366" s="4"/>
       <c r="N366" s="4"/>
       <c r="O366" s="4"/>
-      <c r="P366" s="4"/>
-    </row>
-    <row r="367" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="367" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A367" s="1">
         <v>182.51</v>
       </c>
@@ -8600,9 +8232,8 @@
       <c r="M367" s="4"/>
       <c r="N367" s="4"/>
       <c r="O367" s="4"/>
-      <c r="P367" s="4"/>
-    </row>
-    <row r="368" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="368" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A368" s="1">
         <v>183.01</v>
       </c>
@@ -8622,9 +8253,8 @@
       <c r="M368" s="4"/>
       <c r="N368" s="4"/>
       <c r="O368" s="4"/>
-      <c r="P368" s="4"/>
-    </row>
-    <row r="369" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="369" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A369" s="1">
         <v>183.51</v>
       </c>
@@ -8644,9 +8274,8 @@
       <c r="M369" s="4"/>
       <c r="N369" s="4"/>
       <c r="O369" s="4"/>
-      <c r="P369" s="4"/>
-    </row>
-    <row r="370" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="370" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A370" s="1">
         <v>184.01</v>
       </c>
@@ -8666,9 +8295,8 @@
       <c r="M370" s="4"/>
       <c r="N370" s="4"/>
       <c r="O370" s="4"/>
-      <c r="P370" s="4"/>
-    </row>
-    <row r="371" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="371" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A371" s="1">
         <v>184.51</v>
       </c>
@@ -8688,9 +8316,8 @@
       <c r="M371" s="4"/>
       <c r="N371" s="4"/>
       <c r="O371" s="4"/>
-      <c r="P371" s="4"/>
-    </row>
-    <row r="372" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="372" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A372" s="1">
         <v>185.01</v>
       </c>
@@ -8710,9 +8337,8 @@
       <c r="M372" s="4"/>
       <c r="N372" s="4"/>
       <c r="O372" s="4"/>
-      <c r="P372" s="4"/>
-    </row>
-    <row r="373" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="373" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A373" s="1">
         <v>185.51</v>
       </c>
@@ -8732,9 +8358,8 @@
       <c r="M373" s="4"/>
       <c r="N373" s="4"/>
       <c r="O373" s="4"/>
-      <c r="P373" s="4"/>
-    </row>
-    <row r="374" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="374" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A374" s="1">
         <v>186.01</v>
       </c>
@@ -8754,9 +8379,8 @@
       <c r="M374" s="4"/>
       <c r="N374" s="4"/>
       <c r="O374" s="4"/>
-      <c r="P374" s="4"/>
-    </row>
-    <row r="375" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="375" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A375" s="1">
         <v>186.51</v>
       </c>
@@ -8776,9 +8400,8 @@
       <c r="M375" s="4"/>
       <c r="N375" s="4"/>
       <c r="O375" s="4"/>
-      <c r="P375" s="4"/>
-    </row>
-    <row r="376" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="376" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A376" s="1">
         <v>187.01</v>
       </c>
@@ -8798,9 +8421,8 @@
       <c r="M376" s="4"/>
       <c r="N376" s="4"/>
       <c r="O376" s="4"/>
-      <c r="P376" s="4"/>
-    </row>
-    <row r="377" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="377" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A377" s="1">
         <v>187.51</v>
       </c>
@@ -8820,9 +8442,8 @@
       <c r="M377" s="4"/>
       <c r="N377" s="4"/>
       <c r="O377" s="4"/>
-      <c r="P377" s="4"/>
-    </row>
-    <row r="378" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="378" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A378" s="1">
         <v>188.01</v>
       </c>
@@ -8842,9 +8463,8 @@
       <c r="M378" s="4"/>
       <c r="N378" s="4"/>
       <c r="O378" s="4"/>
-      <c r="P378" s="4"/>
-    </row>
-    <row r="379" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="379" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A379" s="1">
         <v>188.51</v>
       </c>
@@ -8864,9 +8484,8 @@
       <c r="M379" s="4"/>
       <c r="N379" s="4"/>
       <c r="O379" s="4"/>
-      <c r="P379" s="4"/>
-    </row>
-    <row r="380" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="380" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A380" s="1">
         <v>189.01</v>
       </c>
@@ -8886,9 +8505,8 @@
       <c r="M380" s="4"/>
       <c r="N380" s="4"/>
       <c r="O380" s="4"/>
-      <c r="P380" s="4"/>
-    </row>
-    <row r="381" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="381" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A381" s="1">
         <v>189.51</v>
       </c>
@@ -8908,9 +8526,8 @@
       <c r="M381" s="4"/>
       <c r="N381" s="4"/>
       <c r="O381" s="4"/>
-      <c r="P381" s="4"/>
-    </row>
-    <row r="382" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="382" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A382" s="1">
         <v>190.01</v>
       </c>
@@ -8930,9 +8547,8 @@
       <c r="M382" s="4"/>
       <c r="N382" s="4"/>
       <c r="O382" s="4"/>
-      <c r="P382" s="4"/>
-    </row>
-    <row r="383" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="383" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A383" s="1">
         <v>190.51</v>
       </c>
@@ -8952,9 +8568,8 @@
       <c r="M383" s="4"/>
       <c r="N383" s="4"/>
       <c r="O383" s="4"/>
-      <c r="P383" s="4"/>
-    </row>
-    <row r="384" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="384" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A384" s="1">
         <v>191.01</v>
       </c>
@@ -8974,9 +8589,8 @@
       <c r="M384" s="4"/>
       <c r="N384" s="4"/>
       <c r="O384" s="4"/>
-      <c r="P384" s="4"/>
-    </row>
-    <row r="385" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="385" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A385" s="1">
         <v>191.51</v>
       </c>
@@ -8996,9 +8610,8 @@
       <c r="M385" s="4"/>
       <c r="N385" s="4"/>
       <c r="O385" s="4"/>
-      <c r="P385" s="4"/>
-    </row>
-    <row r="386" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="386" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A386" s="1">
         <v>192.01</v>
       </c>
@@ -9018,9 +8631,8 @@
       <c r="M386" s="4"/>
       <c r="N386" s="4"/>
       <c r="O386" s="4"/>
-      <c r="P386" s="4"/>
-    </row>
-    <row r="387" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="387" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A387" s="1">
         <v>192.51</v>
       </c>
@@ -9040,9 +8652,8 @@
       <c r="M387" s="4"/>
       <c r="N387" s="4"/>
       <c r="O387" s="4"/>
-      <c r="P387" s="4"/>
-    </row>
-    <row r="388" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="388" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A388" s="1">
         <v>193.01</v>
       </c>
@@ -9062,9 +8673,8 @@
       <c r="M388" s="4"/>
       <c r="N388" s="4"/>
       <c r="O388" s="4"/>
-      <c r="P388" s="4"/>
-    </row>
-    <row r="389" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="389" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A389" s="1">
         <v>193.51</v>
       </c>
@@ -9084,9 +8694,8 @@
       <c r="M389" s="4"/>
       <c r="N389" s="4"/>
       <c r="O389" s="4"/>
-      <c r="P389" s="4"/>
-    </row>
-    <row r="390" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="390" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A390" s="1">
         <v>194.01</v>
       </c>
@@ -9106,9 +8715,8 @@
       <c r="M390" s="4"/>
       <c r="N390" s="4"/>
       <c r="O390" s="4"/>
-      <c r="P390" s="4"/>
-    </row>
-    <row r="391" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="391" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A391" s="1">
         <v>194.51</v>
       </c>
@@ -9128,9 +8736,8 @@
       <c r="M391" s="4"/>
       <c r="N391" s="4"/>
       <c r="O391" s="4"/>
-      <c r="P391" s="4"/>
-    </row>
-    <row r="392" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="392" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A392" s="1">
         <v>195.01</v>
       </c>
@@ -9150,9 +8757,8 @@
       <c r="M392" s="4"/>
       <c r="N392" s="4"/>
       <c r="O392" s="4"/>
-      <c r="P392" s="4"/>
-    </row>
-    <row r="393" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="393" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A393" s="1">
         <v>195.51</v>
       </c>
@@ -9172,9 +8778,8 @@
       <c r="M393" s="4"/>
       <c r="N393" s="4"/>
       <c r="O393" s="4"/>
-      <c r="P393" s="4"/>
-    </row>
-    <row r="394" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="394" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A394" s="1">
         <v>196.01</v>
       </c>
@@ -9194,9 +8799,8 @@
       <c r="M394" s="4"/>
       <c r="N394" s="4"/>
       <c r="O394" s="4"/>
-      <c r="P394" s="4"/>
-    </row>
-    <row r="395" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="395" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A395" s="1">
         <v>196.51</v>
       </c>
@@ -9216,9 +8820,8 @@
       <c r="M395" s="4"/>
       <c r="N395" s="4"/>
       <c r="O395" s="4"/>
-      <c r="P395" s="4"/>
-    </row>
-    <row r="396" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="396" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A396" s="1">
         <v>197.01</v>
       </c>
@@ -9238,9 +8841,8 @@
       <c r="M396" s="4"/>
       <c r="N396" s="4"/>
       <c r="O396" s="4"/>
-      <c r="P396" s="4"/>
-    </row>
-    <row r="397" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="397" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A397" s="1">
         <v>197.51</v>
       </c>
@@ -9260,9 +8862,8 @@
       <c r="M397" s="4"/>
       <c r="N397" s="4"/>
       <c r="O397" s="4"/>
-      <c r="P397" s="4"/>
-    </row>
-    <row r="398" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="398" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A398" s="1">
         <v>198.01</v>
       </c>
@@ -9282,9 +8883,8 @@
       <c r="M398" s="4"/>
       <c r="N398" s="4"/>
       <c r="O398" s="4"/>
-      <c r="P398" s="4"/>
-    </row>
-    <row r="399" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="399" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A399" s="1">
         <v>198.51</v>
       </c>
@@ -9304,9 +8904,8 @@
       <c r="M399" s="4"/>
       <c r="N399" s="4"/>
       <c r="O399" s="4"/>
-      <c r="P399" s="4"/>
-    </row>
-    <row r="400" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="400" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A400" s="1">
         <v>199.01</v>
       </c>
@@ -9326,9 +8925,8 @@
       <c r="M400" s="4"/>
       <c r="N400" s="4"/>
       <c r="O400" s="4"/>
-      <c r="P400" s="4"/>
-    </row>
-    <row r="401" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="401" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A401" s="1">
         <v>199.51</v>
       </c>
@@ -9348,9 +8946,8 @@
       <c r="M401" s="4"/>
       <c r="N401" s="4"/>
       <c r="O401" s="4"/>
-      <c r="P401" s="4"/>
-    </row>
-    <row r="402" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="402" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A402" s="1">
         <v>200.01</v>
       </c>
@@ -9370,9 +8967,8 @@
       <c r="M402" s="4"/>
       <c r="N402" s="4"/>
       <c r="O402" s="4"/>
-      <c r="P402" s="4"/>
-    </row>
-    <row r="403" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="403" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A403" s="1">
         <v>200.51</v>
       </c>
@@ -9392,9 +8988,8 @@
       <c r="M403" s="4"/>
       <c r="N403" s="4"/>
       <c r="O403" s="4"/>
-      <c r="P403" s="4"/>
-    </row>
-    <row r="404" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="404" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A404" s="1">
         <v>201.01</v>
       </c>
@@ -9414,9 +9009,8 @@
       <c r="M404" s="4"/>
       <c r="N404" s="4"/>
       <c r="O404" s="4"/>
-      <c r="P404" s="4"/>
-    </row>
-    <row r="405" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="405" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A405" s="1">
         <v>201.51</v>
       </c>
@@ -9436,9 +9030,8 @@
       <c r="M405" s="4"/>
       <c r="N405" s="4"/>
       <c r="O405" s="4"/>
-      <c r="P405" s="4"/>
-    </row>
-    <row r="406" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="406" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A406" s="1">
         <v>202.01</v>
       </c>
@@ -9458,9 +9051,8 @@
       <c r="M406" s="4"/>
       <c r="N406" s="4"/>
       <c r="O406" s="4"/>
-      <c r="P406" s="4"/>
-    </row>
-    <row r="407" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="407" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A407" s="1">
         <v>202.51</v>
       </c>
@@ -9480,9 +9072,8 @@
       <c r="M407" s="4"/>
       <c r="N407" s="4"/>
       <c r="O407" s="4"/>
-      <c r="P407" s="4"/>
-    </row>
-    <row r="408" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="408" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A408" s="1">
         <v>203.01</v>
       </c>
@@ -9502,9 +9093,8 @@
       <c r="M408" s="4"/>
       <c r="N408" s="4"/>
       <c r="O408" s="4"/>
-      <c r="P408" s="4"/>
-    </row>
-    <row r="409" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="409" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A409" s="1">
         <v>203.51</v>
       </c>
@@ -9524,9 +9114,8 @@
       <c r="M409" s="4"/>
       <c r="N409" s="4"/>
       <c r="O409" s="4"/>
-      <c r="P409" s="4"/>
-    </row>
-    <row r="410" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="410" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A410" s="1">
         <v>204.01</v>
       </c>
@@ -9546,9 +9135,8 @@
       <c r="M410" s="4"/>
       <c r="N410" s="4"/>
       <c r="O410" s="4"/>
-      <c r="P410" s="4"/>
-    </row>
-    <row r="411" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="411" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A411" s="1">
         <v>204.51</v>
       </c>
@@ -9568,9 +9156,8 @@
       <c r="M411" s="4"/>
       <c r="N411" s="4"/>
       <c r="O411" s="4"/>
-      <c r="P411" s="4"/>
-    </row>
-    <row r="412" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="412" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A412" s="1">
         <v>205.01</v>
       </c>
@@ -9590,9 +9177,8 @@
       <c r="M412" s="4"/>
       <c r="N412" s="4"/>
       <c r="O412" s="4"/>
-      <c r="P412" s="4"/>
-    </row>
-    <row r="413" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="413" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A413" s="1">
         <v>205.51</v>
       </c>
@@ -9612,9 +9198,8 @@
       <c r="M413" s="4"/>
       <c r="N413" s="4"/>
       <c r="O413" s="4"/>
-      <c r="P413" s="4"/>
-    </row>
-    <row r="414" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="414" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A414" s="1">
         <v>206.01</v>
       </c>
@@ -9634,9 +9219,8 @@
       <c r="M414" s="4"/>
       <c r="N414" s="4"/>
       <c r="O414" s="4"/>
-      <c r="P414" s="4"/>
-    </row>
-    <row r="415" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="415" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A415" s="1">
         <v>206.51</v>
       </c>
@@ -9656,9 +9240,8 @@
       <c r="M415" s="4"/>
       <c r="N415" s="4"/>
       <c r="O415" s="4"/>
-      <c r="P415" s="4"/>
-    </row>
-    <row r="416" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="416" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A416" s="1">
         <v>207.01</v>
       </c>
@@ -9678,9 +9261,8 @@
       <c r="M416" s="4"/>
       <c r="N416" s="4"/>
       <c r="O416" s="4"/>
-      <c r="P416" s="4"/>
-    </row>
-    <row r="417" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="417" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A417" s="1">
         <v>207.51</v>
       </c>
@@ -9700,9 +9282,8 @@
       <c r="M417" s="4"/>
       <c r="N417" s="4"/>
       <c r="O417" s="4"/>
-      <c r="P417" s="4"/>
-    </row>
-    <row r="418" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="418" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A418" s="1">
         <v>208.01</v>
       </c>
@@ -9722,9 +9303,8 @@
       <c r="M418" s="4"/>
       <c r="N418" s="4"/>
       <c r="O418" s="4"/>
-      <c r="P418" s="4"/>
-    </row>
-    <row r="419" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="419" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A419" s="1">
         <v>208.51</v>
       </c>
@@ -9744,9 +9324,8 @@
       <c r="M419" s="4"/>
       <c r="N419" s="4"/>
       <c r="O419" s="4"/>
-      <c r="P419" s="4"/>
-    </row>
-    <row r="420" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="420" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A420" s="1">
         <v>209.01</v>
       </c>
@@ -9766,9 +9345,8 @@
       <c r="M420" s="4"/>
       <c r="N420" s="4"/>
       <c r="O420" s="4"/>
-      <c r="P420" s="4"/>
-    </row>
-    <row r="421" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="421" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A421" s="1">
         <v>209.51</v>
       </c>
@@ -9788,9 +9366,8 @@
       <c r="M421" s="4"/>
       <c r="N421" s="4"/>
       <c r="O421" s="4"/>
-      <c r="P421" s="4"/>
-    </row>
-    <row r="422" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="422" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A422" s="1">
         <v>210.01</v>
       </c>
@@ -9810,9 +9387,8 @@
       <c r="M422" s="4"/>
       <c r="N422" s="4"/>
       <c r="O422" s="4"/>
-      <c r="P422" s="4"/>
-    </row>
-    <row r="423" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="423" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A423" s="1">
         <v>210.51</v>
       </c>
@@ -9832,9 +9408,8 @@
       <c r="M423" s="4"/>
       <c r="N423" s="4"/>
       <c r="O423" s="4"/>
-      <c r="P423" s="4"/>
-    </row>
-    <row r="424" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="424" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A424" s="1">
         <v>211.01</v>
       </c>
@@ -9854,9 +9429,8 @@
       <c r="M424" s="4"/>
       <c r="N424" s="4"/>
       <c r="O424" s="4"/>
-      <c r="P424" s="4"/>
-    </row>
-    <row r="425" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="425" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A425" s="1">
         <v>211.51</v>
       </c>
@@ -9876,9 +9450,8 @@
       <c r="M425" s="4"/>
       <c r="N425" s="4"/>
       <c r="O425" s="4"/>
-      <c r="P425" s="4"/>
-    </row>
-    <row r="426" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="426" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A426" s="1">
         <v>212.01</v>
       </c>
@@ -9898,9 +9471,8 @@
       <c r="M426" s="4"/>
       <c r="N426" s="4"/>
       <c r="O426" s="4"/>
-      <c r="P426" s="4"/>
-    </row>
-    <row r="427" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="427" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A427" s="1">
         <v>212.51</v>
       </c>
@@ -9920,9 +9492,8 @@
       <c r="M427" s="4"/>
       <c r="N427" s="4"/>
       <c r="O427" s="4"/>
-      <c r="P427" s="4"/>
-    </row>
-    <row r="428" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="428" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A428" s="1">
         <v>213.01</v>
       </c>
@@ -9942,9 +9513,8 @@
       <c r="M428" s="4"/>
       <c r="N428" s="4"/>
       <c r="O428" s="4"/>
-      <c r="P428" s="4"/>
-    </row>
-    <row r="429" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="429" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A429" s="1">
         <v>213.51</v>
       </c>
@@ -9964,9 +9534,8 @@
       <c r="M429" s="4"/>
       <c r="N429" s="4"/>
       <c r="O429" s="4"/>
-      <c r="P429" s="4"/>
-    </row>
-    <row r="430" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="430" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A430" s="1">
         <v>214.01</v>
       </c>
@@ -9986,9 +9555,8 @@
       <c r="M430" s="4"/>
       <c r="N430" s="4"/>
       <c r="O430" s="4"/>
-      <c r="P430" s="4"/>
-    </row>
-    <row r="431" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="431" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A431" s="1">
         <v>214.51</v>
       </c>
@@ -10008,9 +9576,8 @@
       <c r="M431" s="4"/>
       <c r="N431" s="4"/>
       <c r="O431" s="4"/>
-      <c r="P431" s="4"/>
-    </row>
-    <row r="432" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="432" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A432" s="1">
         <v>215.01</v>
       </c>
@@ -10030,9 +9597,8 @@
       <c r="M432" s="4"/>
       <c r="N432" s="4"/>
       <c r="O432" s="4"/>
-      <c r="P432" s="4"/>
-    </row>
-    <row r="433" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="433" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A433" s="1">
         <v>215.51</v>
       </c>
@@ -10052,9 +9618,8 @@
       <c r="M433" s="4"/>
       <c r="N433" s="4"/>
       <c r="O433" s="4"/>
-      <c r="P433" s="4"/>
-    </row>
-    <row r="434" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="434" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A434" s="1">
         <v>216.01</v>
       </c>
@@ -10074,9 +9639,8 @@
       <c r="M434" s="4"/>
       <c r="N434" s="4"/>
       <c r="O434" s="4"/>
-      <c r="P434" s="4"/>
-    </row>
-    <row r="435" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="435" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A435" s="1">
         <v>216.51</v>
       </c>
@@ -10096,9 +9660,8 @@
       <c r="M435" s="4"/>
       <c r="N435" s="4"/>
       <c r="O435" s="4"/>
-      <c r="P435" s="4"/>
-    </row>
-    <row r="436" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="436" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A436" s="1">
         <v>217.01</v>
       </c>
@@ -10118,9 +9681,8 @@
       <c r="M436" s="4"/>
       <c r="N436" s="4"/>
       <c r="O436" s="4"/>
-      <c r="P436" s="4"/>
-    </row>
-    <row r="437" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="437" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A437" s="1">
         <v>217.51</v>
       </c>
@@ -10140,9 +9702,8 @@
       <c r="M437" s="4"/>
       <c r="N437" s="4"/>
       <c r="O437" s="4"/>
-      <c r="P437" s="4"/>
-    </row>
-    <row r="438" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="438" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A438" s="1">
         <v>218.01</v>
       </c>
@@ -10162,9 +9723,8 @@
       <c r="M438" s="4"/>
       <c r="N438" s="4"/>
       <c r="O438" s="4"/>
-      <c r="P438" s="4"/>
-    </row>
-    <row r="439" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="439" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A439" s="1">
         <v>218.51</v>
       </c>
@@ -10184,9 +9744,8 @@
       <c r="M439" s="4"/>
       <c r="N439" s="4"/>
       <c r="O439" s="4"/>
-      <c r="P439" s="4"/>
-    </row>
-    <row r="440" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="440" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A440" s="1">
         <v>219.01</v>
       </c>
@@ -10206,9 +9765,8 @@
       <c r="M440" s="4"/>
       <c r="N440" s="4"/>
       <c r="O440" s="4"/>
-      <c r="P440" s="4"/>
-    </row>
-    <row r="441" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="441" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A441" s="1">
         <v>219.51</v>
       </c>
@@ -10228,9 +9786,8 @@
       <c r="M441" s="4"/>
       <c r="N441" s="4"/>
       <c r="O441" s="4"/>
-      <c r="P441" s="4"/>
-    </row>
-    <row r="442" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="442" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A442" s="1">
         <v>220.01</v>
       </c>
@@ -10250,9 +9807,8 @@
       <c r="M442" s="4"/>
       <c r="N442" s="4"/>
       <c r="O442" s="4"/>
-      <c r="P442" s="4"/>
-    </row>
-    <row r="443" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="443" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A443" s="1">
         <v>220.51</v>
       </c>
@@ -10272,9 +9828,8 @@
       <c r="M443" s="4"/>
       <c r="N443" s="4"/>
       <c r="O443" s="4"/>
-      <c r="P443" s="4"/>
-    </row>
-    <row r="444" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="444" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A444" s="1">
         <v>221.01</v>
       </c>
@@ -10294,9 +9849,8 @@
       <c r="M444" s="4"/>
       <c r="N444" s="4"/>
       <c r="O444" s="4"/>
-      <c r="P444" s="4"/>
-    </row>
-    <row r="445" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="445" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A445" s="1">
         <v>221.51</v>
       </c>
@@ -10316,9 +9870,8 @@
       <c r="M445" s="4"/>
       <c r="N445" s="4"/>
       <c r="O445" s="4"/>
-      <c r="P445" s="4"/>
-    </row>
-    <row r="446" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="446" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A446" s="1">
         <v>222.01</v>
       </c>
@@ -10338,9 +9891,8 @@
       <c r="M446" s="4"/>
       <c r="N446" s="4"/>
       <c r="O446" s="4"/>
-      <c r="P446" s="4"/>
-    </row>
-    <row r="447" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="447" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A447" s="1">
         <v>222.51</v>
       </c>
@@ -10360,9 +9912,8 @@
       <c r="M447" s="4"/>
       <c r="N447" s="4"/>
       <c r="O447" s="4"/>
-      <c r="P447" s="4"/>
-    </row>
-    <row r="448" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="448" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A448" s="1">
         <v>223.01</v>
       </c>
@@ -10382,9 +9933,8 @@
       <c r="M448" s="4"/>
       <c r="N448" s="4"/>
       <c r="O448" s="4"/>
-      <c r="P448" s="4"/>
-    </row>
-    <row r="449" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="449" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A449" s="1">
         <v>223.51</v>
       </c>
@@ -10404,9 +9954,8 @@
       <c r="M449" s="4"/>
       <c r="N449" s="4"/>
       <c r="O449" s="4"/>
-      <c r="P449" s="4"/>
-    </row>
-    <row r="450" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="450" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A450" s="1">
         <v>224.01</v>
       </c>
@@ -10426,9 +9975,8 @@
       <c r="M450" s="4"/>
       <c r="N450" s="4"/>
       <c r="O450" s="4"/>
-      <c r="P450" s="4"/>
-    </row>
-    <row r="451" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="451" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A451" s="1">
         <v>224.51</v>
       </c>
@@ -10448,9 +9996,8 @@
       <c r="M451" s="4"/>
       <c r="N451" s="4"/>
       <c r="O451" s="4"/>
-      <c r="P451" s="4"/>
-    </row>
-    <row r="452" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="452" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A452" s="1">
         <v>225.01</v>
       </c>
@@ -10470,9 +10017,8 @@
       <c r="M452" s="4"/>
       <c r="N452" s="4"/>
       <c r="O452" s="4"/>
-      <c r="P452" s="4"/>
-    </row>
-    <row r="453" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="453" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A453" s="1">
         <v>225.51</v>
       </c>
@@ -10492,9 +10038,8 @@
       <c r="M453" s="4"/>
       <c r="N453" s="4"/>
       <c r="O453" s="4"/>
-      <c r="P453" s="4"/>
-    </row>
-    <row r="454" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="454" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A454" s="1">
         <v>226.01</v>
       </c>
@@ -10514,9 +10059,8 @@
       <c r="M454" s="4"/>
       <c r="N454" s="4"/>
       <c r="O454" s="4"/>
-      <c r="P454" s="4"/>
-    </row>
-    <row r="455" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="455" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A455" s="1">
         <v>226.51</v>
       </c>
@@ -10536,9 +10080,8 @@
       <c r="M455" s="4"/>
       <c r="N455" s="4"/>
       <c r="O455" s="4"/>
-      <c r="P455" s="4"/>
-    </row>
-    <row r="456" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="456" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A456" s="1">
         <v>227.01</v>
       </c>
@@ -10558,9 +10101,8 @@
       <c r="M456" s="4"/>
       <c r="N456" s="4"/>
       <c r="O456" s="4"/>
-      <c r="P456" s="4"/>
-    </row>
-    <row r="457" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="457" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A457" s="1">
         <v>227.51</v>
       </c>
@@ -10580,9 +10122,8 @@
       <c r="M457" s="4"/>
       <c r="N457" s="4"/>
       <c r="O457" s="4"/>
-      <c r="P457" s="4"/>
-    </row>
-    <row r="458" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="458" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A458" s="1">
         <v>228.01</v>
       </c>
@@ -10602,9 +10143,8 @@
       <c r="M458" s="4"/>
       <c r="N458" s="4"/>
       <c r="O458" s="4"/>
-      <c r="P458" s="4"/>
-    </row>
-    <row r="459" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="459" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A459" s="1">
         <v>228.51</v>
       </c>
@@ -10624,9 +10164,8 @@
       <c r="M459" s="4"/>
       <c r="N459" s="4"/>
       <c r="O459" s="4"/>
-      <c r="P459" s="4"/>
-    </row>
-    <row r="460" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="460" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A460" s="1">
         <v>229.01</v>
       </c>
@@ -10646,9 +10185,8 @@
       <c r="M460" s="4"/>
       <c r="N460" s="4"/>
       <c r="O460" s="4"/>
-      <c r="P460" s="4"/>
-    </row>
-    <row r="461" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="461" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A461" s="1">
         <v>229.51</v>
       </c>
@@ -10668,9 +10206,8 @@
       <c r="M461" s="4"/>
       <c r="N461" s="4"/>
       <c r="O461" s="4"/>
-      <c r="P461" s="4"/>
-    </row>
-    <row r="462" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="462" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A462" s="1">
         <v>230.01</v>
       </c>
@@ -10690,9 +10227,8 @@
       <c r="M462" s="4"/>
       <c r="N462" s="4"/>
       <c r="O462" s="4"/>
-      <c r="P462" s="4"/>
-    </row>
-    <row r="463" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="463" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A463" s="1">
         <v>230.51</v>
       </c>
@@ -10712,9 +10248,8 @@
       <c r="M463" s="4"/>
       <c r="N463" s="4"/>
       <c r="O463" s="4"/>
-      <c r="P463" s="4"/>
-    </row>
-    <row r="464" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="464" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A464" s="1">
         <v>231.01</v>
       </c>
@@ -10734,9 +10269,8 @@
       <c r="M464" s="4"/>
       <c r="N464" s="4"/>
       <c r="O464" s="4"/>
-      <c r="P464" s="4"/>
-    </row>
-    <row r="465" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="465" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A465" s="1">
         <v>231.51</v>
       </c>
@@ -10756,9 +10290,8 @@
       <c r="M465" s="4"/>
       <c r="N465" s="4"/>
       <c r="O465" s="4"/>
-      <c r="P465" s="4"/>
-    </row>
-    <row r="466" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="466" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A466" s="1">
         <v>232.01</v>
       </c>
@@ -10778,9 +10311,8 @@
       <c r="M466" s="4"/>
       <c r="N466" s="4"/>
       <c r="O466" s="4"/>
-      <c r="P466" s="4"/>
-    </row>
-    <row r="467" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="467" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A467" s="1">
         <v>232.51</v>
       </c>
@@ -10800,9 +10332,8 @@
       <c r="M467" s="4"/>
       <c r="N467" s="4"/>
       <c r="O467" s="4"/>
-      <c r="P467" s="4"/>
-    </row>
-    <row r="468" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="468" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A468" s="1">
         <v>233.01</v>
       </c>
@@ -10822,9 +10353,8 @@
       <c r="M468" s="4"/>
       <c r="N468" s="4"/>
       <c r="O468" s="4"/>
-      <c r="P468" s="4"/>
-    </row>
-    <row r="469" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="469" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A469" s="1">
         <v>233.51</v>
       </c>
@@ -10844,9 +10374,8 @@
       <c r="M469" s="4"/>
       <c r="N469" s="4"/>
       <c r="O469" s="4"/>
-      <c r="P469" s="4"/>
-    </row>
-    <row r="470" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="470" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A470" s="1">
         <v>234.01</v>
       </c>
@@ -10866,9 +10395,8 @@
       <c r="M470" s="4"/>
       <c r="N470" s="4"/>
       <c r="O470" s="4"/>
-      <c r="P470" s="4"/>
-    </row>
-    <row r="471" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="471" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A471" s="1">
         <v>234.51</v>
       </c>
@@ -10888,9 +10416,8 @@
       <c r="M471" s="4"/>
       <c r="N471" s="4"/>
       <c r="O471" s="4"/>
-      <c r="P471" s="4"/>
-    </row>
-    <row r="472" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="472" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A472" s="1">
         <v>235.01</v>
       </c>
@@ -10910,9 +10437,8 @@
       <c r="M472" s="4"/>
       <c r="N472" s="4"/>
       <c r="O472" s="4"/>
-      <c r="P472" s="4"/>
-    </row>
-    <row r="473" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="473" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A473" s="1">
         <v>235.51</v>
       </c>
@@ -10932,9 +10458,8 @@
       <c r="M473" s="4"/>
       <c r="N473" s="4"/>
       <c r="O473" s="4"/>
-      <c r="P473" s="4"/>
-    </row>
-    <row r="474" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="474" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A474" s="1">
         <v>236.01</v>
       </c>
@@ -10954,9 +10479,8 @@
       <c r="M474" s="4"/>
       <c r="N474" s="4"/>
       <c r="O474" s="4"/>
-      <c r="P474" s="4"/>
-    </row>
-    <row r="475" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="475" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A475" s="1">
         <v>236.51</v>
       </c>
@@ -10976,9 +10500,8 @@
       <c r="M475" s="4"/>
       <c r="N475" s="4"/>
       <c r="O475" s="4"/>
-      <c r="P475" s="4"/>
-    </row>
-    <row r="476" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="476" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A476" s="1">
         <v>237.01</v>
       </c>
@@ -10998,9 +10521,8 @@
       <c r="M476" s="4"/>
       <c r="N476" s="4"/>
       <c r="O476" s="4"/>
-      <c r="P476" s="4"/>
-    </row>
-    <row r="477" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="477" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A477" s="1">
         <v>237.51</v>
       </c>
@@ -11020,9 +10542,8 @@
       <c r="M477" s="4"/>
       <c r="N477" s="4"/>
       <c r="O477" s="4"/>
-      <c r="P477" s="4"/>
-    </row>
-    <row r="478" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="478" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A478" s="1">
         <v>238.01</v>
       </c>
@@ -11042,9 +10563,8 @@
       <c r="M478" s="4"/>
       <c r="N478" s="4"/>
       <c r="O478" s="4"/>
-      <c r="P478" s="4"/>
-    </row>
-    <row r="479" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="479" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A479" s="1">
         <v>238.51</v>
       </c>
@@ -11064,9 +10584,8 @@
       <c r="M479" s="4"/>
       <c r="N479" s="4"/>
       <c r="O479" s="4"/>
-      <c r="P479" s="4"/>
-    </row>
-    <row r="480" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="480" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A480" s="1">
         <v>239.01</v>
       </c>
@@ -11086,9 +10605,8 @@
       <c r="M480" s="4"/>
       <c r="N480" s="4"/>
       <c r="O480" s="4"/>
-      <c r="P480" s="4"/>
-    </row>
-    <row r="481" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="481" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A481" s="1">
         <v>239.51</v>
       </c>
@@ -11108,9 +10626,8 @@
       <c r="M481" s="4"/>
       <c r="N481" s="4"/>
       <c r="O481" s="4"/>
-      <c r="P481" s="4"/>
-    </row>
-    <row r="482" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="482" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A482" s="1">
         <v>240.01</v>
       </c>
@@ -11130,9 +10647,8 @@
       <c r="M482" s="4"/>
       <c r="N482" s="4"/>
       <c r="O482" s="4"/>
-      <c r="P482" s="4"/>
-    </row>
-    <row r="483" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="483" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A483" s="1">
         <v>240.51</v>
       </c>
@@ -11152,9 +10668,8 @@
       <c r="M483" s="4"/>
       <c r="N483" s="4"/>
       <c r="O483" s="4"/>
-      <c r="P483" s="4"/>
-    </row>
-    <row r="484" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="484" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A484" s="1">
         <v>241.01</v>
       </c>
@@ -11174,9 +10689,8 @@
       <c r="M484" s="4"/>
       <c r="N484" s="4"/>
       <c r="O484" s="4"/>
-      <c r="P484" s="4"/>
-    </row>
-    <row r="485" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="485" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A485" s="1">
         <v>241.51</v>
       </c>
@@ -11196,9 +10710,8 @@
       <c r="M485" s="4"/>
       <c r="N485" s="4"/>
       <c r="O485" s="4"/>
-      <c r="P485" s="4"/>
-    </row>
-    <row r="486" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="486" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A486" s="1">
         <v>242.01</v>
       </c>
@@ -11218,9 +10731,8 @@
       <c r="M486" s="4"/>
       <c r="N486" s="4"/>
       <c r="O486" s="4"/>
-      <c r="P486" s="4"/>
-    </row>
-    <row r="487" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="487" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A487" s="1">
         <v>242.51</v>
       </c>
@@ -11240,9 +10752,8 @@
       <c r="M487" s="4"/>
       <c r="N487" s="4"/>
       <c r="O487" s="4"/>
-      <c r="P487" s="4"/>
-    </row>
-    <row r="488" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="488" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A488" s="1">
         <v>243.01</v>
       </c>
@@ -11262,9 +10773,8 @@
       <c r="M488" s="4"/>
       <c r="N488" s="4"/>
       <c r="O488" s="4"/>
-      <c r="P488" s="4"/>
-    </row>
-    <row r="489" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="489" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A489" s="1">
         <v>243.51</v>
       </c>
@@ -11284,9 +10794,8 @@
       <c r="M489" s="4"/>
       <c r="N489" s="4"/>
       <c r="O489" s="4"/>
-      <c r="P489" s="4"/>
-    </row>
-    <row r="490" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="490" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A490" s="1">
         <v>244.01</v>
       </c>
@@ -11306,9 +10815,8 @@
       <c r="M490" s="4"/>
       <c r="N490" s="4"/>
       <c r="O490" s="4"/>
-      <c r="P490" s="4"/>
-    </row>
-    <row r="491" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="491" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A491" s="1">
         <v>244.51</v>
       </c>
@@ -11328,9 +10836,8 @@
       <c r="M491" s="4"/>
       <c r="N491" s="4"/>
       <c r="O491" s="4"/>
-      <c r="P491" s="4"/>
-    </row>
-    <row r="492" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="492" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A492" s="1">
         <v>245.01</v>
       </c>
@@ -11350,9 +10857,8 @@
       <c r="M492" s="4"/>
       <c r="N492" s="4"/>
       <c r="O492" s="4"/>
-      <c r="P492" s="4"/>
-    </row>
-    <row r="493" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="493" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A493" s="1">
         <v>245.51</v>
       </c>
@@ -11372,9 +10878,8 @@
       <c r="M493" s="4"/>
       <c r="N493" s="4"/>
       <c r="O493" s="4"/>
-      <c r="P493" s="4"/>
-    </row>
-    <row r="494" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="494" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A494" s="1">
         <v>246.01</v>
       </c>
@@ -11394,9 +10899,8 @@
       <c r="M494" s="4"/>
       <c r="N494" s="4"/>
       <c r="O494" s="4"/>
-      <c r="P494" s="4"/>
-    </row>
-    <row r="495" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="495" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A495" s="1">
         <v>246.51</v>
       </c>
@@ -11416,9 +10920,8 @@
       <c r="M495" s="4"/>
       <c r="N495" s="4"/>
       <c r="O495" s="4"/>
-      <c r="P495" s="4"/>
-    </row>
-    <row r="496" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="496" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A496" s="1">
         <v>247.01</v>
       </c>
@@ -11438,9 +10941,8 @@
       <c r="M496" s="4"/>
       <c r="N496" s="4"/>
       <c r="O496" s="4"/>
-      <c r="P496" s="4"/>
-    </row>
-    <row r="497" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="497" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A497" s="1">
         <v>247.51</v>
       </c>
@@ -11460,9 +10962,8 @@
       <c r="M497" s="4"/>
       <c r="N497" s="4"/>
       <c r="O497" s="4"/>
-      <c r="P497" s="4"/>
-    </row>
-    <row r="498" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="498" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A498" s="1">
         <v>248.01</v>
       </c>
@@ -11482,9 +10983,8 @@
       <c r="M498" s="4"/>
       <c r="N498" s="4"/>
       <c r="O498" s="4"/>
-      <c r="P498" s="4"/>
-    </row>
-    <row r="499" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="499" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A499" s="1">
         <v>248.51</v>
       </c>
@@ -11504,9 +11004,8 @@
       <c r="M499" s="4"/>
       <c r="N499" s="4"/>
       <c r="O499" s="4"/>
-      <c r="P499" s="4"/>
-    </row>
-    <row r="500" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="500" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A500" s="1">
         <v>249.01</v>
       </c>
@@ -11526,9 +11025,8 @@
       <c r="M500" s="4"/>
       <c r="N500" s="4"/>
       <c r="O500" s="4"/>
-      <c r="P500" s="4"/>
-    </row>
-    <row r="501" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="501" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A501" s="1">
         <v>249.51</v>
       </c>
@@ -11548,9 +11046,8 @@
       <c r="M501" s="4"/>
       <c r="N501" s="4"/>
       <c r="O501" s="4"/>
-      <c r="P501" s="4"/>
-    </row>
-    <row r="502" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="502" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A502" s="1">
         <v>250.01</v>
       </c>
@@ -11570,9 +11067,8 @@
       <c r="M502" s="4"/>
       <c r="N502" s="4"/>
       <c r="O502" s="4"/>
-      <c r="P502" s="4"/>
-    </row>
-    <row r="503" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="503" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A503" s="1">
         <v>250.51</v>
       </c>
@@ -11592,9 +11088,8 @@
       <c r="M503" s="4"/>
       <c r="N503" s="4"/>
       <c r="O503" s="4"/>
-      <c r="P503" s="4"/>
-    </row>
-    <row r="504" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="504" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A504" s="1">
         <v>251.01</v>
       </c>
@@ -11614,9 +11109,8 @@
       <c r="M504" s="4"/>
       <c r="N504" s="4"/>
       <c r="O504" s="4"/>
-      <c r="P504" s="4"/>
-    </row>
-    <row r="505" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="505" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A505" s="1">
         <v>251.51</v>
       </c>
@@ -11636,9 +11130,8 @@
       <c r="M505" s="4"/>
       <c r="N505" s="4"/>
       <c r="O505" s="4"/>
-      <c r="P505" s="4"/>
-    </row>
-    <row r="506" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="506" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A506" s="1">
         <v>252.01</v>
       </c>
@@ -11658,9 +11151,8 @@
       <c r="M506" s="4"/>
       <c r="N506" s="4"/>
       <c r="O506" s="4"/>
-      <c r="P506" s="4"/>
-    </row>
-    <row r="507" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="507" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A507" s="1">
         <v>252.51</v>
       </c>
@@ -11680,9 +11172,8 @@
       <c r="M507" s="4"/>
       <c r="N507" s="4"/>
       <c r="O507" s="4"/>
-      <c r="P507" s="4"/>
-    </row>
-    <row r="508" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="508" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A508" s="1">
         <v>253.01</v>
       </c>
@@ -11702,9 +11193,8 @@
       <c r="M508" s="4"/>
       <c r="N508" s="4"/>
       <c r="O508" s="4"/>
-      <c r="P508" s="4"/>
-    </row>
-    <row r="509" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="509" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A509" s="1">
         <v>253.51</v>
       </c>
@@ -11724,9 +11214,8 @@
       <c r="M509" s="4"/>
       <c r="N509" s="4"/>
       <c r="O509" s="4"/>
-      <c r="P509" s="4"/>
-    </row>
-    <row r="510" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="510" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A510" s="1">
         <v>254.01</v>
       </c>
@@ -11746,9 +11235,8 @@
       <c r="M510" s="4"/>
       <c r="N510" s="4"/>
       <c r="O510" s="4"/>
-      <c r="P510" s="4"/>
-    </row>
-    <row r="511" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="511" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A511" s="1">
         <v>254.51</v>
       </c>
@@ -11768,9 +11256,8 @@
       <c r="M511" s="4"/>
       <c r="N511" s="4"/>
       <c r="O511" s="4"/>
-      <c r="P511" s="4"/>
-    </row>
-    <row r="512" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="512" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A512" s="1">
         <v>255.01</v>
       </c>
@@ -11790,9 +11277,8 @@
       <c r="M512" s="4"/>
       <c r="N512" s="4"/>
       <c r="O512" s="4"/>
-      <c r="P512" s="4"/>
-    </row>
-    <row r="513" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="513" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A513" s="1">
         <v>255.51</v>
       </c>
@@ -11812,9 +11298,8 @@
       <c r="M513" s="4"/>
       <c r="N513" s="4"/>
       <c r="O513" s="4"/>
-      <c r="P513" s="4"/>
-    </row>
-    <row r="514" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="514" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A514" s="1">
         <v>256.01</v>
       </c>
@@ -11834,9 +11319,8 @@
       <c r="M514" s="4"/>
       <c r="N514" s="4"/>
       <c r="O514" s="4"/>
-      <c r="P514" s="4"/>
-    </row>
-    <row r="515" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="515" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A515" s="1">
         <v>256.51</v>
       </c>
@@ -11856,9 +11340,8 @@
       <c r="M515" s="4"/>
       <c r="N515" s="4"/>
       <c r="O515" s="4"/>
-      <c r="P515" s="4"/>
-    </row>
-    <row r="516" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="516" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A516" s="1">
         <v>257.01</v>
       </c>
@@ -11878,9 +11361,8 @@
       <c r="M516" s="4"/>
       <c r="N516" s="4"/>
       <c r="O516" s="4"/>
-      <c r="P516" s="4"/>
-    </row>
-    <row r="517" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="517" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A517" s="1">
         <v>257.51</v>
       </c>
@@ -11900,9 +11382,8 @@
       <c r="M517" s="4"/>
       <c r="N517" s="4"/>
       <c r="O517" s="4"/>
-      <c r="P517" s="4"/>
-    </row>
-    <row r="518" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="518" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A518" s="1">
         <v>258.01</v>
       </c>
@@ -11922,9 +11403,8 @@
       <c r="M518" s="4"/>
       <c r="N518" s="4"/>
       <c r="O518" s="4"/>
-      <c r="P518" s="4"/>
-    </row>
-    <row r="519" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="519" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A519" s="1">
         <v>258.51</v>
       </c>
@@ -11944,9 +11424,8 @@
       <c r="M519" s="4"/>
       <c r="N519" s="4"/>
       <c r="O519" s="4"/>
-      <c r="P519" s="4"/>
-    </row>
-    <row r="520" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="520" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A520" s="1">
         <v>259.01</v>
       </c>
@@ -11966,9 +11445,8 @@
       <c r="M520" s="4"/>
       <c r="N520" s="4"/>
       <c r="O520" s="4"/>
-      <c r="P520" s="4"/>
-    </row>
-    <row r="521" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="521" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A521" s="1">
         <v>259.51</v>
       </c>
@@ -11988,9 +11466,8 @@
       <c r="M521" s="4"/>
       <c r="N521" s="4"/>
       <c r="O521" s="4"/>
-      <c r="P521" s="4"/>
-    </row>
-    <row r="522" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="522" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A522" s="1">
         <v>260.01</v>
       </c>
@@ -12010,9 +11487,8 @@
       <c r="M522" s="4"/>
       <c r="N522" s="4"/>
       <c r="O522" s="4"/>
-      <c r="P522" s="4"/>
-    </row>
-    <row r="523" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="523" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A523" s="1">
         <v>260.51</v>
       </c>
@@ -12032,9 +11508,8 @@
       <c r="M523" s="4"/>
       <c r="N523" s="4"/>
       <c r="O523" s="4"/>
-      <c r="P523" s="4"/>
-    </row>
-    <row r="524" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="524" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A524" s="1">
         <v>261.01</v>
       </c>
@@ -12054,9 +11529,8 @@
       <c r="M524" s="4"/>
       <c r="N524" s="4"/>
       <c r="O524" s="4"/>
-      <c r="P524" s="4"/>
-    </row>
-    <row r="525" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="525" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A525" s="1">
         <v>261.51</v>
       </c>
@@ -12076,9 +11550,8 @@
       <c r="M525" s="4"/>
       <c r="N525" s="4"/>
       <c r="O525" s="4"/>
-      <c r="P525" s="4"/>
-    </row>
-    <row r="526" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="526" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A526" s="1">
         <v>262.01</v>
       </c>
@@ -12098,9 +11571,8 @@
       <c r="M526" s="4"/>
       <c r="N526" s="4"/>
       <c r="O526" s="4"/>
-      <c r="P526" s="4"/>
-    </row>
-    <row r="527" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="527" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A527" s="1">
         <v>262.51</v>
       </c>
@@ -12120,9 +11592,8 @@
       <c r="M527" s="4"/>
       <c r="N527" s="4"/>
       <c r="O527" s="4"/>
-      <c r="P527" s="4"/>
-    </row>
-    <row r="528" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="528" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A528" s="1">
         <v>263.01</v>
       </c>
@@ -12142,9 +11613,8 @@
       <c r="M528" s="4"/>
       <c r="N528" s="4"/>
       <c r="O528" s="4"/>
-      <c r="P528" s="4"/>
-    </row>
-    <row r="529" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="529" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A529" s="1">
         <v>263.51</v>
       </c>
@@ -12164,9 +11634,8 @@
       <c r="M529" s="4"/>
       <c r="N529" s="4"/>
       <c r="O529" s="4"/>
-      <c r="P529" s="4"/>
-    </row>
-    <row r="530" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="530" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A530" s="1">
         <v>264.01</v>
       </c>
@@ -12186,9 +11655,8 @@
       <c r="M530" s="4"/>
       <c r="N530" s="4"/>
       <c r="O530" s="4"/>
-      <c r="P530" s="4"/>
-    </row>
-    <row r="531" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="531" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A531" s="1">
         <v>264.51</v>
       </c>
@@ -12208,9 +11676,8 @@
       <c r="M531" s="4"/>
       <c r="N531" s="4"/>
       <c r="O531" s="4"/>
-      <c r="P531" s="4"/>
-    </row>
-    <row r="532" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="532" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A532" s="1">
         <v>265.01</v>
       </c>
@@ -12230,9 +11697,8 @@
       <c r="M532" s="4"/>
       <c r="N532" s="4"/>
       <c r="O532" s="4"/>
-      <c r="P532" s="4"/>
-    </row>
-    <row r="533" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="533" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A533" s="1">
         <v>265.51</v>
       </c>
@@ -12252,9 +11718,8 @@
       <c r="M533" s="4"/>
       <c r="N533" s="4"/>
       <c r="O533" s="4"/>
-      <c r="P533" s="4"/>
-    </row>
-    <row r="534" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="534" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A534" s="1">
         <v>266.01</v>
       </c>
@@ -12274,9 +11739,8 @@
       <c r="M534" s="4"/>
       <c r="N534" s="4"/>
       <c r="O534" s="4"/>
-      <c r="P534" s="4"/>
-    </row>
-    <row r="535" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="535" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A535" s="1">
         <v>266.51</v>
       </c>
@@ -12296,9 +11760,8 @@
       <c r="M535" s="4"/>
       <c r="N535" s="4"/>
       <c r="O535" s="4"/>
-      <c r="P535" s="4"/>
-    </row>
-    <row r="536" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="536" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A536" s="1">
         <v>267.01</v>
       </c>
@@ -12318,9 +11781,8 @@
       <c r="M536" s="4"/>
       <c r="N536" s="4"/>
       <c r="O536" s="4"/>
-      <c r="P536" s="4"/>
-    </row>
-    <row r="537" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="537" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A537" s="1">
         <v>267.51</v>
       </c>
@@ -12340,9 +11802,8 @@
       <c r="M537" s="4"/>
       <c r="N537" s="4"/>
       <c r="O537" s="4"/>
-      <c r="P537" s="4"/>
-    </row>
-    <row r="538" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="538" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A538" s="1">
         <v>268.01</v>
       </c>
@@ -12362,9 +11823,8 @@
       <c r="M538" s="4"/>
       <c r="N538" s="4"/>
       <c r="O538" s="4"/>
-      <c r="P538" s="4"/>
-    </row>
-    <row r="539" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="539" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A539" s="1">
         <v>268.51</v>
       </c>
@@ -12384,9 +11844,8 @@
       <c r="M539" s="4"/>
       <c r="N539" s="4"/>
       <c r="O539" s="4"/>
-      <c r="P539" s="4"/>
-    </row>
-    <row r="540" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="540" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A540" s="1">
         <v>269.01</v>
       </c>
@@ -12406,9 +11865,8 @@
       <c r="M540" s="4"/>
       <c r="N540" s="4"/>
       <c r="O540" s="4"/>
-      <c r="P540" s="4"/>
-    </row>
-    <row r="541" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="541" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A541" s="1">
         <v>269.51</v>
       </c>
@@ -12428,9 +11886,8 @@
       <c r="M541" s="4"/>
       <c r="N541" s="4"/>
       <c r="O541" s="4"/>
-      <c r="P541" s="4"/>
-    </row>
-    <row r="542" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="542" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A542" s="1">
         <v>270.01</v>
       </c>
@@ -12450,9 +11907,8 @@
       <c r="M542" s="4"/>
       <c r="N542" s="4"/>
       <c r="O542" s="4"/>
-      <c r="P542" s="4"/>
-    </row>
-    <row r="543" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="543" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A543" s="1">
         <v>270.51</v>
       </c>
@@ -12472,9 +11928,8 @@
       <c r="M543" s="4"/>
       <c r="N543" s="4"/>
       <c r="O543" s="4"/>
-      <c r="P543" s="4"/>
-    </row>
-    <row r="544" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="544" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A544" s="1">
         <v>271.01</v>
       </c>
@@ -12494,9 +11949,8 @@
       <c r="M544" s="4"/>
       <c r="N544" s="4"/>
       <c r="O544" s="4"/>
-      <c r="P544" s="4"/>
-    </row>
-    <row r="545" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="545" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A545" s="1">
         <v>271.51</v>
       </c>
@@ -12516,9 +11970,8 @@
       <c r="M545" s="4"/>
       <c r="N545" s="4"/>
       <c r="O545" s="4"/>
-      <c r="P545" s="4"/>
-    </row>
-    <row r="546" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="546" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A546" s="1">
         <v>272.01</v>
       </c>
@@ -12538,9 +11991,8 @@
       <c r="M546" s="4"/>
       <c r="N546" s="4"/>
       <c r="O546" s="4"/>
-      <c r="P546" s="4"/>
-    </row>
-    <row r="547" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="547" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A547" s="1">
         <v>272.51</v>
       </c>
@@ -12560,9 +12012,8 @@
       <c r="M547" s="4"/>
       <c r="N547" s="4"/>
       <c r="O547" s="4"/>
-      <c r="P547" s="4"/>
-    </row>
-    <row r="548" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="548" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A548" s="1">
         <v>273.01</v>
       </c>
@@ -12582,9 +12033,8 @@
       <c r="M548" s="4"/>
       <c r="N548" s="4"/>
       <c r="O548" s="4"/>
-      <c r="P548" s="4"/>
-    </row>
-    <row r="549" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="549" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A549" s="1">
         <v>273.51</v>
       </c>
@@ -12604,9 +12054,8 @@
       <c r="M549" s="4"/>
       <c r="N549" s="4"/>
       <c r="O549" s="4"/>
-      <c r="P549" s="4"/>
-    </row>
-    <row r="550" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="550" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A550" s="1">
         <v>274.01</v>
       </c>
@@ -12626,9 +12075,8 @@
       <c r="M550" s="4"/>
       <c r="N550" s="4"/>
       <c r="O550" s="4"/>
-      <c r="P550" s="4"/>
-    </row>
-    <row r="551" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="551" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A551" s="1">
         <v>274.51</v>
       </c>
@@ -12648,9 +12096,8 @@
       <c r="M551" s="4"/>
       <c r="N551" s="4"/>
       <c r="O551" s="4"/>
-      <c r="P551" s="4"/>
-    </row>
-    <row r="552" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="552" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A552" s="1">
         <v>275.01</v>
       </c>
@@ -12670,9 +12117,8 @@
       <c r="M552" s="4"/>
       <c r="N552" s="4"/>
       <c r="O552" s="4"/>
-      <c r="P552" s="4"/>
-    </row>
-    <row r="553" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="553" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A553" s="1">
         <v>275.51</v>
       </c>
@@ -12692,9 +12138,8 @@
       <c r="M553" s="4"/>
       <c r="N553" s="4"/>
       <c r="O553" s="4"/>
-      <c r="P553" s="4"/>
-    </row>
-    <row r="554" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="554" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A554" s="1">
         <v>276.01</v>
       </c>
@@ -12714,9 +12159,8 @@
       <c r="M554" s="4"/>
       <c r="N554" s="4"/>
       <c r="O554" s="4"/>
-      <c r="P554" s="4"/>
-    </row>
-    <row r="555" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="555" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A555" s="1">
         <v>276.51</v>
       </c>
@@ -12736,9 +12180,8 @@
       <c r="M555" s="4"/>
       <c r="N555" s="4"/>
       <c r="O555" s="4"/>
-      <c r="P555" s="4"/>
-    </row>
-    <row r="556" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="556" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A556" s="1">
         <v>277.01</v>
       </c>
@@ -12758,9 +12201,8 @@
       <c r="M556" s="4"/>
       <c r="N556" s="4"/>
       <c r="O556" s="4"/>
-      <c r="P556" s="4"/>
-    </row>
-    <row r="557" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="557" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A557" s="1">
         <v>277.51</v>
       </c>
@@ -12780,9 +12222,8 @@
       <c r="M557" s="4"/>
       <c r="N557" s="4"/>
       <c r="O557" s="4"/>
-      <c r="P557" s="4"/>
-    </row>
-    <row r="558" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="558" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A558" s="1">
         <v>278.01</v>
       </c>
@@ -12802,9 +12243,8 @@
       <c r="M558" s="4"/>
       <c r="N558" s="4"/>
       <c r="O558" s="4"/>
-      <c r="P558" s="4"/>
-    </row>
-    <row r="559" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="559" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A559" s="1">
         <v>278.51</v>
       </c>
@@ -12824,9 +12264,8 @@
       <c r="M559" s="4"/>
       <c r="N559" s="4"/>
       <c r="O559" s="4"/>
-      <c r="P559" s="4"/>
-    </row>
-    <row r="560" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="560" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A560" s="1">
         <v>279.01</v>
       </c>
@@ -12846,9 +12285,8 @@
       <c r="M560" s="4"/>
       <c r="N560" s="4"/>
       <c r="O560" s="4"/>
-      <c r="P560" s="4"/>
-    </row>
-    <row r="561" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="561" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A561" s="1">
         <v>279.51</v>
       </c>
@@ -12868,9 +12306,8 @@
       <c r="M561" s="4"/>
       <c r="N561" s="4"/>
       <c r="O561" s="4"/>
-      <c r="P561" s="4"/>
-    </row>
-    <row r="562" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="562" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A562" s="1">
         <v>280.01</v>
       </c>
@@ -12890,9 +12327,8 @@
       <c r="M562" s="4"/>
       <c r="N562" s="4"/>
       <c r="O562" s="4"/>
-      <c r="P562" s="4"/>
-    </row>
-    <row r="563" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="563" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A563" s="1">
         <v>280.51</v>
       </c>
@@ -12912,9 +12348,8 @@
       <c r="M563" s="4"/>
       <c r="N563" s="4"/>
       <c r="O563" s="4"/>
-      <c r="P563" s="4"/>
-    </row>
-    <row r="564" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="564" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A564" s="1">
         <v>281.01</v>
       </c>
@@ -12934,9 +12369,8 @@
       <c r="M564" s="4"/>
       <c r="N564" s="4"/>
       <c r="O564" s="4"/>
-      <c r="P564" s="4"/>
-    </row>
-    <row r="565" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="565" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A565" s="1">
         <v>281.51</v>
       </c>
@@ -12956,9 +12390,8 @@
       <c r="M565" s="4"/>
       <c r="N565" s="4"/>
       <c r="O565" s="4"/>
-      <c r="P565" s="4"/>
-    </row>
-    <row r="566" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="566" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A566" s="1">
         <v>282.01</v>
       </c>
@@ -12978,9 +12411,8 @@
       <c r="M566" s="4"/>
       <c r="N566" s="4"/>
       <c r="O566" s="4"/>
-      <c r="P566" s="4"/>
-    </row>
-    <row r="567" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="567" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A567" s="1">
         <v>282.51</v>
       </c>
@@ -13000,9 +12432,8 @@
       <c r="M567" s="4"/>
       <c r="N567" s="4"/>
       <c r="O567" s="4"/>
-      <c r="P567" s="4"/>
-    </row>
-    <row r="568" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="568" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A568" s="1">
         <v>283.01</v>
       </c>
@@ -13022,9 +12453,8 @@
       <c r="M568" s="4"/>
       <c r="N568" s="4"/>
       <c r="O568" s="4"/>
-      <c r="P568" s="4"/>
-    </row>
-    <row r="569" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="569" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A569" s="1">
         <v>283.51</v>
       </c>
@@ -13044,9 +12474,8 @@
       <c r="M569" s="4"/>
       <c r="N569" s="4"/>
       <c r="O569" s="4"/>
-      <c r="P569" s="4"/>
-    </row>
-    <row r="570" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="570" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A570" s="1">
         <v>284.01</v>
       </c>
@@ -13066,9 +12495,8 @@
       <c r="M570" s="4"/>
       <c r="N570" s="4"/>
       <c r="O570" s="4"/>
-      <c r="P570" s="4"/>
-    </row>
-    <row r="571" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="571" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A571" s="1">
         <v>284.51</v>
       </c>
@@ -13088,9 +12516,8 @@
       <c r="M571" s="4"/>
       <c r="N571" s="4"/>
       <c r="O571" s="4"/>
-      <c r="P571" s="4"/>
-    </row>
-    <row r="572" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="572" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A572" s="1">
         <v>285.01</v>
       </c>
@@ -13110,9 +12537,8 @@
       <c r="M572" s="4"/>
       <c r="N572" s="4"/>
       <c r="O572" s="4"/>
-      <c r="P572" s="4"/>
-    </row>
-    <row r="573" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="573" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A573" s="1">
         <v>285.51</v>
       </c>
@@ -13132,9 +12558,8 @@
       <c r="M573" s="4"/>
       <c r="N573" s="4"/>
       <c r="O573" s="4"/>
-      <c r="P573" s="4"/>
-    </row>
-    <row r="574" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="574" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A574" s="1">
         <v>286.01</v>
       </c>
@@ -13154,9 +12579,8 @@
       <c r="M574" s="4"/>
       <c r="N574" s="4"/>
       <c r="O574" s="4"/>
-      <c r="P574" s="4"/>
-    </row>
-    <row r="575" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="575" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A575" s="1">
         <v>286.51</v>
       </c>
@@ -13176,9 +12600,8 @@
       <c r="M575" s="4"/>
       <c r="N575" s="4"/>
       <c r="O575" s="4"/>
-      <c r="P575" s="4"/>
-    </row>
-    <row r="576" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="576" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A576" s="1">
         <v>287.01</v>
       </c>
@@ -13198,9 +12621,8 @@
       <c r="M576" s="4"/>
       <c r="N576" s="4"/>
       <c r="O576" s="4"/>
-      <c r="P576" s="4"/>
-    </row>
-    <row r="577" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="577" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A577" s="1">
         <v>287.51</v>
       </c>
@@ -13220,9 +12642,8 @@
       <c r="M577" s="4"/>
       <c r="N577" s="4"/>
       <c r="O577" s="4"/>
-      <c r="P577" s="4"/>
-    </row>
-    <row r="578" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="578" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A578" s="1">
         <v>288.01</v>
       </c>
@@ -13242,9 +12663,8 @@
       <c r="M578" s="4"/>
       <c r="N578" s="4"/>
       <c r="O578" s="4"/>
-      <c r="P578" s="4"/>
-    </row>
-    <row r="579" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="579" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A579" s="1">
         <v>288.51</v>
       </c>
@@ -13264,9 +12684,8 @@
       <c r="M579" s="4"/>
       <c r="N579" s="4"/>
       <c r="O579" s="4"/>
-      <c r="P579" s="4"/>
-    </row>
-    <row r="580" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="580" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A580" s="1">
         <v>289.01</v>
       </c>
@@ -13286,9 +12705,8 @@
       <c r="M580" s="4"/>
       <c r="N580" s="4"/>
       <c r="O580" s="4"/>
-      <c r="P580" s="4"/>
-    </row>
-    <row r="581" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="581" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A581" s="1">
         <v>289.51</v>
       </c>
@@ -13308,9 +12726,8 @@
       <c r="M581" s="4"/>
       <c r="N581" s="4"/>
       <c r="O581" s="4"/>
-      <c r="P581" s="4"/>
-    </row>
-    <row r="582" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="582" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A582" s="1">
         <v>290.01</v>
       </c>
@@ -13330,9 +12747,8 @@
       <c r="M582" s="4"/>
       <c r="N582" s="4"/>
       <c r="O582" s="4"/>
-      <c r="P582" s="4"/>
-    </row>
-    <row r="583" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="583" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A583" s="1">
         <v>290.51</v>
       </c>
@@ -13352,9 +12768,8 @@
       <c r="M583" s="4"/>
       <c r="N583" s="4"/>
       <c r="O583" s="4"/>
-      <c r="P583" s="4"/>
-    </row>
-    <row r="584" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="584" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A584" s="1">
         <v>291.01</v>
       </c>
@@ -13374,9 +12789,8 @@
       <c r="M584" s="4"/>
       <c r="N584" s="4"/>
       <c r="O584" s="4"/>
-      <c r="P584" s="4"/>
-    </row>
-    <row r="585" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="585" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A585" s="1">
         <v>291.51</v>
       </c>
@@ -13396,9 +12810,8 @@
       <c r="M585" s="4"/>
       <c r="N585" s="4"/>
       <c r="O585" s="4"/>
-      <c r="P585" s="4"/>
-    </row>
-    <row r="586" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="586" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A586" s="1">
         <v>292.01</v>
       </c>
@@ -13418,9 +12831,8 @@
       <c r="M586" s="4"/>
       <c r="N586" s="4"/>
       <c r="O586" s="4"/>
-      <c r="P586" s="4"/>
-    </row>
-    <row r="587" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="587" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A587" s="1">
         <v>292.51</v>
       </c>
@@ -13440,9 +12852,8 @@
       <c r="M587" s="4"/>
       <c r="N587" s="4"/>
       <c r="O587" s="4"/>
-      <c r="P587" s="4"/>
-    </row>
-    <row r="588" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="588" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A588" s="1">
         <v>293.01</v>
       </c>
@@ -13462,9 +12873,8 @@
       <c r="M588" s="4"/>
       <c r="N588" s="4"/>
       <c r="O588" s="4"/>
-      <c r="P588" s="4"/>
-    </row>
-    <row r="589" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="589" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A589" s="1">
         <v>293.51</v>
       </c>
@@ -13484,9 +12894,8 @@
       <c r="M589" s="4"/>
       <c r="N589" s="4"/>
       <c r="O589" s="4"/>
-      <c r="P589" s="4"/>
-    </row>
-    <row r="590" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="590" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A590" s="1">
         <v>294.01</v>
       </c>
@@ -13506,9 +12915,8 @@
       <c r="M590" s="4"/>
       <c r="N590" s="4"/>
       <c r="O590" s="4"/>
-      <c r="P590" s="4"/>
-    </row>
-    <row r="591" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="591" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A591" s="1">
         <v>294.51</v>
       </c>
@@ -13528,9 +12936,8 @@
       <c r="M591" s="4"/>
       <c r="N591" s="4"/>
       <c r="O591" s="4"/>
-      <c r="P591" s="4"/>
-    </row>
-    <row r="592" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="592" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A592" s="1">
         <v>295.01</v>
       </c>
@@ -13550,9 +12957,8 @@
       <c r="M592" s="4"/>
       <c r="N592" s="4"/>
       <c r="O592" s="4"/>
-      <c r="P592" s="4"/>
-    </row>
-    <row r="593" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="593" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A593" s="1">
         <v>295.51</v>
       </c>
@@ -13572,9 +12978,8 @@
       <c r="M593" s="4"/>
       <c r="N593" s="4"/>
       <c r="O593" s="4"/>
-      <c r="P593" s="4"/>
-    </row>
-    <row r="594" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="594" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A594" s="1">
         <v>296.01</v>
       </c>
@@ -13594,9 +12999,8 @@
       <c r="M594" s="4"/>
       <c r="N594" s="4"/>
       <c r="O594" s="4"/>
-      <c r="P594" s="4"/>
-    </row>
-    <row r="595" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="595" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A595" s="1">
         <v>296.51</v>
       </c>
@@ -13616,9 +13020,8 @@
       <c r="M595" s="4"/>
       <c r="N595" s="4"/>
       <c r="O595" s="4"/>
-      <c r="P595" s="4"/>
-    </row>
-    <row r="596" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="596" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A596" s="1">
         <v>297.01</v>
       </c>
@@ -13638,9 +13041,8 @@
       <c r="M596" s="4"/>
       <c r="N596" s="4"/>
       <c r="O596" s="4"/>
-      <c r="P596" s="4"/>
-    </row>
-    <row r="597" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="597" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A597" s="1">
         <v>297.51</v>
       </c>
@@ -13660,9 +13062,8 @@
       <c r="M597" s="4"/>
       <c r="N597" s="4"/>
       <c r="O597" s="4"/>
-      <c r="P597" s="4"/>
-    </row>
-    <row r="598" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="598" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A598" s="1">
         <v>298.01</v>
       </c>
@@ -13682,9 +13083,8 @@
       <c r="M598" s="4"/>
       <c r="N598" s="4"/>
       <c r="O598" s="4"/>
-      <c r="P598" s="4"/>
-    </row>
-    <row r="599" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="599" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A599" s="1">
         <v>298.51</v>
       </c>
@@ -13704,9 +13104,8 @@
       <c r="M599" s="4"/>
       <c r="N599" s="4"/>
       <c r="O599" s="4"/>
-      <c r="P599" s="4"/>
-    </row>
-    <row r="600" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="600" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A600" s="1">
         <v>299.01</v>
       </c>
@@ -13726,9 +13125,8 @@
       <c r="M600" s="4"/>
       <c r="N600" s="4"/>
       <c r="O600" s="4"/>
-      <c r="P600" s="4"/>
-    </row>
-    <row r="601" spans="1:16" x14ac:dyDescent="0.35">
+    </row>
+    <row r="601" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A601" s="1">
         <v>299.51</v>
       </c>
@@ -13748,7 +13146,6 @@
       <c r="M601" s="4"/>
       <c r="N601" s="4"/>
       <c r="O601" s="4"/>
-      <c r="P601" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/public/file/International Standard Rates Upload Template.xlsx
+++ b/public/file/International Standard Rates Upload Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\sonic_3\public\file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62DB5763-0289-4D8F-8E91-3D71D2B22BDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A10B6E8B-9CF2-4D4E-9C39-376ECA6175DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -60,9 +60,6 @@
     <t>Range Up</t>
   </si>
   <si>
-    <t>Zone 8a</t>
-  </si>
-  <si>
     <t>Zone 1</t>
   </si>
   <si>
@@ -70,6 +67,9 @@
   </si>
   <si>
     <t>Zone 13</t>
+  </si>
+  <si>
+    <t>Zone 8</t>
   </si>
 </sst>
 </file>
@@ -508,7 +508,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>1</v>
@@ -529,7 +529,7 @@
         <v>6</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K1" s="2" t="s">
         <v>7</v>
@@ -541,10 +541,10 @@
         <v>9</v>
       </c>
       <c r="N1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.35">
